--- a/data/13_events_hazards.xlsx
+++ b/data/13_events_hazards.xlsx
@@ -2,16 +2,16 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Events" sheetId="1" r:id="Rc2a2df0054614fff"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Event Locations" sheetId="2" r:id="R766731f29c6945c5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Event Asset Links" sheetId="3" r:id="R52d7b71003b24a32"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Event Company Links" sheetId="4" r:id="Rda9075aa724f464d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Event System Links" sheetId="5" r:id="R326579a656474ef7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Impact Chains" sheetId="6" r:id="R4d8e432f72db42a6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Event Status History" sheetId="7" r:id="R6231c43257984dd2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Event Taxonomy" sheetId="8" r:id="Rf59faf7f981f41a3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="9" r:id="R0e2b7ce4ff374f42"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overview" sheetId="10" r:id="R67290d05a6384295"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Events" sheetId="1" r:id="R873502a9dd6d4641"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Event Locations" sheetId="2" r:id="R1d5f08521a8641a1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Event Asset Links" sheetId="3" r:id="R2bdfd348c64d45e3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Event Company Links" sheetId="4" r:id="R305f351b23024fad"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Event System Links" sheetId="5" r:id="R22638258982c489e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Impact Chains" sheetId="6" r:id="R1815e0523c854060"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Event Status History" sheetId="7" r:id="R35f78d471ca841a3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Event Taxonomy" sheetId="8" r:id="Rbba3d5b282df45c4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="9" r:id="R6838ce16c6c045fa"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overview" sheetId="10" r:id="R1854b9260d82449d"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1042,6 +1042,261 @@
         <x:v>https://www.adportsgroup.com/en/news-and-media/2026/04/14/ad-ports-group-signs-agreement-to-explore-investment-opportunities-in-the-port-of-constanta</x:v>
       </x:c>
     </x:row>
+    <x:row r="15">
+      <x:c r="A15" t="str">
+        <x:v>EVT132_001</x:v>
+      </x:c>
+      <x:c r="B15" t="str">
+        <x:v>2026-09-08</x:v>
+      </x:c>
+      <x:c r="C15"/>
+      <x:c r="D15" t="str">
+        <x:v>Conflict / Security</x:v>
+      </x:c>
+      <x:c r="E15" t="str">
+        <x:v>State-on-vessel kinetic strike</x:v>
+      </x:c>
+      <x:c r="F15" t="str">
+        <x:v>Severe</x:v>
+      </x:c>
+      <x:c r="G15" t="str">
+        <x:v>Occurred / vessels disabled</x:v>
+      </x:c>
+      <x:c r="H15" t="str">
+        <x:v>Maritime / Energy</x:v>
+      </x:c>
+      <x:c r="I15" t="str">
+        <x:v>Iran / Gulf of Oman</x:v>
+      </x:c>
+      <x:c r="J15" t="str">
+        <x:v>Gulf of Oman / Kharg Island</x:v>
+      </x:c>
+      <x:c r="K15" t="str">
+        <x:v>CENTCOM strikes five Iran-linked tankers</x:v>
+      </x:c>
+      <x:c r="L15" t="str">
+        <x:v>CENTCOM struck RIESCO, HORIZON 1, KAVIZ, CHARMINAR and DERYA after attempted IRGC missile attacks on a U.S. warship; crews were warned to abandon ship.</x:v>
+      </x:c>
+      <x:c r="M15" t="str">
+        <x:v>Five tankers rendered inoperable; RIESCO reported sunk</x:v>
+      </x:c>
+      <x:c r="N15" t="str">
+        <x:v>Direct loss of tanker capacity; higher kinetic, sanctions and war-risk exposure across Gulf energy shipping</x:v>
+      </x:c>
+      <x:c r="O15" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="P15" t="str">
+        <x:v>SRC132_001</x:v>
+      </x:c>
+      <x:c r="Q15" t="str">
+        <x:v>https://www.centcom.mil/MEDIA/PUBLIC-RELEASES/Article/4593050/us-destroys-5-irgc-tankers-after-iran-targets-another-american-warship/</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16">
+      <x:c r="A16" t="str">
+        <x:v>EVT132_002</x:v>
+      </x:c>
+      <x:c r="B16" t="str">
+        <x:v>2026-09-09</x:v>
+      </x:c>
+      <x:c r="C16"/>
+      <x:c r="D16" t="str">
+        <x:v>Conflict / Security</x:v>
+      </x:c>
+      <x:c r="E16" t="str">
+        <x:v>Drone strike on commercial tanker</x:v>
+      </x:c>
+      <x:c r="F16" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="G16" t="str">
+        <x:v>Occurred / damaged</x:v>
+      </x:c>
+      <x:c r="H16" t="str">
+        <x:v>Maritime / Energy</x:v>
+      </x:c>
+      <x:c r="I16" t="str">
+        <x:v>Iraq</x:v>
+      </x:c>
+      <x:c r="J16" t="str">
+        <x:v>Iraqi territorial waters / southeast of Al-Faw</x:v>
+      </x:c>
+      <x:c r="K16" t="str">
+        <x:v>NEW ANDROS struck by drone</x:v>
+      </x:c>
+      <x:c r="L16" t="str">
+        <x:v>NEW ANDROS was struck by a drone while holding about 2 million barrels of Iraqi fuel oil; crew safe and no cargo leakage reported.</x:v>
+      </x:c>
+      <x:c r="M16" t="str">
+        <x:v>Minor hull damage / fire; floating-storage operation disrupted</x:v>
+      </x:c>
+      <x:c r="N16" t="str">
+        <x:v>Extends tanker attack risk into Iraqi Gulf waters and storage operations</x:v>
+      </x:c>
+      <x:c r="O16" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="P16" t="str">
+        <x:v>SRC132_003</x:v>
+      </x:c>
+      <x:c r="Q16" t="str">
+        <x:v>https://www.reuters.com/world/europe/several-merchant-vessels-hit-by-disabling-fire-gulf-gulf-oman-2026-09-09/</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17">
+      <x:c r="A17" t="str">
+        <x:v>EVT132_003</x:v>
+      </x:c>
+      <x:c r="B17" t="str">
+        <x:v>2026-09-09</x:v>
+      </x:c>
+      <x:c r="C17"/>
+      <x:c r="D17" t="str">
+        <x:v>Conflict / Security</x:v>
+      </x:c>
+      <x:c r="E17" t="str">
+        <x:v>Projectile / water-ingress incident</x:v>
+      </x:c>
+      <x:c r="F17" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="G17" t="str">
+        <x:v>Active investigation</x:v>
+      </x:c>
+      <x:c r="H17" t="str">
+        <x:v>Maritime / Anchorage</x:v>
+      </x:c>
+      <x:c r="I17" t="str">
+        <x:v>United Arab Emirates</x:v>
+      </x:c>
+      <x:c r="J17" t="str">
+        <x:v>24 nm northwest of Port Rashid / Mina Rashid</x:v>
+      </x:c>
+      <x:c r="K17" t="str">
+        <x:v>Unidentified tanker listing near Dubai</x:v>
+      </x:c>
+      <x:c r="L17" t="str">
+        <x:v>UKMTO reported an anchored vessel listing, possibly after water ingress from an unknown projectile; vessel identity not confirmed.</x:v>
+      </x:c>
+      <x:c r="M17" t="str">
+        <x:v>Potential flooding / anchorage disruption</x:v>
+      </x:c>
+      <x:c r="N17" t="str">
+        <x:v>Raises anchorage, bunkering and port-approach risk around Dubai</x:v>
+      </x:c>
+      <x:c r="O17" t="str">
+        <x:v>Medium-High</x:v>
+      </x:c>
+      <x:c r="P17" t="str">
+        <x:v>SRC132_003</x:v>
+      </x:c>
+      <x:c r="Q17" t="str">
+        <x:v>https://www.reuters.com/world/europe/several-merchant-vessels-hit-by-disabling-fire-gulf-gulf-oman-2026-09-09/</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18">
+      <x:c r="A18" t="str">
+        <x:v>EVT132_004</x:v>
+      </x:c>
+      <x:c r="B18" t="str">
+        <x:v>2026-09-09</x:v>
+      </x:c>
+      <x:c r="C18"/>
+      <x:c r="D18" t="str">
+        <x:v>Conflict / Security</x:v>
+      </x:c>
+      <x:c r="E18" t="str">
+        <x:v>Regional multi-vessel attack wave</x:v>
+      </x:c>
+      <x:c r="F18" t="str">
+        <x:v>Severe</x:v>
+      </x:c>
+      <x:c r="G18" t="str">
+        <x:v>Active / developing</x:v>
+      </x:c>
+      <x:c r="H18" t="str">
+        <x:v>Maritime / Energy / Trade</x:v>
+      </x:c>
+      <x:c r="I18" t="str">
+        <x:v>Regional</x:v>
+      </x:c>
+      <x:c r="J18" t="str">
+        <x:v>Persian Gulf / Strait of Hormuz / Gulf of Oman</x:v>
+      </x:c>
+      <x:c r="K18" t="str">
+        <x:v>Iran claims attacks on 10 ships as merchant-vessel strikes widen</x:v>
+      </x:c>
+      <x:c r="L18" t="str">
+        <x:v>Iran claimed attacks on 10 ships near Hormuz while UKMTO reported several merchant vessels subject to disabling fire during ongoing military activity.</x:v>
+      </x:c>
+      <x:c r="M18" t="str">
+        <x:v>Multiple commercial-vessel casualties / disruptions; exact attribution incomplete</x:v>
+      </x:c>
+      <x:c r="N18" t="str">
+        <x:v>Systemic war-risk, route avoidance, bunkering disruption and lower Hormuz throughput</x:v>
+      </x:c>
+      <x:c r="O18" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="P18" t="str">
+        <x:v>SRC132_003</x:v>
+      </x:c>
+      <x:c r="Q18" t="str">
+        <x:v>https://www.reuters.com/world/europe/several-merchant-vessels-hit-by-disabling-fire-gulf-gulf-oman-2026-09-09/</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19">
+      <x:c r="A19" t="str">
+        <x:v>EVT132_005</x:v>
+      </x:c>
+      <x:c r="B19" t="str">
+        <x:v>2026-09-05</x:v>
+      </x:c>
+      <x:c r="C19"/>
+      <x:c r="D19" t="str">
+        <x:v>Conflict / Security</x:v>
+      </x:c>
+      <x:c r="E19" t="str">
+        <x:v>UKMTO regional advisory</x:v>
+      </x:c>
+      <x:c r="F19" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="G19" t="str">
+        <x:v>Advisory / ongoing context</x:v>
+      </x:c>
+      <x:c r="H19" t="str">
+        <x:v>Maritime</x:v>
+      </x:c>
+      <x:c r="I19" t="str">
+        <x:v>Regional</x:v>
+      </x:c>
+      <x:c r="J19" t="str">
+        <x:v>Northern Arabian Gulf / Gulf of Oman</x:v>
+      </x:c>
+      <x:c r="K19" t="str">
+        <x:v>UKMTO Advisory 127-26: several merchant vessels subjected to disabling fire</x:v>
+      </x:c>
+      <x:c r="L19" t="str">
+        <x:v>UKMTO reported several merchant vessels subjected to disabling fire as part of ongoing military activity; casualties and environmental impact were unconfirmed at publication.</x:v>
+      </x:c>
+      <x:c r="M19" t="str">
+        <x:v>Regional merchant-shipping threat notification</x:v>
+      </x:c>
+      <x:c r="N19" t="str">
+        <x:v>Provides precursor context for the 8–9 September escalation</x:v>
+      </x:c>
+      <x:c r="O19" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="P19" t="str">
+        <x:v>SRC132_012</x:v>
+      </x:c>
+      <x:c r="Q19" t="str">
+        <x:v>https://www.ukmto.org/</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -1595,6 +1850,136 @@
         <x:v>Investment framework</x:v>
       </x:c>
     </x:row>
+    <x:row r="15">
+      <x:c r="A15" t="str">
+        <x:v>LOC132_001</x:v>
+      </x:c>
+      <x:c r="B15" t="str">
+        <x:v>EVT132_001</x:v>
+      </x:c>
+      <x:c r="C15" t="str">
+        <x:v>Gulf of Oman strike area</x:v>
+      </x:c>
+      <x:c r="D15" t="str">
+        <x:v>International waters / Iran-adjacent</x:v>
+      </x:c>
+      <x:c r="E15" t="n">
+        <x:v>25.5</x:v>
+      </x:c>
+      <x:c r="F15" t="n">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="G15" t="str">
+        <x:v>Regional approximate</x:v>
+      </x:c>
+      <x:c r="H15" t="str">
+        <x:v>Four vessels in Gulf of Oman; DERYA separately near Kharg Island</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16">
+      <x:c r="A16" t="str">
+        <x:v>LOC132_002</x:v>
+      </x:c>
+      <x:c r="B16" t="str">
+        <x:v>EVT132_002</x:v>
+      </x:c>
+      <x:c r="C16" t="str">
+        <x:v>Iraqi Gulf waters southeast of Al-Faw</x:v>
+      </x:c>
+      <x:c r="D16" t="str">
+        <x:v>Iraq</x:v>
+      </x:c>
+      <x:c r="E16" t="n">
+        <x:v>29.59</x:v>
+      </x:c>
+      <x:c r="F16" t="n">
+        <x:v>48.76</x:v>
+      </x:c>
+      <x:c r="G16" t="str">
+        <x:v>Approximate / AIS-region</x:v>
+      </x:c>
+      <x:c r="H16" t="str">
+        <x:v>Representative point near reported incident area; not a precise strike coordinate</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17">
+      <x:c r="A17" t="str">
+        <x:v>LOC132_003</x:v>
+      </x:c>
+      <x:c r="B17" t="str">
+        <x:v>EVT132_003</x:v>
+      </x:c>
+      <x:c r="C17" t="str">
+        <x:v>Northwest of Port Rashid / Mina Rashid</x:v>
+      </x:c>
+      <x:c r="D17" t="str">
+        <x:v>United Arab Emirates</x:v>
+      </x:c>
+      <x:c r="E17" t="n">
+        <x:v>25.5</x:v>
+      </x:c>
+      <x:c r="F17" t="n">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="G17" t="str">
+        <x:v>Approximate / relative-distance</x:v>
+      </x:c>
+      <x:c r="H17" t="str">
+        <x:v>24 nm northwest of Port Rashid; exact coordinates not published in Reuters report</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18">
+      <x:c r="A18" t="str">
+        <x:v>LOC132_004</x:v>
+      </x:c>
+      <x:c r="B18" t="str">
+        <x:v>EVT132_004</x:v>
+      </x:c>
+      <x:c r="C18" t="str">
+        <x:v>Strait of Hormuz / Gulf of Oman</x:v>
+      </x:c>
+      <x:c r="D18" t="str">
+        <x:v>Regional</x:v>
+      </x:c>
+      <x:c r="E18" t="n">
+        <x:v>26.3</x:v>
+      </x:c>
+      <x:c r="F18" t="n">
+        <x:v>56.3</x:v>
+      </x:c>
+      <x:c r="G18" t="str">
+        <x:v>Regional chokepoint</x:v>
+      </x:c>
+      <x:c r="H18" t="str">
+        <x:v>System-level marker</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19">
+      <x:c r="A19" t="str">
+        <x:v>LOC132_005</x:v>
+      </x:c>
+      <x:c r="B19" t="str">
+        <x:v>EVT132_005</x:v>
+      </x:c>
+      <x:c r="C19" t="str">
+        <x:v>Northern Arabian Gulf / Gulf of Oman</x:v>
+      </x:c>
+      <x:c r="D19" t="str">
+        <x:v>Regional</x:v>
+      </x:c>
+      <x:c r="E19" t="n">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="F19" t="n">
+        <x:v>54.5</x:v>
+      </x:c>
+      <x:c r="G19" t="str">
+        <x:v>Regional advisory area</x:v>
+      </x:c>
+      <x:c r="H19" t="str">
+        <x:v>Broad UKMTO advisory geography</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -2134,6 +2519,266 @@
         <x:v>Framework / exploratory</x:v>
       </x:c>
     </x:row>
+    <x:row r="21">
+      <x:c r="A21" t="str">
+        <x:v>EAL132_001</x:v>
+      </x:c>
+      <x:c r="B21" t="str">
+        <x:v>EVT132_001</x:v>
+      </x:c>
+      <x:c r="C21" t="str">
+        <x:v>VES_GULF_RIESCO</x:v>
+      </x:c>
+      <x:c r="D21" t="str">
+        <x:v>RIESCO</x:v>
+      </x:c>
+      <x:c r="E21" t="str">
+        <x:v>Vessel</x:v>
+      </x:c>
+      <x:c r="F21" t="str">
+        <x:v>DIRECTLY_AFFECTED</x:v>
+      </x:c>
+      <x:c r="G21" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="H21" t="str">
+        <x:v>CENTCOM strike / sunk reported</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22">
+      <x:c r="A22" t="str">
+        <x:v>EAL132_002</x:v>
+      </x:c>
+      <x:c r="B22" t="str">
+        <x:v>EVT132_001</x:v>
+      </x:c>
+      <x:c r="C22" t="str">
+        <x:v>VES_GULF_HORIZON1</x:v>
+      </x:c>
+      <x:c r="D22" t="str">
+        <x:v>HORIZON 1</x:v>
+      </x:c>
+      <x:c r="E22" t="str">
+        <x:v>Vessel</x:v>
+      </x:c>
+      <x:c r="F22" t="str">
+        <x:v>DIRECTLY_AFFECTED</x:v>
+      </x:c>
+      <x:c r="G22" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="H22" t="str">
+        <x:v>CENTCOM strike / rendered inoperable</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23">
+      <x:c r="A23" t="str">
+        <x:v>EAL132_003</x:v>
+      </x:c>
+      <x:c r="B23" t="str">
+        <x:v>EVT132_001</x:v>
+      </x:c>
+      <x:c r="C23" t="str">
+        <x:v>VES_GULF_KAVIZ</x:v>
+      </x:c>
+      <x:c r="D23" t="str">
+        <x:v>KAVIZ</x:v>
+      </x:c>
+      <x:c r="E23" t="str">
+        <x:v>Vessel</x:v>
+      </x:c>
+      <x:c r="F23" t="str">
+        <x:v>DIRECTLY_AFFECTED</x:v>
+      </x:c>
+      <x:c r="G23" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="H23" t="str">
+        <x:v>CENTCOM strike / rendered inoperable</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24">
+      <x:c r="A24" t="str">
+        <x:v>EAL132_004</x:v>
+      </x:c>
+      <x:c r="B24" t="str">
+        <x:v>EVT132_001</x:v>
+      </x:c>
+      <x:c r="C24" t="str">
+        <x:v>VES_GULF_CHARMINAR</x:v>
+      </x:c>
+      <x:c r="D24" t="str">
+        <x:v>CHARMINAR</x:v>
+      </x:c>
+      <x:c r="E24" t="str">
+        <x:v>Vessel</x:v>
+      </x:c>
+      <x:c r="F24" t="str">
+        <x:v>DIRECTLY_AFFECTED</x:v>
+      </x:c>
+      <x:c r="G24" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="H24" t="str">
+        <x:v>CENTCOM strike / rendered inoperable</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25">
+      <x:c r="A25" t="str">
+        <x:v>EAL132_005</x:v>
+      </x:c>
+      <x:c r="B25" t="str">
+        <x:v>EVT132_001</x:v>
+      </x:c>
+      <x:c r="C25" t="str">
+        <x:v>VES_GULF_DERYA</x:v>
+      </x:c>
+      <x:c r="D25" t="str">
+        <x:v>DERYA</x:v>
+      </x:c>
+      <x:c r="E25" t="str">
+        <x:v>Vessel</x:v>
+      </x:c>
+      <x:c r="F25" t="str">
+        <x:v>DIRECTLY_AFFECTED</x:v>
+      </x:c>
+      <x:c r="G25" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="H25" t="str">
+        <x:v>CENTCOM strike near Kharg Island</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26">
+      <x:c r="A26" t="str">
+        <x:v>EAL132_006</x:v>
+      </x:c>
+      <x:c r="B26" t="str">
+        <x:v>EVT132_002</x:v>
+      </x:c>
+      <x:c r="C26" t="str">
+        <x:v>VES_GULF_NEW_ANDROS</x:v>
+      </x:c>
+      <x:c r="D26" t="str">
+        <x:v>NEW ANDROS</x:v>
+      </x:c>
+      <x:c r="E26" t="str">
+        <x:v>Vessel</x:v>
+      </x:c>
+      <x:c r="F26" t="str">
+        <x:v>DIRECTLY_AFFECTED</x:v>
+      </x:c>
+      <x:c r="G26" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="H26" t="str">
+        <x:v>Drone strike / minor hull damage</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27">
+      <x:c r="A27" t="str">
+        <x:v>EAL132_007</x:v>
+      </x:c>
+      <x:c r="B27" t="str">
+        <x:v>EVT132_003</x:v>
+      </x:c>
+      <x:c r="C27" t="str">
+        <x:v>PORTG0045</x:v>
+      </x:c>
+      <x:c r="D27" t="str">
+        <x:v>Mina Rashid</x:v>
+      </x:c>
+      <x:c r="E27" t="str">
+        <x:v>Port</x:v>
+      </x:c>
+      <x:c r="F27" t="str">
+        <x:v>NEARBY_ANCHORAGE_EXPOSURE</x:v>
+      </x:c>
+      <x:c r="G27" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="H27" t="str">
+        <x:v>Incident 24 nm northwest of port</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28">
+      <x:c r="A28" t="str">
+        <x:v>EAL132_008</x:v>
+      </x:c>
+      <x:c r="B28" t="str">
+        <x:v>EVT132_004</x:v>
+      </x:c>
+      <x:c r="C28" t="str">
+        <x:v>PORTG0046</x:v>
+      </x:c>
+      <x:c r="D28" t="str">
+        <x:v>Fujairah</x:v>
+      </x:c>
+      <x:c r="E28" t="str">
+        <x:v>Port</x:v>
+      </x:c>
+      <x:c r="F28" t="str">
+        <x:v>REGIONAL_SECURITY_EXPOSURE</x:v>
+      </x:c>
+      <x:c r="G28" t="str">
+        <x:v>Medium</x:v>
+      </x:c>
+      <x:c r="H28" t="str">
+        <x:v>Bunkering / Gulf of Oman gateway exposure</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29">
+      <x:c r="A29" t="str">
+        <x:v>EAL132_009</x:v>
+      </x:c>
+      <x:c r="B29" t="str">
+        <x:v>EVT132_004</x:v>
+      </x:c>
+      <x:c r="C29" t="str">
+        <x:v>PORTG0071</x:v>
+      </x:c>
+      <x:c r="D29" t="str">
+        <x:v>Fujairah Port / Fujairah Terminals</x:v>
+      </x:c>
+      <x:c r="E29" t="str">
+        <x:v>Port</x:v>
+      </x:c>
+      <x:c r="F29" t="str">
+        <x:v>REGIONAL_SECURITY_EXPOSURE</x:v>
+      </x:c>
+      <x:c r="G29" t="str">
+        <x:v>Medium</x:v>
+      </x:c>
+      <x:c r="H29" t="str">
+        <x:v>UAE Gulf of Oman gateway exposure</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30">
+      <x:c r="A30" t="str">
+        <x:v>EAL132_010</x:v>
+      </x:c>
+      <x:c r="B30" t="str">
+        <x:v>EVT132_004</x:v>
+      </x:c>
+      <x:c r="C30" t="str">
+        <x:v>PORTG0250</x:v>
+      </x:c>
+      <x:c r="D30" t="str">
+        <x:v>Port of Umm Qasr / Basra</x:v>
+      </x:c>
+      <x:c r="E30" t="str">
+        <x:v>Port</x:v>
+      </x:c>
+      <x:c r="F30" t="str">
+        <x:v>NORTHERN_GULF_EXPOSURE</x:v>
+      </x:c>
+      <x:c r="G30" t="str">
+        <x:v>Medium</x:v>
+      </x:c>
+      <x:c r="H30" t="str">
+        <x:v>Iraqi Gulf gateway exposure</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -2451,6 +3096,106 @@
         <x:v>High</x:v>
       </x:c>
     </x:row>
+    <x:row r="16">
+      <x:c r="A16" t="str">
+        <x:v>ECL132_001</x:v>
+      </x:c>
+      <x:c r="B16" t="str">
+        <x:v>EVT132_002</x:v>
+      </x:c>
+      <x:c r="C16" t="str">
+        <x:v>COMP_IOTC</x:v>
+      </x:c>
+      <x:c r="D16" t="str">
+        <x:v>Iraqi Oil Tankers Company</x:v>
+      </x:c>
+      <x:c r="E16" t="str">
+        <x:v>Charterer / floating-storage exposure</x:v>
+      </x:c>
+      <x:c r="F16" t="str">
+        <x:v>High</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17">
+      <x:c r="A17" t="str">
+        <x:v>ECL132_002</x:v>
+      </x:c>
+      <x:c r="B17" t="str">
+        <x:v>EVT132_002</x:v>
+      </x:c>
+      <x:c r="C17" t="str">
+        <x:v>COMP_INVINCIBLE_SHIPPING</x:v>
+      </x:c>
+      <x:c r="D17" t="str">
+        <x:v>Invincible Shipping Services Inc.</x:v>
+      </x:c>
+      <x:c r="E17" t="str">
+        <x:v>Registered owner exposure</x:v>
+      </x:c>
+      <x:c r="F17" t="str">
+        <x:v>High</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18">
+      <x:c r="A18" t="str">
+        <x:v>ECL132_003</x:v>
+      </x:c>
+      <x:c r="B18" t="str">
+        <x:v>EVT132_002</x:v>
+      </x:c>
+      <x:c r="C18" t="str">
+        <x:v>COMP_NEW_SHIPPING</x:v>
+      </x:c>
+      <x:c r="D18" t="str">
+        <x:v>New Shipping Limited</x:v>
+      </x:c>
+      <x:c r="E18" t="str">
+        <x:v>Management-company exposure</x:v>
+      </x:c>
+      <x:c r="F18" t="str">
+        <x:v>High</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19">
+      <x:c r="A19" t="str">
+        <x:v>ECL132_004</x:v>
+      </x:c>
+      <x:c r="B19" t="str">
+        <x:v>EVT132_001</x:v>
+      </x:c>
+      <x:c r="C19" t="str">
+        <x:v>COMP_NITC</x:v>
+      </x:c>
+      <x:c r="D19" t="str">
+        <x:v>National Iranian Tanker Company</x:v>
+      </x:c>
+      <x:c r="E19" t="str">
+        <x:v>DERYA owner / sanctions-linked exposure</x:v>
+      </x:c>
+      <x:c r="F19" t="str">
+        <x:v>High</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20">
+      <x:c r="A20" t="str">
+        <x:v>ECL132_005</x:v>
+      </x:c>
+      <x:c r="B20" t="str">
+        <x:v>EVT132_001</x:v>
+      </x:c>
+      <x:c r="C20" t="str">
+        <x:v>COMP_ALGAE_SHIP</x:v>
+      </x:c>
+      <x:c r="D20" t="str">
+        <x:v>Algae Ship Charter - FZCO</x:v>
+      </x:c>
+      <x:c r="E20" t="str">
+        <x:v>CHARMINAR sanctions-network exposure</x:v>
+      </x:c>
+      <x:c r="F20" t="str">
+        <x:v>High</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -2685,6 +3430,106 @@
         <x:v>INVESTMENT_EVENT</x:v>
       </x:c>
       <x:c r="F11" s="10" t="str">
+        <x:v>High</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" t="str">
+        <x:v>ESL132_001</x:v>
+      </x:c>
+      <x:c r="B12" t="str">
+        <x:v>EVT132_001</x:v>
+      </x:c>
+      <x:c r="C12" t="str">
+        <x:v>SYS_HORMUZ_SECURITY</x:v>
+      </x:c>
+      <x:c r="D12" t="str">
+        <x:v>Persian Gulf / Hormuz / Gulf of Oman Security System</x:v>
+      </x:c>
+      <x:c r="E12" t="str">
+        <x:v>DIRECT_SYSTEM_IMPACT</x:v>
+      </x:c>
+      <x:c r="F12" t="str">
+        <x:v>High</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13" t="str">
+        <x:v>ESL132_002</x:v>
+      </x:c>
+      <x:c r="B13" t="str">
+        <x:v>EVT132_002</x:v>
+      </x:c>
+      <x:c r="C13" t="str">
+        <x:v>SYS_HORMUZ_SECURITY</x:v>
+      </x:c>
+      <x:c r="D13" t="str">
+        <x:v>Persian Gulf / Hormuz / Gulf of Oman Security System</x:v>
+      </x:c>
+      <x:c r="E13" t="str">
+        <x:v>DIRECT_SYSTEM_IMPACT</x:v>
+      </x:c>
+      <x:c r="F13" t="str">
+        <x:v>High</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14" t="str">
+        <x:v>ESL132_003</x:v>
+      </x:c>
+      <x:c r="B14" t="str">
+        <x:v>EVT132_003</x:v>
+      </x:c>
+      <x:c r="C14" t="str">
+        <x:v>SYS_HORMUZ_SECURITY</x:v>
+      </x:c>
+      <x:c r="D14" t="str">
+        <x:v>Persian Gulf / Hormuz / Gulf of Oman Security System</x:v>
+      </x:c>
+      <x:c r="E14" t="str">
+        <x:v>DIRECT_SYSTEM_IMPACT</x:v>
+      </x:c>
+      <x:c r="F14" t="str">
+        <x:v>High</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15">
+      <x:c r="A15" t="str">
+        <x:v>ESL132_004</x:v>
+      </x:c>
+      <x:c r="B15" t="str">
+        <x:v>EVT132_004</x:v>
+      </x:c>
+      <x:c r="C15" t="str">
+        <x:v>SYS_HORMUZ_SECURITY</x:v>
+      </x:c>
+      <x:c r="D15" t="str">
+        <x:v>Persian Gulf / Hormuz / Gulf of Oman Security System</x:v>
+      </x:c>
+      <x:c r="E15" t="str">
+        <x:v>REGIONAL_ESCALATION</x:v>
+      </x:c>
+      <x:c r="F15" t="str">
+        <x:v>High</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16">
+      <x:c r="A16" t="str">
+        <x:v>ESL132_005</x:v>
+      </x:c>
+      <x:c r="B16" t="str">
+        <x:v>EVT132_005</x:v>
+      </x:c>
+      <x:c r="C16" t="str">
+        <x:v>SYS_HORMUZ_SECURITY</x:v>
+      </x:c>
+      <x:c r="D16" t="str">
+        <x:v>Persian Gulf / Hormuz / Gulf of Oman Security System</x:v>
+      </x:c>
+      <x:c r="E16" t="str">
+        <x:v>SECURITY_ADVISORY</x:v>
+      </x:c>
+      <x:c r="F16" t="str">
         <x:v>High</x:v>
       </x:c>
     </x:row>
@@ -2998,6 +3843,151 @@
         <x:v>Infrastructure-commercial chain</x:v>
       </x:c>
     </x:row>
+    <x:row r="11">
+      <x:c r="A11" t="str">
+        <x:v>CHAIN132_001</x:v>
+      </x:c>
+      <x:c r="B11" t="str">
+        <x:v>EVT132_001</x:v>
+      </x:c>
+      <x:c r="C11" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D11" t="str">
+        <x:v>State strike on tanker network</x:v>
+      </x:c>
+      <x:c r="E11" t="str">
+        <x:v>Five tanker hulls disabled / one sunk</x:v>
+      </x:c>
+      <x:c r="F11" t="str">
+        <x:v>Iran-linked oil logistics capacity reduced</x:v>
+      </x:c>
+      <x:c r="G11" t="str">
+        <x:v>Operators reroute / increase precautions</x:v>
+      </x:c>
+      <x:c r="H11" t="str">
+        <x:v>War-risk and compliance costs rise across Gulf tanker trade</x:v>
+      </x:c>
+      <x:c r="I11" t="str">
+        <x:v>Security → operational → commercial</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" t="str">
+        <x:v>CHAIN132_002</x:v>
+      </x:c>
+      <x:c r="B12" t="str">
+        <x:v>EVT132_002</x:v>
+      </x:c>
+      <x:c r="C12" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D12" t="str">
+        <x:v>Drone strike on floating-storage VLCC</x:v>
+      </x:c>
+      <x:c r="E12" t="str">
+        <x:v>Hull/fire damage</x:v>
+      </x:c>
+      <x:c r="F12" t="str">
+        <x:v>Storage operation interrupted</x:v>
+      </x:c>
+      <x:c r="G12" t="str">
+        <x:v>Iraqi export / storage resilience questioned</x:v>
+      </x:c>
+      <x:c r="H12" t="str">
+        <x:v>Northern Gulf commercial tanker risk rises</x:v>
+      </x:c>
+      <x:c r="I12" t="str">
+        <x:v>Security → operational → trade</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13" t="str">
+        <x:v>CHAIN132_003</x:v>
+      </x:c>
+      <x:c r="B13" t="str">
+        <x:v>EVT132_003</x:v>
+      </x:c>
+      <x:c r="C13" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D13" t="str">
+        <x:v>Projectile / water ingress near Dubai anchorage</x:v>
+      </x:c>
+      <x:c r="E13" t="str">
+        <x:v>Vessel listing</x:v>
+      </x:c>
+      <x:c r="F13" t="str">
+        <x:v>Anchorage / casualty response risk increases</x:v>
+      </x:c>
+      <x:c r="G13" t="str">
+        <x:v>Port-approach and bunkering confidence falls</x:v>
+      </x:c>
+      <x:c r="H13" t="str">
+        <x:v>UAE anchorage risk pricing rises</x:v>
+      </x:c>
+      <x:c r="I13" t="str">
+        <x:v>Security → port operations → commercial</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14" t="str">
+        <x:v>CHAIN132_004</x:v>
+      </x:c>
+      <x:c r="B14" t="str">
+        <x:v>EVT132_004</x:v>
+      </x:c>
+      <x:c r="C14" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D14" t="str">
+        <x:v>Multi-vessel attack wave</x:v>
+      </x:c>
+      <x:c r="E14" t="str">
+        <x:v>Merchant vessels disabled / damaged</x:v>
+      </x:c>
+      <x:c r="F14" t="str">
+        <x:v>Transit and bunkering disruption</x:v>
+      </x:c>
+      <x:c r="G14" t="str">
+        <x:v>Hormuz throughput / schedules decline</x:v>
+      </x:c>
+      <x:c r="H14" t="str">
+        <x:v>Energy price and war-risk pressure increase</x:v>
+      </x:c>
+      <x:c r="I14" t="str">
+        <x:v>Security → system → energy markets</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15">
+      <x:c r="A15" t="str">
+        <x:v>CHAIN132_005</x:v>
+      </x:c>
+      <x:c r="B15" t="str">
+        <x:v>EVT132_005</x:v>
+      </x:c>
+      <x:c r="C15" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D15" t="str">
+        <x:v>UKMTO regional advisory</x:v>
+      </x:c>
+      <x:c r="E15" t="str">
+        <x:v>Industry threat awareness rises</x:v>
+      </x:c>
+      <x:c r="F15" t="str">
+        <x:v>Masters reroute / heighten readiness</x:v>
+      </x:c>
+      <x:c r="G15" t="str">
+        <x:v>Voyage planning and insurance assumptions change</x:v>
+      </x:c>
+      <x:c r="H15" t="str">
+        <x:v>Precursor signal for wider attack wave</x:v>
+      </x:c>
+      <x:c r="I15" t="str">
+        <x:v>Advisory → operational posture</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -3195,6 +4185,106 @@
         <x:v>Potential investment; not current ownership/control</x:v>
       </x:c>
     </x:row>
+    <x:row r="10">
+      <x:c r="A10" t="str">
+        <x:v>ESH132_001</x:v>
+      </x:c>
+      <x:c r="B10" t="str">
+        <x:v>EVT132_001</x:v>
+      </x:c>
+      <x:c r="C10" t="str">
+        <x:v>2026-09-08</x:v>
+      </x:c>
+      <x:c r="D10" t="str">
+        <x:v>Occurred / vessels disabled</x:v>
+      </x:c>
+      <x:c r="E10" t="str">
+        <x:v>Severe</x:v>
+      </x:c>
+      <x:c r="F10" t="str">
+        <x:v>Five tankers named by CENTCOM; RIESCO reported sunk</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" t="str">
+        <x:v>ESH132_002</x:v>
+      </x:c>
+      <x:c r="B11" t="str">
+        <x:v>EVT132_002</x:v>
+      </x:c>
+      <x:c r="C11" t="str">
+        <x:v>2026-09-09</x:v>
+      </x:c>
+      <x:c r="D11" t="str">
+        <x:v>Occurred / damaged</x:v>
+      </x:c>
+      <x:c r="E11" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="F11" t="str">
+        <x:v>Crew safe; no reported leakage</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" t="str">
+        <x:v>ESH132_003</x:v>
+      </x:c>
+      <x:c r="B12" t="str">
+        <x:v>EVT132_003</x:v>
+      </x:c>
+      <x:c r="C12" t="str">
+        <x:v>2026-09-09</x:v>
+      </x:c>
+      <x:c r="D12" t="str">
+        <x:v>Active investigation</x:v>
+      </x:c>
+      <x:c r="E12" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="F12" t="str">
+        <x:v>Vessel identity and final damage remain unconfirmed</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13" t="str">
+        <x:v>ESH132_004</x:v>
+      </x:c>
+      <x:c r="B13" t="str">
+        <x:v>EVT132_004</x:v>
+      </x:c>
+      <x:c r="C13" t="str">
+        <x:v>2026-09-09</x:v>
+      </x:c>
+      <x:c r="D13" t="str">
+        <x:v>Active / developing</x:v>
+      </x:c>
+      <x:c r="E13" t="str">
+        <x:v>Severe</x:v>
+      </x:c>
+      <x:c r="F13" t="str">
+        <x:v>Multiple attacks / claims; vessel-level attribution incomplete</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14" t="str">
+        <x:v>ESH132_005</x:v>
+      </x:c>
+      <x:c r="B14" t="str">
+        <x:v>EVT132_005</x:v>
+      </x:c>
+      <x:c r="C14" t="str">
+        <x:v>2026-09-05</x:v>
+      </x:c>
+      <x:c r="D14" t="str">
+        <x:v>Advisory / ongoing context</x:v>
+      </x:c>
+      <x:c r="E14" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="F14" t="str">
+        <x:v>Regional disabling-fire reports</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -3575,6 +4665,62 @@
         <x:v>https://www.adportsgroup.com/en/news-and-media/2026/04/14/ad-ports-group-signs-agreement-to-explore-investment-opportunities-in-the-port-of-constanta</x:v>
       </x:c>
     </x:row>
+    <x:row r="15">
+      <x:c r="A15" t="str">
+        <x:v>SRC132_001</x:v>
+      </x:c>
+      <x:c r="B15" t="str">
+        <x:v>U.S. Central Command</x:v>
+      </x:c>
+      <x:c r="C15" t="str">
+        <x:v>Five Iran-linked tanker strikes 8 Sep 2026</x:v>
+      </x:c>
+      <x:c r="D15" t="str">
+        <x:v>https://www.centcom.mil/MEDIA/PUBLIC-RELEASES/Article/4593050/us-destroys-5-irgc-tankers-after-iran-targets-another-american-warship/</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16">
+      <x:c r="A16" t="str">
+        <x:v>SRC132_002</x:v>
+      </x:c>
+      <x:c r="B16" t="str">
+        <x:v>Reuters</x:v>
+      </x:c>
+      <x:c r="C16" t="str">
+        <x:v>Five-tanker strike / escalation context</x:v>
+      </x:c>
+      <x:c r="D16" t="str">
+        <x:v>https://www.reuters.com/business/energy/us-military-says-it-destroyed-five-iranian-oil-carriers-after-attempted-missile-2026-09-08/</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17">
+      <x:c r="A17" t="str">
+        <x:v>SRC132_003</x:v>
+      </x:c>
+      <x:c r="B17" t="str">
+        <x:v>Reuters</x:v>
+      </x:c>
+      <x:c r="C17" t="str">
+        <x:v>NEW ANDROS; Port Rashid listing vessel; wider attacks</x:v>
+      </x:c>
+      <x:c r="D17" t="str">
+        <x:v>https://www.reuters.com/world/europe/several-merchant-vessels-hit-by-disabling-fire-gulf-gulf-oman-2026-09-09/</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18">
+      <x:c r="A18" t="str">
+        <x:v>SRC132_012</x:v>
+      </x:c>
+      <x:c r="B18" t="str">
+        <x:v>UKMTO</x:v>
+      </x:c>
+      <x:c r="C18" t="str">
+        <x:v>Advisory 127-26 / recent incidents</x:v>
+      </x:c>
+      <x:c r="D18" t="str">
+        <x:v>https://www.ukmto.org/</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>

--- a/data/13_events_hazards.xlsx
+++ b/data/13_events_hazards.xlsx
@@ -2,16 +2,16 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Events" sheetId="1" r:id="R873502a9dd6d4641"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Event Locations" sheetId="2" r:id="R1d5f08521a8641a1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Event Asset Links" sheetId="3" r:id="R2bdfd348c64d45e3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Event Company Links" sheetId="4" r:id="R305f351b23024fad"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Event System Links" sheetId="5" r:id="R22638258982c489e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Impact Chains" sheetId="6" r:id="R1815e0523c854060"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Event Status History" sheetId="7" r:id="R35f78d471ca841a3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Event Taxonomy" sheetId="8" r:id="Rbba3d5b282df45c4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="9" r:id="R6838ce16c6c045fa"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overview" sheetId="10" r:id="R1854b9260d82449d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Events" sheetId="1" r:id="Rf76b85141b034790"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Event Locations" sheetId="2" r:id="R8d3ac810aa664ded"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Event Asset Links" sheetId="3" r:id="R9542d6f1f88b429a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Event Company Links" sheetId="4" r:id="R714c7fc8036c4271"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Event System Links" sheetId="5" r:id="Rdd02624feff94f21"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Impact Chains" sheetId="6" r:id="R344a0c11cbd141b8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Event Status History" sheetId="7" r:id="R70e0b96128a741f3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Event Taxonomy" sheetId="8" r:id="R32adfb1cd421471f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="9" r:id="R383b51ee45f848c4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overview" sheetId="10" r:id="Re945f4750fd94c31"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1297,6 +1297,159 @@
         <x:v>https://www.ukmto.org/</x:v>
       </x:c>
     </x:row>
+    <x:row r="20">
+      <x:c r="A20" t="str">
+        <x:v>EVT133_001</x:v>
+      </x:c>
+      <x:c r="B20" t="str">
+        <x:v>2026-09-09</x:v>
+      </x:c>
+      <x:c r="C20" t="str"/>
+      <x:c r="D20" t="str">
+        <x:v>Conflict / Security</x:v>
+      </x:c>
+      <x:c r="E20" t="str">
+        <x:v>Vessel incident / suspected projectile attack</x:v>
+      </x:c>
+      <x:c r="F20" t="str">
+        <x:v>Critical</x:v>
+      </x:c>
+      <x:c r="G20" t="str">
+        <x:v>Casualty response / investigation</x:v>
+      </x:c>
+      <x:c r="H20" t="str">
+        <x:v>Maritime</x:v>
+      </x:c>
+      <x:c r="I20" t="str">
+        <x:v>United Arab Emirates</x:v>
+      </x:c>
+      <x:c r="J20" t="str">
+        <x:v>Anchorage off Dubai</x:v>
+      </x:c>
+      <x:c r="K20" t="str">
+        <x:v>HERCULES STAR incident off Dubai</x:v>
+      </x:c>
+      <x:c r="L20" t="str">
+        <x:v>Peninsula confirmed one crewmember died and one was missing after an incident involving HERCULES STAR at anchorage off Dubai. UKMTO separately reported a nearby vessel taking on water after an unknown projectile; identity equivalence remains unconfirmed in the source.</x:v>
+      </x:c>
+      <x:c r="M20" t="str">
+        <x:v>Crew casualty; vessel emergency response; one person missing</x:v>
+      </x:c>
+      <x:c r="N20" t="str">
+        <x:v>Bunker-supply and regional maritime-security exposure; potential anchorage and insurance impacts</x:v>
+      </x:c>
+      <x:c r="O20" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="P20" t="str">
+        <x:v>SRC133_001</x:v>
+      </x:c>
+      <x:c r="Q20" t="str">
+        <x:v>https://shipandbunker.com/news/world/583774-peninsula-confirms-tanker-involved-in-incident-off-dubai</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21">
+      <x:c r="A21" t="str">
+        <x:v>EVT133_002</x:v>
+      </x:c>
+      <x:c r="B21" t="str">
+        <x:v>2026-09-10</x:v>
+      </x:c>
+      <x:c r="C21" t="str"/>
+      <x:c r="D21" t="str">
+        <x:v>Infrastructure / Commercial</x:v>
+      </x:c>
+      <x:c r="E21" t="str">
+        <x:v>Port opening and expansion planning</x:v>
+      </x:c>
+      <x:c r="F21" t="str">
+        <x:v>Moderate</x:v>
+      </x:c>
+      <x:c r="G21" t="str">
+        <x:v>Official opening reported / expansion planning</x:v>
+      </x:c>
+      <x:c r="H21" t="str">
+        <x:v>Port</x:v>
+      </x:c>
+      <x:c r="I21" t="str">
+        <x:v>Canada</x:v>
+      </x:c>
+      <x:c r="J21" t="str">
+        <x:v>Stewart, British Columbia</x:v>
+      </x:c>
+      <x:c r="K21" t="str">
+        <x:v>Nisg̱a'a and Tahltan Nations mark Stewart port opening</x:v>
+      </x:c>
+      <x:c r="L21" t="str">
+        <x:v>CBC reported that the Nisg̱a'a and Tahltan Nations marked the official opening of a Stewart, B.C. port while expansion plans take shape. Ownership, operator, capacity and expansion phasing are not inferred from the headline.</x:v>
+      </x:c>
+      <x:c r="M21" t="str">
+        <x:v>New northern B.C. port capacity / gateway development signal</x:v>
+      </x:c>
+      <x:c r="N21" t="str">
+        <x:v>Potential mining, project cargo and regional export connectivity; detailed cargo scope requires verification</x:v>
+      </x:c>
+      <x:c r="O21" t="str">
+        <x:v>Medium</x:v>
+      </x:c>
+      <x:c r="P21" t="str">
+        <x:v>SRC133_002</x:v>
+      </x:c>
+      <x:c r="Q21" t="str">
+        <x:v>https://www.cbc.ca/news/canada/british-columbia/nisga-a-talhtan-port-opening-9.7338188</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22">
+      <x:c r="A22" t="str">
+        <x:v>EVT133_003</x:v>
+      </x:c>
+      <x:c r="B22" t="str">
+        <x:v>2024-10-29</x:v>
+      </x:c>
+      <x:c r="C22" t="str"/>
+      <x:c r="D22" t="str">
+        <x:v>Commercial / Strategy</x:v>
+      </x:c>
+      <x:c r="E22" t="str">
+        <x:v>Cruise private-destination investment wave</x:v>
+      </x:c>
+      <x:c r="F22" t="str">
+        <x:v>Moderate</x:v>
+      </x:c>
+      <x:c r="G22" t="str">
+        <x:v>Ongoing investment cycle</x:v>
+      </x:c>
+      <x:c r="H22" t="str">
+        <x:v>Maritime / Tourism</x:v>
+      </x:c>
+      <x:c r="I22" t="str">
+        <x:v>Caribbean region</x:v>
+      </x:c>
+      <x:c r="J22" t="str">
+        <x:v>Caribbean and Bahamas</x:v>
+      </x:c>
+      <x:c r="K22" t="str">
+        <x:v>Cruise groups accelerate private-destination investment</x:v>
+      </x:c>
+      <x:c r="L22" t="str">
+        <x:v>Reuters reported 12 private Caribbean destinations in 2024 and major investment plans by Royal Caribbean, Carnival and Norwegian.</x:v>
+      </x:c>
+      <x:c r="M22" t="str">
+        <x:v>More itineraries anchored around operator-controlled destinations</x:v>
+      </x:c>
+      <x:c r="N22" t="str">
+        <x:v>Higher onboard/destination revenue capture and changed call patterns for public Caribbean ports</x:v>
+      </x:c>
+      <x:c r="O22" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="P22" t="str">
+        <x:v>SRC133_003</x:v>
+      </x:c>
+      <x:c r="Q22" t="str">
+        <x:v>https://www.reuters.com/business/autos-transportation/cruise-operators-reap-benefits-their-own-private-islands-2024-10-29/</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -2779,6 +2932,58 @@
         <x:v>Iraqi Gulf gateway exposure</x:v>
       </x:c>
     </x:row>
+    <x:row r="31">
+      <x:c r="A31" t="str">
+        <x:v>EAL133_001</x:v>
+      </x:c>
+      <x:c r="B31" t="str">
+        <x:v>EVT133_001</x:v>
+      </x:c>
+      <x:c r="C31" t="str">
+        <x:v>VES_HERCULES_STAR</x:v>
+      </x:c>
+      <x:c r="D31" t="str">
+        <x:v>HERCULES STAR</x:v>
+      </x:c>
+      <x:c r="E31" t="str">
+        <x:v>Vessel</x:v>
+      </x:c>
+      <x:c r="F31" t="str">
+        <x:v>SUBJECT VESSEL</x:v>
+      </x:c>
+      <x:c r="G31" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="H31" t="str">
+        <x:v>Distinct from March 2026 incident.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32">
+      <x:c r="A32" t="str">
+        <x:v>EAL133_002</x:v>
+      </x:c>
+      <x:c r="B32" t="str">
+        <x:v>EVT133_002</x:v>
+      </x:c>
+      <x:c r="C32" t="str">
+        <x:v>PORT_STEWART_BC</x:v>
+      </x:c>
+      <x:c r="D32" t="str">
+        <x:v>Port of Stewart</x:v>
+      </x:c>
+      <x:c r="E32" t="str">
+        <x:v>Port</x:v>
+      </x:c>
+      <x:c r="F32" t="str">
+        <x:v>OPENING / EXPANSION SUBJECT</x:v>
+      </x:c>
+      <x:c r="G32" t="str">
+        <x:v>Medium</x:v>
+      </x:c>
+      <x:c r="H32" t="str">
+        <x:v>Headline-level evidence.</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -3193,6 +3398,146 @@
         <x:v>CHARMINAR sanctions-network exposure</x:v>
       </x:c>
       <x:c r="F20" t="str">
+        <x:v>High</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21">
+      <x:c r="A21" t="str">
+        <x:v>ECL133_001</x:v>
+      </x:c>
+      <x:c r="B21" t="str">
+        <x:v>EVT133_001</x:v>
+      </x:c>
+      <x:c r="C21" t="str">
+        <x:v>COMP_PENINSULA</x:v>
+      </x:c>
+      <x:c r="D21" t="str">
+        <x:v>Peninsula</x:v>
+      </x:c>
+      <x:c r="E21" t="str">
+        <x:v>CHARTERER / INCIDENT RESPONDER</x:v>
+      </x:c>
+      <x:c r="F21" t="str">
+        <x:v>High</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22">
+      <x:c r="A22" t="str">
+        <x:v>ECL133_002</x:v>
+      </x:c>
+      <x:c r="B22" t="str">
+        <x:v>EVT133_001</x:v>
+      </x:c>
+      <x:c r="C22" t="str">
+        <x:v>COMP_HERCULES_TANKER</x:v>
+      </x:c>
+      <x:c r="D22" t="str">
+        <x:v>Hercules Tanker Management</x:v>
+      </x:c>
+      <x:c r="E22" t="str">
+        <x:v>SISTER COMPANY / VESSEL PROVIDER</x:v>
+      </x:c>
+      <x:c r="F22" t="str">
+        <x:v>High</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23">
+      <x:c r="A23" t="str">
+        <x:v>ECL133_003</x:v>
+      </x:c>
+      <x:c r="B23" t="str">
+        <x:v>EVT133_002</x:v>
+      </x:c>
+      <x:c r="C23" t="str">
+        <x:v>ORG_NISGAA_NATION</x:v>
+      </x:c>
+      <x:c r="D23" t="str">
+        <x:v>Nisg̱a'a Nation</x:v>
+      </x:c>
+      <x:c r="E23" t="str">
+        <x:v>OPENING PARTICIPANT</x:v>
+      </x:c>
+      <x:c r="F23" t="str">
+        <x:v>Medium</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24">
+      <x:c r="A24" t="str">
+        <x:v>ECL133_004</x:v>
+      </x:c>
+      <x:c r="B24" t="str">
+        <x:v>EVT133_002</x:v>
+      </x:c>
+      <x:c r="C24" t="str">
+        <x:v>ORG_TAHLTAN_NATION</x:v>
+      </x:c>
+      <x:c r="D24" t="str">
+        <x:v>Tahltan Nation</x:v>
+      </x:c>
+      <x:c r="E24" t="str">
+        <x:v>OPENING PARTICIPANT</x:v>
+      </x:c>
+      <x:c r="F24" t="str">
+        <x:v>Medium</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25">
+      <x:c r="A25" t="str">
+        <x:v>ECL133_005</x:v>
+      </x:c>
+      <x:c r="B25" t="str">
+        <x:v>EVT133_003</x:v>
+      </x:c>
+      <x:c r="C25" t="str">
+        <x:v>COMP_ROYAL_CARIBBEAN_GROUP</x:v>
+      </x:c>
+      <x:c r="D25" t="str">
+        <x:v>Royal Caribbean Group</x:v>
+      </x:c>
+      <x:c r="E25" t="str">
+        <x:v>PRIVATE-DESTINATION INVESTOR</x:v>
+      </x:c>
+      <x:c r="F25" t="str">
+        <x:v>High</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26">
+      <x:c r="A26" t="str">
+        <x:v>ECL133_006</x:v>
+      </x:c>
+      <x:c r="B26" t="str">
+        <x:v>EVT133_003</x:v>
+      </x:c>
+      <x:c r="C26" t="str">
+        <x:v>COMP_CARNIVAL_CORP</x:v>
+      </x:c>
+      <x:c r="D26" t="str">
+        <x:v>Carnival Corporation &amp; plc</x:v>
+      </x:c>
+      <x:c r="E26" t="str">
+        <x:v>PRIVATE-DESTINATION INVESTOR</x:v>
+      </x:c>
+      <x:c r="F26" t="str">
+        <x:v>High</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27">
+      <x:c r="A27" t="str">
+        <x:v>ECL133_007</x:v>
+      </x:c>
+      <x:c r="B27" t="str">
+        <x:v>EVT133_003</x:v>
+      </x:c>
+      <x:c r="C27" t="str">
+        <x:v>COMP_NCLH</x:v>
+      </x:c>
+      <x:c r="D27" t="str">
+        <x:v>Norwegian Cruise Line Holdings</x:v>
+      </x:c>
+      <x:c r="E27" t="str">
+        <x:v>PRIVATE-DESTINATION INVESTOR</x:v>
+      </x:c>
+      <x:c r="F27" t="str">
         <x:v>High</x:v>
       </x:c>
     </x:row>
@@ -4721,6 +5066,48 @@
         <x:v>https://www.ukmto.org/</x:v>
       </x:c>
     </x:row>
+    <x:row r="19">
+      <x:c r="A19" t="str">
+        <x:v>SRC133_001</x:v>
+      </x:c>
+      <x:c r="B19" t="str">
+        <x:v>Ship &amp; Bunker</x:v>
+      </x:c>
+      <x:c r="C19" t="str">
+        <x:v>Peninsula confirms fatal Hercules Star incident at anchorage off Dubai; one crewmember missing; 7,998 DWT tanker chartered from Hercules Tanker Management.</x:v>
+      </x:c>
+      <x:c r="D19" t="str">
+        <x:v>https://shipandbunker.com/news/world/583774-peninsula-confirms-tanker-involved-in-incident-off-dubai</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20">
+      <x:c r="A20" t="str">
+        <x:v>SRC133_002</x:v>
+      </x:c>
+      <x:c r="B20" t="str">
+        <x:v>CBC News</x:v>
+      </x:c>
+      <x:c r="C20" t="str">
+        <x:v>Headline-level record: Nisg̱a'a and Tahltan Nations mark official opening of a Stewart, B.C. port as expansion plans take shape. Detailed ownership, capacity and terminal facts remain to be verified.</x:v>
+      </x:c>
+      <x:c r="D20" t="str">
+        <x:v>https://www.cbc.ca/news/canada/british-columbia/nisga-a-talhtan-port-opening-9.7338188</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21">
+      <x:c r="A21" t="str">
+        <x:v>SRC133_003</x:v>
+      </x:c>
+      <x:c r="B21" t="str">
+        <x:v>Reuters</x:v>
+      </x:c>
+      <x:c r="C21" t="str">
+        <x:v>Cruise operators expand private destinations; 12 Caribbean private destinations reported in 2024, with substantial Royal Caribbean, Carnival and Norwegian investment.</x:v>
+      </x:c>
+      <x:c r="D21" t="str">
+        <x:v>https://www.reuters.com/business/autos-transportation/cruise-operators-reap-benefits-their-own-private-islands-2024-10-29/</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>

--- a/data/13_events_hazards.xlsx
+++ b/data/13_events_hazards.xlsx
@@ -2,16 +2,16 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Events" sheetId="1" r:id="Rf76b85141b034790"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Event Locations" sheetId="2" r:id="R8d3ac810aa664ded"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Event Asset Links" sheetId="3" r:id="R9542d6f1f88b429a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Event Company Links" sheetId="4" r:id="R714c7fc8036c4271"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Event System Links" sheetId="5" r:id="Rdd02624feff94f21"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Impact Chains" sheetId="6" r:id="R344a0c11cbd141b8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Event Status History" sheetId="7" r:id="R70e0b96128a741f3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Event Taxonomy" sheetId="8" r:id="R32adfb1cd421471f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="9" r:id="R383b51ee45f848c4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overview" sheetId="10" r:id="Re945f4750fd94c31"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Events" sheetId="1" r:id="Rf1a6bb9137e540e2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Event Locations" sheetId="2" r:id="Rb68daac7eb3140bd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Event Asset Links" sheetId="3" r:id="R1acc9233602f4f2a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Event Company Links" sheetId="4" r:id="R7add1043c89e4e53"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Event System Links" sheetId="5" r:id="R96458049367c4e98"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Impact Chains" sheetId="6" r:id="Rbe6756adea2e4ad8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Event Status History" sheetId="7" r:id="R1f30a8cb421f48d5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Event Taxonomy" sheetId="8" r:id="Rcbb3668447104647"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="9" r:id="Rfbcedf9b6e7d409a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overview" sheetId="10" r:id="R2e9fccb165bd40c1"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1450,6 +1450,257 @@
         <x:v>https://www.reuters.com/business/autos-transportation/cruise-operators-reap-benefits-their-own-private-islands-2024-10-29/</x:v>
       </x:c>
     </x:row>
+    <x:row r="23">
+      <x:c r="A23" t="str">
+        <x:v>EVT134_001</x:v>
+      </x:c>
+      <x:c r="B23" t="str">
+        <x:v>2026-09-08</x:v>
+      </x:c>
+      <x:c r="C23" t="str"/>
+      <x:c r="D23" t="str">
+        <x:v>Commercial / Legal</x:v>
+      </x:c>
+      <x:c r="E23" t="str">
+        <x:v>Tanker rate dispute</x:v>
+      </x:c>
+      <x:c r="F23" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="G23" t="str">
+        <x:v>Active / pending court case</x:v>
+      </x:c>
+      <x:c r="H23" t="str">
+        <x:v>Maritime</x:v>
+      </x:c>
+      <x:c r="I23" t="str">
+        <x:v>Middle East / Global</x:v>
+      </x:c>
+      <x:c r="J23" t="str">
+        <x:v>Saudi Arabia–China tanker market</x:v>
+      </x:c>
+      <x:c r="K23" t="str">
+        <x:v>Hunter Group USD 55m tanker-rate dispute</x:v>
+      </x:c>
+      <x:c r="L23" t="str">
+        <x:v>Hunter Group says an undisclosed counterparty owes USD 55m as wartime tanker-rate benchmarks diverge.</x:v>
+      </x:c>
+      <x:c r="M23" t="str">
+        <x:v>Payment dispute and counterparty exposure</x:v>
+      </x:c>
+      <x:c r="N23" t="str">
+        <x:v>Highlights extreme Hormuz-linked freight-rate volatility and benchmark risk.</x:v>
+      </x:c>
+      <x:c r="O23" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="P23" t="str">
+        <x:v>NEWS134_001</x:v>
+      </x:c>
+      <x:c r="Q23" t="str">
+        <x:v>https://gcaptain.com/oil-tanker-company-says-its-owed-55-million-in-rate-dispute/</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24">
+      <x:c r="A24" t="str">
+        <x:v>EVT134_002</x:v>
+      </x:c>
+      <x:c r="B24" t="str"/>
+      <x:c r="C24" t="str"/>
+      <x:c r="D24" t="str">
+        <x:v>Defence / Industrial</x:v>
+      </x:c>
+      <x:c r="E24" t="str">
+        <x:v>Maintenance contract extension</x:v>
+      </x:c>
+      <x:c r="F24" t="str">
+        <x:v>Moderate</x:v>
+      </x:c>
+      <x:c r="G24" t="str">
+        <x:v>Awarded / through 2032</x:v>
+      </x:c>
+      <x:c r="H24" t="str">
+        <x:v>Maritime / Defence</x:v>
+      </x:c>
+      <x:c r="I24" t="str">
+        <x:v>Canada</x:v>
+      </x:c>
+      <x:c r="J24" t="str">
+        <x:v>Victoria, British Columbia</x:v>
+      </x:c>
+      <x:c r="K24" t="str">
+        <x:v>Seaspan submarine maintenance support extended through 2032</x:v>
+      </x:c>
+      <x:c r="L24" t="str">
+        <x:v>Seaspan announced a Babcock Canada extension supporting submarine maintenance through 2032.</x:v>
+      </x:c>
+      <x:c r="M24" t="str">
+        <x:v>Continued Victoria Shipyards maintenance workload</x:v>
+      </x:c>
+      <x:c r="N24" t="str">
+        <x:v>Extends Canadian submarine MRO capacity and supplier continuity.</x:v>
+      </x:c>
+      <x:c r="O24" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="P24" t="str">
+        <x:v>NEWS134_002</x:v>
+      </x:c>
+      <x:c r="Q24" t="str">
+        <x:v>https://www.seaspan.com/press-release/seaspan-awarded-a-submarine-maintenance-contract-extension-by-babcock-canada-through-2032/</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25">
+      <x:c r="A25" t="str">
+        <x:v>EVT134_003</x:v>
+      </x:c>
+      <x:c r="B25" t="str">
+        <x:v>2026-09-08</x:v>
+      </x:c>
+      <x:c r="C25" t="str"/>
+      <x:c r="D25" t="str">
+        <x:v>Regulatory / Enforcement</x:v>
+      </x:c>
+      <x:c r="E25" t="str">
+        <x:v>Environmental compliance conviction</x:v>
+      </x:c>
+      <x:c r="F25" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="G25" t="str">
+        <x:v>Sentenced / probation</x:v>
+      </x:c>
+      <x:c r="H25" t="str">
+        <x:v>Maritime</x:v>
+      </x:c>
+      <x:c r="I25" t="str">
+        <x:v>United States</x:v>
+      </x:c>
+      <x:c r="J25" t="str">
+        <x:v>Port of Philadelphia / Delaware River</x:v>
+      </x:c>
+      <x:c r="K25" t="str">
+        <x:v>MSC SAMIRA III oily-waste enforcement case</x:v>
+      </x:c>
+      <x:c r="L25" t="str">
+        <x:v>MSC Shipmanagement and Hong Kong Spirit Shipping and Trading received combined USD 1.75m fines for APPS violations.</x:v>
+      </x:c>
+      <x:c r="M25" t="str">
+        <x:v>Four years' probation for each company; compliance oversight</x:v>
+      </x:c>
+      <x:c r="N25" t="str">
+        <x:v>Fleet-wide environmental-control and reputational implications.</x:v>
+      </x:c>
+      <x:c r="O25" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="P25" t="str">
+        <x:v>NEWS134_003</x:v>
+      </x:c>
+      <x:c r="Q25" t="str">
+        <x:v>https://gcaptain.com/msc-shipmanagement-fined-1-75-million-over-illegal-oily-waste-discharges/</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26">
+      <x:c r="A26" t="str">
+        <x:v>EVT134_004</x:v>
+      </x:c>
+      <x:c r="B26" t="str">
+        <x:v>2026-09-08</x:v>
+      </x:c>
+      <x:c r="C26" t="str"/>
+      <x:c r="D26" t="str">
+        <x:v>Workforce / Industrial Capacity</x:v>
+      </x:c>
+      <x:c r="E26" t="str">
+        <x:v>Training network expansion</x:v>
+      </x:c>
+      <x:c r="F26" t="str">
+        <x:v>Moderate</x:v>
+      </x:c>
+      <x:c r="G26" t="str">
+        <x:v>Designated / five-year term</x:v>
+      </x:c>
+      <x:c r="H26" t="str">
+        <x:v>Maritime / Education</x:v>
+      </x:c>
+      <x:c r="I26" t="str">
+        <x:v>United States</x:v>
+      </x:c>
+      <x:c r="J26" t="str">
+        <x:v>16 additional institutions</x:v>
+      </x:c>
+      <x:c r="K26" t="str">
+        <x:v>MARAD adds 16 maritime training centers</x:v>
+      </x:c>
+      <x:c r="L26" t="str">
+        <x:v>The programme reaches 48 institutions, 87 facilities and about 58,000 trainees annually.</x:v>
+      </x:c>
+      <x:c r="M26" t="str">
+        <x:v>Expanded training capacity</x:v>
+      </x:c>
+      <x:c r="N26" t="str">
+        <x:v>Supports mariner supply, shipbuilding and maritime industrial-base expansion.</x:v>
+      </x:c>
+      <x:c r="O26" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="P26" t="str">
+        <x:v>NEWS134_004</x:v>
+      </x:c>
+      <x:c r="Q26" t="str">
+        <x:v>https://gcaptain.com/u-s-adds-16-maritime-training-centers-amid-shipbuilding-push/</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27">
+      <x:c r="A27" t="str">
+        <x:v>EVT134_005</x:v>
+      </x:c>
+      <x:c r="B27" t="str">
+        <x:v>2026-09-08</x:v>
+      </x:c>
+      <x:c r="C27" t="str"/>
+      <x:c r="D27" t="str">
+        <x:v>Commercial / Legal</x:v>
+      </x:c>
+      <x:c r="E27" t="str">
+        <x:v>Shipbuilding arbitration</x:v>
+      </x:c>
+      <x:c r="F27" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="G27" t="str">
+        <x:v>Pending arbitration</x:v>
+      </x:c>
+      <x:c r="H27" t="str">
+        <x:v>Maritime / Energy</x:v>
+      </x:c>
+      <x:c r="I27" t="str">
+        <x:v>Russia / South Korea / Singapore</x:v>
+      </x:c>
+      <x:c r="J27" t="str">
+        <x:v>Arctic LNG 2 seeks USD 1.02bn from Hanwha Ocean</x:v>
+      </x:c>
+      <x:c r="K27" t="str">
+        <x:v>Claim relates to terminated contracts for Arc7 LNG carriers amid sanctions complications.</x:v>
+      </x:c>
+      <x:c r="L27" t="str">
+        <x:v>Carrier-delivery and contract uncertainty</x:v>
+      </x:c>
+      <x:c r="M27" t="str">
+        <x:v>Constrains Arctic LNG export logistics and exposes shipyard/buyer contract risk.</x:v>
+      </x:c>
+      <x:c r="N27" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="O27" t="str">
+        <x:v>NEWS134_005</x:v>
+      </x:c>
+      <x:c r="P27" t="str">
+        <x:v>https://www.reuters.com/business/energy/russias-arctic-lng-2-seeks-1-billion-damages-south-koreas-hanwha-2026-09-08/</x:v>
+      </x:c>
+      <x:c r="Q27" t="str"/>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -2984,6 +3235,58 @@
         <x:v>Headline-level evidence.</x:v>
       </x:c>
     </x:row>
+    <x:row r="33">
+      <x:c r="A33" t="str">
+        <x:v>EAL134_001</x:v>
+      </x:c>
+      <x:c r="B33" t="str">
+        <x:v>EVT134_003</x:v>
+      </x:c>
+      <x:c r="C33" t="str">
+        <x:v>VES_MSC_SAMIRA_III</x:v>
+      </x:c>
+      <x:c r="D33" t="str">
+        <x:v>MSC SAMIRA III</x:v>
+      </x:c>
+      <x:c r="E33" t="str">
+        <x:v>Vessel</x:v>
+      </x:c>
+      <x:c r="F33" t="str">
+        <x:v>SUBJECT VESSEL</x:v>
+      </x:c>
+      <x:c r="G33" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="H33" t="str">
+        <x:v>IMO pending verification.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34">
+      <x:c r="A34" t="str">
+        <x:v>EAL134_002</x:v>
+      </x:c>
+      <x:c r="B34" t="str">
+        <x:v>EVT134_005</x:v>
+      </x:c>
+      <x:c r="C34" t="str">
+        <x:v>ASSET_ARCTIC_LNG2</x:v>
+      </x:c>
+      <x:c r="D34" t="str">
+        <x:v>Arctic LNG 2</x:v>
+      </x:c>
+      <x:c r="E34" t="str">
+        <x:v>LNG project</x:v>
+      </x:c>
+      <x:c r="F34" t="str">
+        <x:v>EXPORT FLEET DEPENDENCY</x:v>
+      </x:c>
+      <x:c r="G34" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="H34" t="str">
+        <x:v>19.8 mtpa planned project capacity.</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -3541,6 +3844,186 @@
         <x:v>High</x:v>
       </x:c>
     </x:row>
+    <x:row r="28">
+      <x:c r="A28" t="str">
+        <x:v>ECL134_001</x:v>
+      </x:c>
+      <x:c r="B28" t="str">
+        <x:v>EVT134_001</x:v>
+      </x:c>
+      <x:c r="C28" t="str">
+        <x:v>COMP_HUNTER_GROUP</x:v>
+      </x:c>
+      <x:c r="D28" t="str">
+        <x:v>Hunter Group ASA</x:v>
+      </x:c>
+      <x:c r="E28" t="str">
+        <x:v>CLAIMANT</x:v>
+      </x:c>
+      <x:c r="F28" t="str">
+        <x:v>High</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29">
+      <x:c r="A29" t="str">
+        <x:v>ECL134_002</x:v>
+      </x:c>
+      <x:c r="B29" t="str">
+        <x:v>EVT134_002</x:v>
+      </x:c>
+      <x:c r="C29" t="str">
+        <x:v>COMP_SEASPAN_ULC</x:v>
+      </x:c>
+      <x:c r="D29" t="str">
+        <x:v>Seaspan ULC</x:v>
+      </x:c>
+      <x:c r="E29" t="str">
+        <x:v>SUBCONTRACTOR / MAINTENANCE YARD</x:v>
+      </x:c>
+      <x:c r="F29" t="str">
+        <x:v>High</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30">
+      <x:c r="A30" t="str">
+        <x:v>ECL134_003</x:v>
+      </x:c>
+      <x:c r="B30" t="str">
+        <x:v>EVT134_002</x:v>
+      </x:c>
+      <x:c r="C30" t="str">
+        <x:v>COMP_BABCOCK_CANADA</x:v>
+      </x:c>
+      <x:c r="D30" t="str">
+        <x:v>Babcock Canada</x:v>
+      </x:c>
+      <x:c r="E30" t="str">
+        <x:v>PRIME CONTRACTOR / CUSTOMER</x:v>
+      </x:c>
+      <x:c r="F30" t="str">
+        <x:v>High</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31">
+      <x:c r="A31" t="str">
+        <x:v>ECL134_004</x:v>
+      </x:c>
+      <x:c r="B31" t="str">
+        <x:v>EVT134_003</x:v>
+      </x:c>
+      <x:c r="C31" t="str">
+        <x:v>COMP_MSC_SHIPMANAGEMENT</x:v>
+      </x:c>
+      <x:c r="D31" t="str">
+        <x:v>MSC Shipmanagement Limited</x:v>
+      </x:c>
+      <x:c r="E31" t="str">
+        <x:v>DEFENDANT / MANAGER</x:v>
+      </x:c>
+      <x:c r="F31" t="str">
+        <x:v>High</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32">
+      <x:c r="A32" t="str">
+        <x:v>ECL134_005</x:v>
+      </x:c>
+      <x:c r="B32" t="str">
+        <x:v>EVT134_003</x:v>
+      </x:c>
+      <x:c r="C32" t="str">
+        <x:v>COMP_HONG_KONG_SPIRIT</x:v>
+      </x:c>
+      <x:c r="D32" t="str">
+        <x:v>Hong Kong Spirit Shipping and Trading Ltd</x:v>
+      </x:c>
+      <x:c r="E32" t="str">
+        <x:v>DEFENDANT / OWNER</x:v>
+      </x:c>
+      <x:c r="F32" t="str">
+        <x:v>High</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33">
+      <x:c r="A33" t="str">
+        <x:v>ECL134_006</x:v>
+      </x:c>
+      <x:c r="B33" t="str">
+        <x:v>EVT134_004</x:v>
+      </x:c>
+      <x:c r="C33" t="str">
+        <x:v>ORG_MARAD</x:v>
+      </x:c>
+      <x:c r="D33" t="str">
+        <x:v>U.S. Maritime Administration</x:v>
+      </x:c>
+      <x:c r="E33" t="str">
+        <x:v>PROGRAMME OWNER</x:v>
+      </x:c>
+      <x:c r="F33" t="str">
+        <x:v>High</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34">
+      <x:c r="A34" t="str">
+        <x:v>ECL134_007</x:v>
+      </x:c>
+      <x:c r="B34" t="str">
+        <x:v>EVT134_005</x:v>
+      </x:c>
+      <x:c r="C34" t="str">
+        <x:v>COMP_ARCTIC_LNG2</x:v>
+      </x:c>
+      <x:c r="D34" t="str">
+        <x:v>Arctic LNG 2 LLC</x:v>
+      </x:c>
+      <x:c r="E34" t="str">
+        <x:v>CLAIMANT</x:v>
+      </x:c>
+      <x:c r="F34" t="str">
+        <x:v>High</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35">
+      <x:c r="A35" t="str">
+        <x:v>ECL134_008</x:v>
+      </x:c>
+      <x:c r="B35" t="str">
+        <x:v>EVT134_005</x:v>
+      </x:c>
+      <x:c r="C35" t="str">
+        <x:v>COMP_HANWHA_OCEAN</x:v>
+      </x:c>
+      <x:c r="D35" t="str">
+        <x:v>Hanwha Ocean</x:v>
+      </x:c>
+      <x:c r="E35" t="str">
+        <x:v>RESPONDENT / BUILDER</x:v>
+      </x:c>
+      <x:c r="F35" t="str">
+        <x:v>High</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36">
+      <x:c r="A36" t="str">
+        <x:v>ECL134_009</x:v>
+      </x:c>
+      <x:c r="B36" t="str">
+        <x:v>EVT134_005</x:v>
+      </x:c>
+      <x:c r="C36" t="str">
+        <x:v>COMP_NOVATEK</x:v>
+      </x:c>
+      <x:c r="D36" t="str">
+        <x:v>PAO NOVATEK</x:v>
+      </x:c>
+      <x:c r="E36" t="str">
+        <x:v>PROJECT LEAD / 60% OWNER</x:v>
+      </x:c>
+      <x:c r="F36" t="str">
+        <x:v>High</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -3875,6 +4358,26 @@
         <x:v>SECURITY_ADVISORY</x:v>
       </x:c>
       <x:c r="F16" t="str">
+        <x:v>High</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17">
+      <x:c r="A17" t="str">
+        <x:v>ESL134_001</x:v>
+      </x:c>
+      <x:c r="B17" t="str">
+        <x:v>EVT134_001</x:v>
+      </x:c>
+      <x:c r="C17" t="str">
+        <x:v>SYS_HORMUZ_SECURITY</x:v>
+      </x:c>
+      <x:c r="D17" t="str">
+        <x:v>Persian Gulf / Hormuz / Gulf of Oman Security System</x:v>
+      </x:c>
+      <x:c r="E17" t="str">
+        <x:v>RATE / ROUTE-RISK TRANSMISSION</x:v>
+      </x:c>
+      <x:c r="F17" t="str">
         <x:v>High</x:v>
       </x:c>
     </x:row>
@@ -4333,6 +4836,93 @@
         <x:v>Advisory → operational posture</x:v>
       </x:c>
     </x:row>
+    <x:row r="16">
+      <x:c r="A16" t="str">
+        <x:v>CHAIN134_001</x:v>
+      </x:c>
+      <x:c r="B16" t="str">
+        <x:v>EVT134_001</x:v>
+      </x:c>
+      <x:c r="C16" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D16" t="str">
+        <x:v>Hormuz conflict risk</x:v>
+      </x:c>
+      <x:c r="E16" t="str">
+        <x:v>Tanker availability and benchmark rates surge</x:v>
+      </x:c>
+      <x:c r="F16" t="str">
+        <x:v>Charter-rate payment dispute</x:v>
+      </x:c>
+      <x:c r="G16" t="str">
+        <x:v>Court exposure and counterparty risk</x:v>
+      </x:c>
+      <x:c r="H16" t="str">
+        <x:v>Volatile energy-transport economics</x:v>
+      </x:c>
+      <x:c r="I16" t="str">
+        <x:v>Security → freight rate → legal / financial</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17">
+      <x:c r="A17" t="str">
+        <x:v>CHAIN134_002</x:v>
+      </x:c>
+      <x:c r="B17" t="str">
+        <x:v>EVT134_005</x:v>
+      </x:c>
+      <x:c r="C17" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D17" t="str">
+        <x:v>Sanctions and contract termination</x:v>
+      </x:c>
+      <x:c r="E17" t="str">
+        <x:v>Arc7 carrier delivery programme disrupted</x:v>
+      </x:c>
+      <x:c r="F17" t="str">
+        <x:v>LNG export logistics constrained</x:v>
+      </x:c>
+      <x:c r="G17" t="str">
+        <x:v>USD 1.02bn arbitration claim</x:v>
+      </x:c>
+      <x:c r="H17" t="str">
+        <x:v>Arctic LNG project monetization risk</x:v>
+      </x:c>
+      <x:c r="I17" t="str">
+        <x:v>Sanctions → fleet → export → arbitration</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18">
+      <x:c r="A18" t="str">
+        <x:v>CHAIN134_003</x:v>
+      </x:c>
+      <x:c r="B18" t="str">
+        <x:v>EVT134_004</x:v>
+      </x:c>
+      <x:c r="C18" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D18" t="str">
+        <x:v>Shipbuilding and mariner workforce shortage</x:v>
+      </x:c>
+      <x:c r="E18" t="str">
+        <x:v>16 institutions added</x:v>
+      </x:c>
+      <x:c r="F18" t="str">
+        <x:v>Training network reaches 48 institutions / 87 facilities</x:v>
+      </x:c>
+      <x:c r="G18" t="str">
+        <x:v>Larger skilled-labour pipeline</x:v>
+      </x:c>
+      <x:c r="H18" t="str">
+        <x:v>Maritime industrial-base capacity</x:v>
+      </x:c>
+      <x:c r="I18" t="str">
+        <x:v>Policy → training → workforce → capacity</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -5108,6 +5698,90 @@
         <x:v>https://www.reuters.com/business/autos-transportation/cruise-operators-reap-benefits-their-own-private-islands-2024-10-29/</x:v>
       </x:c>
     </x:row>
+    <x:row r="22">
+      <x:c r="A22" t="str">
+        <x:v>SRC134_003</x:v>
+      </x:c>
+      <x:c r="B22" t="str">
+        <x:v>gCaptain</x:v>
+      </x:c>
+      <x:c r="C22" t="str">
+        <x:v>Hunter Group says a counterparty owes USD 55 million amid a tanker-rate benchmark dispute.</x:v>
+      </x:c>
+      <x:c r="D22" t="str">
+        <x:v>https://gcaptain.com/oil-tanker-company-says-its-owed-55-million-in-rate-dispute/</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23">
+      <x:c r="A23" t="str">
+        <x:v>SRC134_004</x:v>
+      </x:c>
+      <x:c r="B23" t="str">
+        <x:v>Seaspan</x:v>
+      </x:c>
+      <x:c r="C23" t="str">
+        <x:v>Seaspan awarded a Babcock Canada submarine-maintenance contract extension through 2032.</x:v>
+      </x:c>
+      <x:c r="D23" t="str">
+        <x:v>https://www.seaspan.com/press-release/seaspan-awarded-a-submarine-maintenance-contract-extension-by-babcock-canada-through-2032/</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24">
+      <x:c r="A24" t="str">
+        <x:v>SRC134_005</x:v>
+      </x:c>
+      <x:c r="B24" t="str">
+        <x:v>gCaptain</x:v>
+      </x:c>
+      <x:c r="C24" t="str">
+        <x:v>MSC Shipmanagement and Hong Kong Spirit Shipping and Trading fined USD 1.75 million over illegal oily-waste discharges from MSC SAMIRA III.</x:v>
+      </x:c>
+      <x:c r="D24" t="str">
+        <x:v>https://gcaptain.com/msc-shipmanagement-fined-1-75-million-over-illegal-oily-waste-discharges/</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25">
+      <x:c r="A25" t="str">
+        <x:v>SRC134_006</x:v>
+      </x:c>
+      <x:c r="B25" t="str">
+        <x:v>gCaptain</x:v>
+      </x:c>
+      <x:c r="C25" t="str">
+        <x:v>MARAD adds 16 maritime training institutions, taking the network to 48 institutions and 87 facilities.</x:v>
+      </x:c>
+      <x:c r="D25" t="str">
+        <x:v>https://gcaptain.com/u-s-adds-16-maritime-training-centers-amid-shipbuilding-push/</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26">
+      <x:c r="A26" t="str">
+        <x:v>SRC134_007</x:v>
+      </x:c>
+      <x:c r="B26" t="str">
+        <x:v>gCaptain</x:v>
+      </x:c>
+      <x:c r="C26" t="str">
+        <x:v>Arctic LNG 2 seeks about USD 1 billion from Hanwha Ocean in a shipbuilding-contract dispute.</x:v>
+      </x:c>
+      <x:c r="D26" t="str">
+        <x:v>https://gcaptain.com/russias-arctic-lng-2-seeks-1-billion-in-damages-from-south-koreas-hanwha/</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27">
+      <x:c r="A27" t="str">
+        <x:v>SRC134_008</x:v>
+      </x:c>
+      <x:c r="B27" t="str">
+        <x:v>Reuters</x:v>
+      </x:c>
+      <x:c r="C27" t="str">
+        <x:v>Arctic LNG 2 seeks USD 1.02 billion / KRW 1.37 trillion at SIAC over terminated Arc7 LNG-carrier contracts.</x:v>
+      </x:c>
+      <x:c r="D27" t="str">
+        <x:v>https://www.reuters.com/business/energy/russias-arctic-lng-2-seeks-1-billion-damages-south-koreas-hanwha-2026-09-08/</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>

--- a/data/13_events_hazards.xlsx
+++ b/data/13_events_hazards.xlsx
@@ -2,16 +2,16 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Events" sheetId="1" r:id="Rf1a6bb9137e540e2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Event Locations" sheetId="2" r:id="Rb68daac7eb3140bd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Event Asset Links" sheetId="3" r:id="R1acc9233602f4f2a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Event Company Links" sheetId="4" r:id="R7add1043c89e4e53"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Event System Links" sheetId="5" r:id="R96458049367c4e98"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Impact Chains" sheetId="6" r:id="Rbe6756adea2e4ad8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Event Status History" sheetId="7" r:id="R1f30a8cb421f48d5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Event Taxonomy" sheetId="8" r:id="Rcbb3668447104647"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="9" r:id="Rfbcedf9b6e7d409a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overview" sheetId="10" r:id="R2e9fccb165bd40c1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Events" sheetId="1" r:id="R9a833774744149e4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Event Locations" sheetId="2" r:id="R7afab5acb7454200"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Event Asset Links" sheetId="3" r:id="R5ae2b83a03c64df3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Event Company Links" sheetId="4" r:id="Rc16abfcfd53f413f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Event System Links" sheetId="5" r:id="R3ad6bdddd8654fc0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Impact Chains" sheetId="6" r:id="R9c7919e129c440fe"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Event Status History" sheetId="7" r:id="Rbc3ed4d713e5431a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Event Taxonomy" sheetId="8" r:id="R1435dbb4e89c496f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="9" r:id="R536af2d85e2f4d8f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overview" sheetId="10" r:id="Rbdb6eadf3312413a"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -71,7 +71,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="19">
+  <x:cellXfs count="20">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -105,6 +105,7 @@
     <x:xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -1701,6 +1702,161 @@
       </x:c>
       <x:c r="Q27" t="str"/>
     </x:row>
+    <x:row r="28">
+      <x:c r="A28" s="10" t="str">
+        <x:v>EVT_SEC_001</x:v>
+      </x:c>
+      <x:c r="B28" s="10" t="str">
+        <x:v>2026-08-27</x:v>
+      </x:c>
+      <x:c r="C28" s="10"/>
+      <x:c r="D28" s="10" t="str">
+        <x:v>Maritime Safety / SAR</x:v>
+      </x:c>
+      <x:c r="E28" s="10" t="str">
+        <x:v>Crew injury / foreign vessel rescue</x:v>
+      </x:c>
+      <x:c r="F28" s="10" t="str">
+        <x:v>Medium</x:v>
+      </x:c>
+      <x:c r="G28" s="10" t="str">
+        <x:v>Closed / final update</x:v>
+      </x:c>
+      <x:c r="H28" s="10" t="str">
+        <x:v>Maritime</x:v>
+      </x:c>
+      <x:c r="I28" s="10" t="str">
+        <x:v>Japan</x:v>
+      </x:c>
+      <x:c r="J28" s="10" t="str">
+        <x:v>~220 km northeast of Nosappu Cape</x:v>
+      </x:c>
+      <x:c r="K28" s="10" t="str">
+        <x:v>JCG foreign-vessel crew injury response</x:v>
+      </x:c>
+      <x:c r="L28" s="10" t="str">
+        <x:v>Japan Coast Guard reported a crew injury aboard a Marshall Islands-flagged cargo vessel and coordinated rescue activity in waters surrounding Japan.</x:v>
+      </x:c>
+      <x:c r="M28" s="10" t="str">
+        <x:v>SAR / medical response; foreign-vessel incident</x:v>
+      </x:c>
+      <x:c r="N28" s="10" t="str">
+        <x:v>Operational disruption to vessel; useful MARSEC casualty signal</x:v>
+      </x:c>
+      <x:c r="O28" s="10" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="P28" s="10" t="str">
+        <x:v>SRC_JCG</x:v>
+      </x:c>
+      <x:c r="Q28" s="10" t="str">
+        <x:v>https://www.kaiho.mlit.go.jp/info/topics/rescueforeignvessels.html</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29">
+      <x:c r="A29" s="10" t="str">
+        <x:v>EVT_SEC_002</x:v>
+      </x:c>
+      <x:c r="B29" s="10" t="str">
+        <x:v>2026-08-17</x:v>
+      </x:c>
+      <x:c r="C29" s="10" t="str">
+        <x:v>2026-08-18</x:v>
+      </x:c>
+      <x:c r="D29" s="10" t="str">
+        <x:v>Maritime Casualty</x:v>
+      </x:c>
+      <x:c r="E29" s="10" t="str">
+        <x:v>Grounding</x:v>
+      </x:c>
+      <x:c r="F29" s="10" t="str">
+        <x:v>Medium</x:v>
+      </x:c>
+      <x:c r="G29" s="10" t="str">
+        <x:v>Resolved / response</x:v>
+      </x:c>
+      <x:c r="H29" s="10" t="str">
+        <x:v>Maritime</x:v>
+      </x:c>
+      <x:c r="I29" s="10" t="str">
+        <x:v>South Korea</x:v>
+      </x:c>
+      <x:c r="J29" s="10" t="str">
+        <x:v>South of Jawoldo, Incheon</x:v>
+      </x:c>
+      <x:c r="K29" s="10" t="str">
+        <x:v>Fishing vessel grounded near Jawoldo</x:v>
+      </x:c>
+      <x:c r="L29" s="10" t="str">
+        <x:v>Incheon Coast Guard reported a 4.02-ton fishing vessel driven onto rocks by strong current; one skipper rescued after response assets were deployed.</x:v>
+      </x:c>
+      <x:c r="M29" s="10" t="str">
+        <x:v>Grounding; SAR deployment</x:v>
+      </x:c>
+      <x:c r="N29" s="10" t="str">
+        <x:v>Localised navigation/safety event; validates KCG incident ingestion</x:v>
+      </x:c>
+      <x:c r="O29" s="10" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="P29" s="10" t="str">
+        <x:v>SRC_KCG</x:v>
+      </x:c>
+      <x:c r="Q29" s="10" t="str">
+        <x:v>https://kcg.go.kr/inchoncgs/na/ntt/selectNttInfo.do?mi=2084&amp;nttSn=71395</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30">
+      <x:c r="A30" s="10" t="str">
+        <x:v>EVT_SEC_003</x:v>
+      </x:c>
+      <x:c r="B30" s="10" t="str">
+        <x:v>2025-05-24</x:v>
+      </x:c>
+      <x:c r="C30" s="10"/>
+      <x:c r="D30" s="10" t="str">
+        <x:v>Maritime Casualty / Pollution Risk</x:v>
+      </x:c>
+      <x:c r="E30" s="10" t="str">
+        <x:v>Loss of stability / distress</x:v>
+      </x:c>
+      <x:c r="F30" s="10" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="G30" s="10" t="str">
+        <x:v>Historical / lessons retained</x:v>
+      </x:c>
+      <x:c r="H30" s="10" t="str">
+        <x:v>Maritime</x:v>
+      </x:c>
+      <x:c r="I30" s="10" t="str">
+        <x:v>India</x:v>
+      </x:c>
+      <x:c r="J30" s="10" t="str">
+        <x:v>~38 nm southwest of Kochi, Kerala</x:v>
+      </x:c>
+      <x:c r="K30" s="10" t="str">
+        <x:v>MSC Elsa 3 casualty and ICG response</x:v>
+      </x:c>
+      <x:c r="L30" s="10" t="str">
+        <x:v>Indian Coast Guard records describe MSC Elsa 3 developing a severe list southwest of Kochi, triggering SAR, firefighting, salvage coordination and pollution-response monitoring.</x:v>
+      </x:c>
+      <x:c r="M30" s="10" t="str">
+        <x:v>Crew rescue; salvage; fire/pollution response</x:v>
+      </x:c>
+      <x:c r="N30" s="10" t="str">
+        <x:v>Containerised cargo and coastal pollution exposure; useful India MARSEC case record</x:v>
+      </x:c>
+      <x:c r="O30" s="10" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="P30" s="10" t="str">
+        <x:v>SRC_ICG</x:v>
+      </x:c>
+      <x:c r="Q30" s="10" t="str">
+        <x:v>https://www.indiancoastguard.gov.in/other-assistance</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -2384,6 +2540,72 @@
         <x:v>Broad UKMTO advisory geography</x:v>
       </x:c>
     </x:row>
+    <x:row r="20">
+      <x:c r="A20" s="10" t="str">
+        <x:v>LOC_SEC_001</x:v>
+      </x:c>
+      <x:c r="B20" s="10" t="str">
+        <x:v>EVT_SEC_001</x:v>
+      </x:c>
+      <x:c r="C20" s="10" t="str">
+        <x:v>Waters northeast of Nosappu Cape</x:v>
+      </x:c>
+      <x:c r="D20" s="10" t="str">
+        <x:v>Japan</x:v>
+      </x:c>
+      <x:c r="E20" s="10"/>
+      <x:c r="F20" s="10"/>
+      <x:c r="G20" s="10" t="str">
+        <x:v>Regional / official description</x:v>
+      </x:c>
+      <x:c r="H20" s="10" t="str">
+        <x:v>Approx. 220 km northeast of cape; retain official wording until coordinates parsed.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21">
+      <x:c r="A21" s="10" t="str">
+        <x:v>LOC_SEC_002</x:v>
+      </x:c>
+      <x:c r="B21" s="10" t="str">
+        <x:v>EVT_SEC_002</x:v>
+      </x:c>
+      <x:c r="C21" s="10" t="str">
+        <x:v>South of Jawoldo, Ongjin-gun, Incheon</x:v>
+      </x:c>
+      <x:c r="D21" s="10" t="str">
+        <x:v>South Korea</x:v>
+      </x:c>
+      <x:c r="E21" s="10"/>
+      <x:c r="F21" s="10"/>
+      <x:c r="G21" s="10" t="str">
+        <x:v>Local / official description</x:v>
+      </x:c>
+      <x:c r="H21" s="10" t="str">
+        <x:v>Reported approx. 0.2 nm south of Jawoldo.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22">
+      <x:c r="A22" s="10" t="str">
+        <x:v>LOC_SEC_003</x:v>
+      </x:c>
+      <x:c r="B22" s="10" t="str">
+        <x:v>EVT_SEC_003</x:v>
+      </x:c>
+      <x:c r="C22" s="10" t="str">
+        <x:v>Southwest of Kochi, Kerala</x:v>
+      </x:c>
+      <x:c r="D22" s="10" t="str">
+        <x:v>India</x:v>
+      </x:c>
+      <x:c r="E22" s="10"/>
+      <x:c r="F22" s="10"/>
+      <x:c r="G22" s="10" t="str">
+        <x:v>Regional / official description</x:v>
+      </x:c>
+      <x:c r="H22" s="10" t="str">
+        <x:v>Approx. 38 nm southwest of Kochi.</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -4923,6 +5145,93 @@
         <x:v>Policy → training → workforce → capacity</x:v>
       </x:c>
     </x:row>
+    <x:row r="19">
+      <x:c r="A19" s="10" t="str">
+        <x:v>CHAIN_SEC_001</x:v>
+      </x:c>
+      <x:c r="B19" s="10" t="str">
+        <x:v>EVT_SEC_001</x:v>
+      </x:c>
+      <x:c r="C19" s="10" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D19" s="10" t="str">
+        <x:v>Crew injury on foreign cargo vessel</x:v>
+      </x:c>
+      <x:c r="E19" s="10" t="str">
+        <x:v>SAR / medical response</x:v>
+      </x:c>
+      <x:c r="F19" s="10" t="str">
+        <x:v>Potential voyage interruption</x:v>
+      </x:c>
+      <x:c r="G19" s="10" t="str">
+        <x:v>Official response activity / nearby traffic coordination</x:v>
+      </x:c>
+      <x:c r="H19" s="10" t="str">
+        <x:v>MARSEC casualty awareness</x:v>
+      </x:c>
+      <x:c r="I19" s="10" t="str">
+        <x:v>Safety propagation</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20">
+      <x:c r="A20" s="10" t="str">
+        <x:v>CHAIN_SEC_002</x:v>
+      </x:c>
+      <x:c r="B20" s="10" t="str">
+        <x:v>EVT_SEC_002</x:v>
+      </x:c>
+      <x:c r="C20" s="10" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D20" s="10" t="str">
+        <x:v>Strong current drives vessel onto rocks</x:v>
+      </x:c>
+      <x:c r="E20" s="10" t="str">
+        <x:v>Grounding and rescue response</x:v>
+      </x:c>
+      <x:c r="F20" s="10" t="str">
+        <x:v>Potential pollution/navigation hazard</x:v>
+      </x:c>
+      <x:c r="G20" s="10" t="str">
+        <x:v>Local operating caution</x:v>
+      </x:c>
+      <x:c r="H20" s="10" t="str">
+        <x:v>Grounding / casualty monitoring</x:v>
+      </x:c>
+      <x:c r="I20" s="10" t="str">
+        <x:v>Safety propagation</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21">
+      <x:c r="A21" s="10" t="str">
+        <x:v>CHAIN_SEC_003</x:v>
+      </x:c>
+      <x:c r="B21" s="10" t="str">
+        <x:v>EVT_SEC_003</x:v>
+      </x:c>
+      <x:c r="C21" s="10" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D21" s="10" t="str">
+        <x:v>Loss of stability / severe list</x:v>
+      </x:c>
+      <x:c r="E21" s="10" t="str">
+        <x:v>Crew rescue and salvage response</x:v>
+      </x:c>
+      <x:c r="F21" s="10" t="str">
+        <x:v>Fire/pollution monitoring</x:v>
+      </x:c>
+      <x:c r="G21" s="10" t="str">
+        <x:v>Potential coastal/container/cargo consequence</x:v>
+      </x:c>
+      <x:c r="H21" s="10" t="str">
+        <x:v>India maritime casualty and resilience case</x:v>
+      </x:c>
+      <x:c r="I21" s="10" t="str">
+        <x:v>Safety → environmental → commercial</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>

--- a/data/13_events_hazards.xlsx
+++ b/data/13_events_hazards.xlsx
@@ -2,16 +2,16 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Events" sheetId="1" r:id="R9a833774744149e4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Event Locations" sheetId="2" r:id="R7afab5acb7454200"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Event Asset Links" sheetId="3" r:id="R5ae2b83a03c64df3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Event Company Links" sheetId="4" r:id="Rc16abfcfd53f413f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Event System Links" sheetId="5" r:id="R3ad6bdddd8654fc0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Impact Chains" sheetId="6" r:id="R9c7919e129c440fe"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Event Status History" sheetId="7" r:id="Rbc3ed4d713e5431a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Event Taxonomy" sheetId="8" r:id="R1435dbb4e89c496f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="9" r:id="R536af2d85e2f4d8f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overview" sheetId="10" r:id="Rbdb6eadf3312413a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Events" sheetId="1" r:id="R582e3b0d2b0a4dda"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Event Locations" sheetId="2" r:id="R0999b2127d6b41eb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Event Asset Links" sheetId="3" r:id="R4c6abacb149744c7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Event Company Links" sheetId="4" r:id="Rd014727f722a4f41"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Event System Links" sheetId="5" r:id="R9d98f4b3bf0249ef"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Impact Chains" sheetId="6" r:id="Rb669642fa325460d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Event Status History" sheetId="7" r:id="Ree2a3fe1e5d540f0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Event Taxonomy" sheetId="8" r:id="Rf81ec03985b64744"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="9" r:id="R74fd20e9e65c4302"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overview" sheetId="10" r:id="Rc4ffcbe0622343a8"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -2659,7 +2659,7 @@
         <x:v>EVT128_001</x:v>
       </x:c>
       <x:c r="C2" s="10" t="str">
-        <x:v>PORT_ROTTERDAM</x:v>
+        <x:v>PORTG0242</x:v>
       </x:c>
       <x:c r="D2" s="10" t="str">
         <x:v>Port of Rotterdam</x:v>
@@ -2737,7 +2737,7 @@
         <x:v>EVT128_002</x:v>
       </x:c>
       <x:c r="C5" s="10" t="str">
-        <x:v>PORT_ROTTERDAM</x:v>
+        <x:v>PORTG0242</x:v>
       </x:c>
       <x:c r="D5" s="10" t="str">
         <x:v>Port of Rotterdam</x:v>
@@ -2841,7 +2841,7 @@
         <x:v>EVT128_005</x:v>
       </x:c>
       <x:c r="C9" s="10" t="str">
-        <x:v>PORT_ROTTERDAM</x:v>
+        <x:v>PORTG0242</x:v>
       </x:c>
       <x:c r="D9" s="10" t="str">
         <x:v>Port of Rotterdam</x:v>
@@ -4243,6 +4243,26 @@
         <x:v>PROJECT LEAD / 60% OWNER</x:v>
       </x:c>
       <x:c r="F36" t="str">
+        <x:v>High</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37">
+      <x:c r="A37" t="str">
+        <x:v>ECL128_015</x:v>
+      </x:c>
+      <x:c r="B37" t="str">
+        <x:v>EVT128_005</x:v>
+      </x:c>
+      <x:c r="C37" t="str">
+        <x:v>COMP_POR_AUTH</x:v>
+      </x:c>
+      <x:c r="D37" t="str">
+        <x:v>Port of Rotterdam Authority</x:v>
+      </x:c>
+      <x:c r="E37" t="str">
+        <x:v>Affected authority / port-system context</x:v>
+      </x:c>
+      <x:c r="F37" t="str">
         <x:v>High</x:v>
       </x:c>
     </x:row>

--- a/data/13_events_hazards.xlsx
+++ b/data/13_events_hazards.xlsx
@@ -2,16 +2,16 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Events" sheetId="1" r:id="R582e3b0d2b0a4dda"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Event Locations" sheetId="2" r:id="R0999b2127d6b41eb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Event Asset Links" sheetId="3" r:id="R4c6abacb149744c7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Event Company Links" sheetId="4" r:id="Rd014727f722a4f41"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Event System Links" sheetId="5" r:id="R9d98f4b3bf0249ef"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Impact Chains" sheetId="6" r:id="Rb669642fa325460d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Event Status History" sheetId="7" r:id="Ree2a3fe1e5d540f0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Event Taxonomy" sheetId="8" r:id="Rf81ec03985b64744"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="9" r:id="R74fd20e9e65c4302"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overview" sheetId="10" r:id="Rc4ffcbe0622343a8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Events" sheetId="1" r:id="R81fefc1772aa4a55"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Event Locations" sheetId="2" r:id="R7e92f84546aa4868"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Event Asset Links" sheetId="3" r:id="Ree6e7f5511aa49fc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Event Company Links" sheetId="4" r:id="R538f77c7a22346cf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Event System Links" sheetId="5" r:id="Rf276195771d947d8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Impact Chains" sheetId="6" r:id="R4e243b1778384eae"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Event Status History" sheetId="7" r:id="R86b814b329ac48cc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Event Taxonomy" sheetId="8" r:id="R2f5e4e35339c4056"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="9" r:id="R5901a4f7b3414520"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overview" sheetId="10" r:id="R22533ce8a4054d5a"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -71,7 +71,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="20">
+  <x:cellXfs count="19">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -105,7 +105,6 @@
     <x:xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -1300,561 +1299,1379 @@
     </x:row>
     <x:row r="20">
       <x:c r="A20" t="str">
-        <x:v>EVT133_001</x:v>
+        <x:v>EVT260910_001</x:v>
       </x:c>
       <x:c r="B20" t="str">
-        <x:v>2026-09-09</x:v>
-      </x:c>
-      <x:c r="C20" t="str"/>
+        <x:v>2026-09-08</x:v>
+      </x:c>
+      <x:c r="C20"/>
       <x:c r="D20" t="str">
         <x:v>Conflict / Security</x:v>
       </x:c>
       <x:c r="E20" t="str">
-        <x:v>Vessel incident / suspected projectile attack</x:v>
+        <x:v>Drone / missile attack on energy infrastructure</x:v>
       </x:c>
       <x:c r="F20" t="str">
-        <x:v>Critical</x:v>
+        <x:v>High</x:v>
       </x:c>
       <x:c r="G20" t="str">
-        <x:v>Casualty response / investigation</x:v>
+        <x:v>Active / developing</x:v>
       </x:c>
       <x:c r="H20" t="str">
-        <x:v>Maritime</x:v>
+        <x:v>Security / Energy</x:v>
       </x:c>
       <x:c r="I20" t="str">
-        <x:v>United Arab Emirates</x:v>
+        <x:v>Saudi Arabia / Yemen</x:v>
       </x:c>
       <x:c r="J20" t="str">
-        <x:v>Anchorage off Dubai</x:v>
+        <x:v>Jazan Refinery / Jazan (mapped)</x:v>
       </x:c>
       <x:c r="K20" t="str">
-        <x:v>HERCULES STAR incident off Dubai</x:v>
+        <x:v>Houthi Forces Attack Saudi Aramco's Jazan Refinery</x:v>
       </x:c>
       <x:c r="L20" t="str">
-        <x:v>Peninsula confirmed one crewmember died and one was missing after an incident involving HERCULES STAR at anchorage off Dubai. UKMTO separately reported a nearby vessel taking on water after an unknown projectile; identity equivalence remains unconfirmed in the source.</x:v>
+        <x:v>Houthi forces struck Saudi Aramco's Jazan refining complex in back-to-back attacks, with fires reported and the refinery taken offline.</x:v>
       </x:c>
       <x:c r="M20" t="str">
-        <x:v>Crew casualty; vessel emergency response; one person missing</x:v>
+        <x:v>Refinery outage; damage assessment and recovery required.</x:v>
       </x:c>
       <x:c r="N20" t="str">
-        <x:v>Bunker-supply and regional maritime-security exposure; potential anchorage and insurance impacts</x:v>
+        <x:v>Red Sea energy-export and refining risk; possible oil-price and routing effects.</x:v>
       </x:c>
       <x:c r="O20" t="str">
         <x:v>High</x:v>
       </x:c>
       <x:c r="P20" t="str">
-        <x:v>SRC133_001</x:v>
+        <x:v>SRC260910_001</x:v>
       </x:c>
       <x:c r="Q20" t="str">
-        <x:v>https://shipandbunker.com/news/world/583774-peninsula-confirms-tanker-involved-in-incident-off-dubai</x:v>
+        <x:v>https://maritime-executive.com/article/houthi-forces-attack-saudi-aramco-s-jazan-refinery</x:v>
       </x:c>
     </x:row>
     <x:row r="21">
       <x:c r="A21" t="str">
-        <x:v>EVT133_002</x:v>
+        <x:v>EVT260910_002</x:v>
       </x:c>
       <x:c r="B21" t="str">
-        <x:v>2026-09-10</x:v>
-      </x:c>
-      <x:c r="C21" t="str"/>
+        <x:v>2026-09-08</x:v>
+      </x:c>
+      <x:c r="C21"/>
       <x:c r="D21" t="str">
-        <x:v>Infrastructure / Commercial</x:v>
+        <x:v>Maritime Security / Interdiction</x:v>
       </x:c>
       <x:c r="E21" t="str">
-        <x:v>Port opening and expansion planning</x:v>
+        <x:v>Counter-narcotics boarding / vessel destruction</x:v>
       </x:c>
       <x:c r="F21" t="str">
-        <x:v>Moderate</x:v>
+        <x:v>High</x:v>
       </x:c>
       <x:c r="G21" t="str">
-        <x:v>Official opening reported / expansion planning</x:v>
+        <x:v>Completed / monitoring</x:v>
       </x:c>
       <x:c r="H21" t="str">
-        <x:v>Port</x:v>
+        <x:v>Security / Maritime</x:v>
       </x:c>
       <x:c r="I21" t="str">
-        <x:v>Canada</x:v>
+        <x:v>Ecuador / United States</x:v>
       </x:c>
       <x:c r="J21" t="str">
-        <x:v>Stewart, British Columbia</x:v>
+        <x:v>Eastern Pacific off Ecuador</x:v>
       </x:c>
       <x:c r="K21" t="str">
-        <x:v>Nisg̱a'a and Tahltan Nations mark Stewart port opening</x:v>
+        <x:v>U.S. Forces Destroy Drug-Runners' Floating Gas Station Off Ecuador</x:v>
       </x:c>
       <x:c r="L21" t="str">
-        <x:v>CBC reported that the Nisg̱a'a and Tahltan Nations marked the official opening of a Stewart, B.C. port while expansion plans take shape. Ownership, operator, capacity and expansion phasing are not inferred from the headline.</x:v>
+        <x:v>U.S. Southern Command boarded a high-seas refueling vessel linked to drug-running boats, removed the crew and destroyed the vessel.</x:v>
       </x:c>
       <x:c r="M21" t="str">
-        <x:v>New northern B.C. port capacity / gateway development signal</x:v>
+        <x:v>High-seas interdiction removed a suspected logistics node used by narcotics traffickers.</x:v>
       </x:c>
       <x:c r="N21" t="str">
-        <x:v>Potential mining, project cargo and regional export connectivity; detailed cargo scope requires verification</x:v>
+        <x:v>Operational precedent for maritime counter-narcotics enforcement and offshore logistics networks.</x:v>
       </x:c>
       <x:c r="O21" t="str">
-        <x:v>Medium</x:v>
+        <x:v>High</x:v>
       </x:c>
       <x:c r="P21" t="str">
-        <x:v>SRC133_002</x:v>
+        <x:v>SRC260910_002</x:v>
       </x:c>
       <x:c r="Q21" t="str">
-        <x:v>https://www.cbc.ca/news/canada/british-columbia/nisga-a-talhtan-port-opening-9.7338188</x:v>
+        <x:v>https://maritime-executive.com/article/u-s-forces-destroy-drug-runners-floating-gas-station-off-ecuador</x:v>
       </x:c>
     </x:row>
     <x:row r="22">
       <x:c r="A22" t="str">
-        <x:v>EVT133_003</x:v>
+        <x:v>EVT260910_003</x:v>
       </x:c>
       <x:c r="B22" t="str">
-        <x:v>2024-10-29</x:v>
-      </x:c>
-      <x:c r="C22" t="str"/>
+        <x:v>2026-09-10</x:v>
+      </x:c>
+      <x:c r="C22"/>
       <x:c r="D22" t="str">
-        <x:v>Commercial / Strategy</x:v>
+        <x:v>Shipyard / Joint Venture</x:v>
       </x:c>
       <x:c r="E22" t="str">
-        <x:v>Cruise private-destination investment wave</x:v>
+        <x:v>Ship repair joint venture</x:v>
       </x:c>
       <x:c r="F22" t="str">
-        <x:v>Moderate</x:v>
+        <x:v>Medium</x:v>
       </x:c>
       <x:c r="G22" t="str">
-        <x:v>Ongoing investment cycle</x:v>
+        <x:v>Announced / approvals pending</x:v>
       </x:c>
       <x:c r="H22" t="str">
-        <x:v>Maritime / Tourism</x:v>
+        <x:v>Trade / Commercial</x:v>
       </x:c>
       <x:c r="I22" t="str">
-        <x:v>Caribbean region</x:v>
+        <x:v>India / United Arab Emirates</x:v>
       </x:c>
       <x:c r="J22" t="str">
-        <x:v>Caribbean and Bahamas</x:v>
+        <x:v>Kochi, India</x:v>
       </x:c>
       <x:c r="K22" t="str">
-        <x:v>Cruise groups accelerate private-destination investment</x:v>
+        <x:v>Cochin and Drydocks World seal Kochi repair venture</x:v>
       </x:c>
       <x:c r="L22" t="str">
-        <x:v>Reuters reported 12 private Caribbean destinations in 2024 and major investment plans by Royal Caribbean, Carnival and Norwegian.</x:v>
+        <x:v>Cochin Shipyard approved a 50:50 joint venture with DP World's Drydocks World to take over and operate the International Ship Repair Facility in Kochi.</x:v>
       </x:c>
       <x:c r="M22" t="str">
-        <x:v>More itineraries anchored around operator-controlled destinations</x:v>
+        <x:v>Operating control and expansion of ship-repair capacity are planned subject to approvals.</x:v>
       </x:c>
       <x:c r="N22" t="str">
-        <x:v>Higher onboard/destination revenue capture and changed call patterns for public Caribbean ports</x:v>
+        <x:v>Deepens UAE-India ship-repair integration and expands Drydocks World's international repair footprint.</x:v>
       </x:c>
       <x:c r="O22" t="str">
         <x:v>High</x:v>
       </x:c>
       <x:c r="P22" t="str">
-        <x:v>SRC133_003</x:v>
+        <x:v>SRC260910_003</x:v>
       </x:c>
       <x:c r="Q22" t="str">
-        <x:v>https://www.reuters.com/business/autos-transportation/cruise-operators-reap-benefits-their-own-private-islands-2024-10-29/</x:v>
+        <x:v>https://splash247.com/cochin-and-drydocks-world-seal-kochi-repair-venture/</x:v>
       </x:c>
     </x:row>
     <x:row r="23">
       <x:c r="A23" t="str">
-        <x:v>EVT134_001</x:v>
+        <x:v>EVT260910_004</x:v>
       </x:c>
       <x:c r="B23" t="str">
         <x:v>2026-09-08</x:v>
       </x:c>
-      <x:c r="C23" t="str"/>
+      <x:c r="C23"/>
       <x:c r="D23" t="str">
-        <x:v>Commercial / Legal</x:v>
+        <x:v>Conflict / Security</x:v>
       </x:c>
       <x:c r="E23" t="str">
-        <x:v>Tanker rate dispute</x:v>
+        <x:v>Strike on commercial tankers</x:v>
       </x:c>
       <x:c r="F23" t="str">
-        <x:v>High</x:v>
+        <x:v>Critical</x:v>
       </x:c>
       <x:c r="G23" t="str">
-        <x:v>Active / pending court case</x:v>
+        <x:v>Active / developing</x:v>
       </x:c>
       <x:c r="H23" t="str">
-        <x:v>Maritime</x:v>
+        <x:v>Security / Maritime</x:v>
       </x:c>
       <x:c r="I23" t="str">
-        <x:v>Middle East / Global</x:v>
+        <x:v>Iran / Gulf states / United States</x:v>
       </x:c>
       <x:c r="J23" t="str">
-        <x:v>Saudi Arabia–China tanker market</x:v>
+        <x:v>Gulf of Oman / approaches to Kharg Island</x:v>
       </x:c>
       <x:c r="K23" t="str">
-        <x:v>Hunter Group USD 55m tanker-rate dispute</x:v>
+        <x:v>U.S. Hits Five More Iranian Tankers After Second Attack on U.S. Warship</x:v>
       </x:c>
       <x:c r="L23" t="str">
-        <x:v>Hunter Group says an undisclosed counterparty owes USD 55m as wartime tanker-rate benchmarks diverge.</x:v>
+        <x:v>U.S. forces struck five Iran-linked tankers—Derya, Horizon 1, Kaviz, Charminar and Riesco—after another attempted Iranian strike on a U.S. warship; Riesco later sank.</x:v>
       </x:c>
       <x:c r="M23" t="str">
-        <x:v>Payment dispute and counterparty exposure</x:v>
+        <x:v>Multiple tankers disabled or destroyed; threat warnings expanded around Gulf shipping.</x:v>
       </x:c>
       <x:c r="N23" t="str">
-        <x:v>Highlights extreme Hormuz-linked freight-rate volatility and benchmark risk.</x:v>
+        <x:v>Higher war-risk exposure, tanker availability loss and escalation risk for Gulf energy shipping.</x:v>
       </x:c>
       <x:c r="O23" t="str">
         <x:v>High</x:v>
       </x:c>
       <x:c r="P23" t="str">
-        <x:v>NEWS134_001</x:v>
+        <x:v>SRC260910_004</x:v>
       </x:c>
       <x:c r="Q23" t="str">
-        <x:v>https://gcaptain.com/oil-tanker-company-says-its-owed-55-million-in-rate-dispute/</x:v>
+        <x:v>https://maritime-executive.com/article/u-s-hits-three-more-iranian-tankers-after-second-attack-on-u-s-warship</x:v>
       </x:c>
     </x:row>
     <x:row r="24">
       <x:c r="A24" t="str">
-        <x:v>EVT134_002</x:v>
-      </x:c>
-      <x:c r="B24" t="str"/>
-      <x:c r="C24" t="str"/>
+        <x:v>EVT260910_005</x:v>
+      </x:c>
+      <x:c r="B24" t="str">
+        <x:v>2026-09-08</x:v>
+      </x:c>
+      <x:c r="C24"/>
       <x:c r="D24" t="str">
-        <x:v>Defence / Industrial</x:v>
+        <x:v>Contract / Charter</x:v>
       </x:c>
       <x:c r="E24" t="str">
-        <x:v>Maintenance contract extension</x:v>
+        <x:v>Long-term bulk shipping contract</x:v>
       </x:c>
       <x:c r="F24" t="str">
-        <x:v>Moderate</x:v>
+        <x:v>Medium</x:v>
       </x:c>
       <x:c r="G24" t="str">
-        <x:v>Awarded / through 2032</x:v>
+        <x:v>Contract announced</x:v>
       </x:c>
       <x:c r="H24" t="str">
-        <x:v>Maritime / Defence</x:v>
+        <x:v>Trade / Commercial</x:v>
       </x:c>
       <x:c r="I24" t="str">
-        <x:v>Canada</x:v>
+        <x:v>South Korea / Brazil / Global</x:v>
       </x:c>
       <x:c r="J24" t="str">
-        <x:v>Victoria, British Columbia</x:v>
+        <x:v>Global iron-ore trade</x:v>
       </x:c>
       <x:c r="K24" t="str">
-        <x:v>Seaspan submarine maintenance support extended through 2032</x:v>
+        <x:v>HMM Continues Diversification with $3.5B Ore Deal with Vale</x:v>
       </x:c>
       <x:c r="L24" t="str">
-        <x:v>Seaspan announced a Babcock Canada extension supporting submarine maintenance through 2032.</x:v>
+        <x:v>HMM announced a 25-year ore transport contract with Vale valued at $3.5bn, starting in 2030, supported by eight 210,000 dwt Newcastlemax newbuilds.</x:v>
       </x:c>
       <x:c r="M24" t="str">
-        <x:v>Continued Victoria Shipyards maintenance workload</x:v>
+        <x:v>Long-duration cargo commitment and fleet expansion.</x:v>
       </x:c>
       <x:c r="N24" t="str">
-        <x:v>Extends Canadian submarine MRO capacity and supplier continuity.</x:v>
+        <x:v>Strengthens HMM's bulk earnings base and Vale-linked iron-ore shipping capacity.</x:v>
       </x:c>
       <x:c r="O24" t="str">
         <x:v>High</x:v>
       </x:c>
       <x:c r="P24" t="str">
-        <x:v>NEWS134_002</x:v>
+        <x:v>SRC260910_005</x:v>
       </x:c>
       <x:c r="Q24" t="str">
-        <x:v>https://www.seaspan.com/press-release/seaspan-awarded-a-submarine-maintenance-contract-extension-by-babcock-canada-through-2032/</x:v>
+        <x:v>https://maritime-executive.com/article/hmm-continues-diversification-with-3-5b-ore-deal-with-vale</x:v>
       </x:c>
     </x:row>
     <x:row r="25">
       <x:c r="A25" t="str">
-        <x:v>EVT134_003</x:v>
+        <x:v>EVT260910_006</x:v>
       </x:c>
       <x:c r="B25" t="str">
-        <x:v>2026-09-08</x:v>
-      </x:c>
-      <x:c r="C25" t="str"/>
+        <x:v>2026-09-09</x:v>
+      </x:c>
+      <x:c r="C25"/>
       <x:c r="D25" t="str">
-        <x:v>Regulatory / Enforcement</x:v>
+        <x:v>Conflict / Security</x:v>
       </x:c>
       <x:c r="E25" t="str">
-        <x:v>Environmental compliance conviction</x:v>
+        <x:v>Blockade and maritime escalation assessment</x:v>
       </x:c>
       <x:c r="F25" t="str">
         <x:v>High</x:v>
       </x:c>
       <x:c r="G25" t="str">
-        <x:v>Sentenced / probation</x:v>
+        <x:v>Active / developing</x:v>
       </x:c>
       <x:c r="H25" t="str">
-        <x:v>Maritime</x:v>
+        <x:v>Security / Maritime</x:v>
       </x:c>
       <x:c r="I25" t="str">
-        <x:v>United States</x:v>
+        <x:v>Iran / United States / Gulf states</x:v>
       </x:c>
       <x:c r="J25" t="str">
-        <x:v>Port of Philadelphia / Delaware River</x:v>
+        <x:v>Strait of Hormuz / Gulf of Oman</x:v>
       </x:c>
       <x:c r="K25" t="str">
-        <x:v>MSC SAMIRA III oily-waste enforcement case</x:v>
+        <x:v>Iran Battles to Beat the Blockade</x:v>
       </x:c>
       <x:c r="L25" t="str">
-        <x:v>MSC Shipmanagement and Hong Kong Spirit Shipping and Trading received combined USD 1.75m fines for APPS violations.</x:v>
+        <x:v>Analysis describes a continuing U.S.-Iran strike cycle around blockade enforcement, Iranian anti-ship attacks and merchant traffic through Hormuz.</x:v>
       </x:c>
       <x:c r="M25" t="str">
-        <x:v>Four years' probation for each company; compliance oversight</x:v>
+        <x:v>Persistent military pressure on shipping and blockade operations.</x:v>
       </x:c>
       <x:c r="N25" t="str">
-        <x:v>Fleet-wide environmental-control and reputational implications.</x:v>
+        <x:v>Sustained energy-export constraints and elevated merchant-shipping risk around Hormuz.</x:v>
       </x:c>
       <x:c r="O25" t="str">
-        <x:v>High</x:v>
+        <x:v>Medium</x:v>
       </x:c>
       <x:c r="P25" t="str">
-        <x:v>NEWS134_003</x:v>
+        <x:v>SRC260910_006</x:v>
       </x:c>
       <x:c r="Q25" t="str">
-        <x:v>https://gcaptain.com/msc-shipmanagement-fined-1-75-million-over-illegal-oily-waste-discharges/</x:v>
+        <x:v>https://maritime-executive.com/editorials/iran-battles-to-beat-the-blockade</x:v>
       </x:c>
     </x:row>
     <x:row r="26">
       <x:c r="A26" t="str">
-        <x:v>EVT134_004</x:v>
+        <x:v>EVT260910_007</x:v>
       </x:c>
       <x:c r="B26" t="str">
-        <x:v>2026-09-08</x:v>
-      </x:c>
-      <x:c r="C26" t="str"/>
+        <x:v>2026-09-09</x:v>
+      </x:c>
+      <x:c r="C26"/>
       <x:c r="D26" t="str">
-        <x:v>Workforce / Industrial Capacity</x:v>
+        <x:v>Corporate / Investment</x:v>
       </x:c>
       <x:c r="E26" t="str">
-        <x:v>Training network expansion</x:v>
+        <x:v>Competing non-binding acquisition interest</x:v>
       </x:c>
       <x:c r="F26" t="str">
-        <x:v>Moderate</x:v>
+        <x:v>Medium</x:v>
       </x:c>
       <x:c r="G26" t="str">
-        <x:v>Designated / five-year term</x:v>
+        <x:v>Under review / due diligence</x:v>
       </x:c>
       <x:c r="H26" t="str">
-        <x:v>Maritime / Education</x:v>
+        <x:v>Trade / Commercial</x:v>
       </x:c>
       <x:c r="I26" t="str">
-        <x:v>United States</x:v>
+        <x:v>United States / Australia / South Korea</x:v>
       </x:c>
       <x:c r="J26" t="str">
-        <x:v>16 additional institutions</x:v>
+        <x:v>Austal USA</x:v>
       </x:c>
       <x:c r="K26" t="str">
-        <x:v>MARAD adds 16 maritime training centers</x:v>
+        <x:v>US Investors Top Hanwha's Bid for Austal USA</x:v>
       </x:c>
       <x:c r="L26" t="str">
-        <x:v>The programme reaches 48 institutions, 87 facilities and about 58,000 trainees annually.</x:v>
+        <x:v>Florida-based Wildcat Infrastructure indicated a $1.25bn-$1.35bn enterprise value for Austal USA, above Hanwha's indicated $1.05bn-$1.20bn range.</x:v>
       </x:c>
       <x:c r="M26" t="str">
-        <x:v>Expanded training capacity</x:v>
+        <x:v>Potential ownership change remains subject to due diligence and government approval.</x:v>
       </x:c>
       <x:c r="N26" t="str">
-        <x:v>Supports mariner supply, shipbuilding and maritime industrial-base expansion.</x:v>
+        <x:v>Could reshape ownership of a major U.S. naval and government shipbuilding platform.</x:v>
       </x:c>
       <x:c r="O26" t="str">
         <x:v>High</x:v>
       </x:c>
       <x:c r="P26" t="str">
-        <x:v>NEWS134_004</x:v>
+        <x:v>SRC260910_007</x:v>
       </x:c>
       <x:c r="Q26" t="str">
-        <x:v>https://gcaptain.com/u-s-adds-16-maritime-training-centers-amid-shipbuilding-push/</x:v>
+        <x:v>https://maritime-executive.com/article/us-investors-top-hanwha-s-bid-for-austal-usa</x:v>
       </x:c>
     </x:row>
     <x:row r="27">
       <x:c r="A27" t="str">
-        <x:v>EVT134_005</x:v>
+        <x:v>EVT260910_008</x:v>
       </x:c>
       <x:c r="B27" t="str">
-        <x:v>2026-09-08</x:v>
-      </x:c>
-      <x:c r="C27" t="str"/>
+        <x:v>2026-09-09</x:v>
+      </x:c>
+      <x:c r="C27"/>
       <x:c r="D27" t="str">
-        <x:v>Commercial / Legal</x:v>
+        <x:v>Port Development</x:v>
       </x:c>
       <x:c r="E27" t="str">
-        <x:v>Shipbuilding arbitration</x:v>
+        <x:v>Commissioning of export infrastructure</x:v>
       </x:c>
       <x:c r="F27" t="str">
-        <x:v>High</x:v>
+        <x:v>Medium</x:v>
       </x:c>
       <x:c r="G27" t="str">
-        <x:v>Pending arbitration</x:v>
+        <x:v>Commissioning</x:v>
       </x:c>
       <x:c r="H27" t="str">
-        <x:v>Maritime / Energy</x:v>
+        <x:v>Trade / Commercial</x:v>
       </x:c>
       <x:c r="I27" t="str">
-        <x:v>Russia / South Korea / Singapore</x:v>
+        <x:v>Guinea</x:v>
       </x:c>
       <x:c r="J27" t="str">
-        <x:v>Arctic LNG 2 seeks USD 1.02bn from Hanwha Ocean</x:v>
+        <x:v>Morebaya port</x:v>
       </x:c>
       <x:c r="K27" t="str">
-        <x:v>Claim relates to terminated contracts for Arc7 LNG carriers amid sanctions complications.</x:v>
+        <x:v>Simandou's Morebaya port moves into commissioning</x:v>
       </x:c>
       <x:c r="L27" t="str">
-        <x:v>Carrier-delivery and contract uncertainty</x:v>
+        <x:v>SimFer began commissioning stockyard, stacker-reclaimer and shiploader systems at Morebaya as Simandou export infrastructure advances toward operation.</x:v>
       </x:c>
       <x:c r="M27" t="str">
-        <x:v>Constrains Arctic LNG export logistics and exposes shipyard/buyer contract risk.</x:v>
+        <x:v>Export handling systems entering commissioning.</x:v>
       </x:c>
       <x:c r="N27" t="str">
-        <x:v>High</x:v>
+        <x:v>Supports future Simandou iron-ore exports of up to 120m tonnes a year across the shared system.</x:v>
       </x:c>
       <x:c r="O27" t="str">
-        <x:v>NEWS134_005</x:v>
+        <x:v>High</x:v>
       </x:c>
       <x:c r="P27" t="str">
-        <x:v>https://www.reuters.com/business/energy/russias-arctic-lng-2-seeks-1-billion-damages-south-koreas-hanwha-2026-09-08/</x:v>
-      </x:c>
-      <x:c r="Q27" t="str"/>
+        <x:v>SRC260910_008</x:v>
+      </x:c>
+      <x:c r="Q27" t="str">
+        <x:v>https://splash247.com/simandous-morebaya-port-moves-into-commissioning/</x:v>
+      </x:c>
     </x:row>
     <x:row r="28">
-      <x:c r="A28" s="10" t="str">
-        <x:v>EVT_SEC_001</x:v>
-      </x:c>
-      <x:c r="B28" s="10" t="str">
-        <x:v>2026-08-27</x:v>
-      </x:c>
-      <x:c r="C28" s="10"/>
-      <x:c r="D28" s="10" t="str">
-        <x:v>Maritime Safety / SAR</x:v>
-      </x:c>
-      <x:c r="E28" s="10" t="str">
-        <x:v>Crew injury / foreign vessel rescue</x:v>
-      </x:c>
-      <x:c r="F28" s="10" t="str">
+      <x:c r="A28" t="str">
+        <x:v>EVT260910_009</x:v>
+      </x:c>
+      <x:c r="B28" t="str">
+        <x:v>2026-09-09</x:v>
+      </x:c>
+      <x:c r="C28"/>
+      <x:c r="D28" t="str">
+        <x:v>Port Development</x:v>
+      </x:c>
+      <x:c r="E28" t="str">
+        <x:v>Container-terminal equipment expansion</x:v>
+      </x:c>
+      <x:c r="F28" t="str">
+        <x:v>Low</x:v>
+      </x:c>
+      <x:c r="G28" t="str">
+        <x:v>Equipment delivered / expansion ongoing</x:v>
+      </x:c>
+      <x:c r="H28" t="str">
+        <x:v>Trade / Commercial</x:v>
+      </x:c>
+      <x:c r="I28" t="str">
+        <x:v>Thailand</x:v>
+      </x:c>
+      <x:c r="J28" t="str">
+        <x:v>Port of Songkhla</x:v>
+      </x:c>
+      <x:c r="K28" t="str">
+        <x:v>Thailand's Songkhla gets first ship-to-shore cranes</x:v>
+      </x:c>
+      <x:c r="L28" t="str">
+        <x:v>Songkhla received its first two ship-to-shore cranes as part of a programme intended to lift annual container capacity from 150,000 to 450,000 TEU.</x:v>
+      </x:c>
+      <x:c r="M28" t="str">
+        <x:v>Improved quay handling and reduced dependence on geared vessels.</x:v>
+      </x:c>
+      <x:c r="N28" t="str">
+        <x:v>Adds southern Thailand container-handling capacity and strengthens Malaysia/Singapore service connectivity.</x:v>
+      </x:c>
+      <x:c r="O28" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="P28" t="str">
+        <x:v>SRC260910_009</x:v>
+      </x:c>
+      <x:c r="Q28" t="str">
+        <x:v>https://splash247.com/thailands-songkhla-gets-first-ship-to-shore-cranes/</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29">
+      <x:c r="A29" t="str">
+        <x:v>EVT260910_010</x:v>
+      </x:c>
+      <x:c r="B29" t="str">
+        <x:v>2026-09-09</x:v>
+      </x:c>
+      <x:c r="C29"/>
+      <x:c r="D29" t="str">
+        <x:v>Infrastructure Investment</x:v>
+      </x:c>
+      <x:c r="E29" t="str">
+        <x:v>Offshore-wind port development</x:v>
+      </x:c>
+      <x:c r="F29" t="str">
         <x:v>Medium</x:v>
       </x:c>
-      <x:c r="G28" s="10" t="str">
-        <x:v>Closed / final update</x:v>
-      </x:c>
-      <x:c r="H28" s="10" t="str">
-        <x:v>Maritime</x:v>
-      </x:c>
-      <x:c r="I28" s="10" t="str">
-        <x:v>Japan</x:v>
-      </x:c>
-      <x:c r="J28" s="10" t="str">
-        <x:v>~220 km northeast of Nosappu Cape</x:v>
-      </x:c>
-      <x:c r="K28" s="10" t="str">
-        <x:v>JCG foreign-vessel crew injury response</x:v>
-      </x:c>
-      <x:c r="L28" s="10" t="str">
-        <x:v>Japan Coast Guard reported a crew injury aboard a Marshall Islands-flagged cargo vessel and coordinated rescue activity in waters surrounding Japan.</x:v>
-      </x:c>
-      <x:c r="M28" s="10" t="str">
-        <x:v>SAR / medical response; foreign-vessel incident</x:v>
-      </x:c>
-      <x:c r="N28" s="10" t="str">
-        <x:v>Operational disruption to vessel; useful MARSEC casualty signal</x:v>
-      </x:c>
-      <x:c r="O28" s="10" t="str">
-        <x:v>High</x:v>
-      </x:c>
-      <x:c r="P28" s="10" t="str">
-        <x:v>SRC_JCG</x:v>
-      </x:c>
-      <x:c r="Q28" s="10" t="str">
-        <x:v>https://www.kaiho.mlit.go.jp/info/topics/rescueforeignvessels.html</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="29">
-      <x:c r="A29" s="10" t="str">
-        <x:v>EVT_SEC_002</x:v>
-      </x:c>
-      <x:c r="B29" s="10" t="str">
-        <x:v>2026-08-17</x:v>
-      </x:c>
-      <x:c r="C29" s="10" t="str">
-        <x:v>2026-08-18</x:v>
-      </x:c>
-      <x:c r="D29" s="10" t="str">
-        <x:v>Maritime Casualty</x:v>
-      </x:c>
-      <x:c r="E29" s="10" t="str">
-        <x:v>Grounding</x:v>
-      </x:c>
-      <x:c r="F29" s="10" t="str">
+      <x:c r="G29" t="str">
+        <x:v>Approved / pre-construction</x:v>
+      </x:c>
+      <x:c r="H29" t="str">
+        <x:v>Trade / Commercial</x:v>
+      </x:c>
+      <x:c r="I29" t="str">
+        <x:v>China</x:v>
+      </x:c>
+      <x:c r="J29" t="str">
+        <x:v>Xiangshan Port / Ningbo</x:v>
+      </x:c>
+      <x:c r="K29" t="str">
+        <x:v>Ningbo clears $223m offshore wind port development</x:v>
+      </x:c>
+      <x:c r="L29" t="str">
+        <x:v>Ningbo approved a RMB1.5bn ($223m) specialist port project at Xiangshan for offshore-wind component assembly and shipment.</x:v>
+      </x:c>
+      <x:c r="M29" t="str">
+        <x:v>New heavy-lift and ro-ro port capacity planned.</x:v>
+      </x:c>
+      <x:c r="N29" t="str">
+        <x:v>Expands Zhejiang's offshore-wind manufacturing and logistics chain.</x:v>
+      </x:c>
+      <x:c r="O29" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="P29" t="str">
+        <x:v>SRC260910_010</x:v>
+      </x:c>
+      <x:c r="Q29" t="str">
+        <x:v>https://splash247.com/ningbo-clears-223m-offshore-wind-port-development/</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30">
+      <x:c r="A30" t="str">
+        <x:v>EVT260910_011</x:v>
+      </x:c>
+      <x:c r="B30" t="str">
+        <x:v>2026-09-09</x:v>
+      </x:c>
+      <x:c r="C30"/>
+      <x:c r="D30" t="str">
+        <x:v>Infrastructure Investment</x:v>
+      </x:c>
+      <x:c r="E30" t="str">
+        <x:v>Port digitalisation assistance</x:v>
+      </x:c>
+      <x:c r="F30" t="str">
+        <x:v>Low</x:v>
+      </x:c>
+      <x:c r="G30" t="str">
+        <x:v>Proposed / approval pending</x:v>
+      </x:c>
+      <x:c r="H30" t="str">
+        <x:v>Trade / Commercial</x:v>
+      </x:c>
+      <x:c r="I30" t="str">
+        <x:v>Sri Lanka / United States</x:v>
+      </x:c>
+      <x:c r="J30" t="str">
+        <x:v>Port of Colombo</x:v>
+      </x:c>
+      <x:c r="K30" t="str">
+        <x:v>US lines up $15m for Colombo port digital upgrade</x:v>
+      </x:c>
+      <x:c r="L30" t="str">
+        <x:v>The U.S. is preparing a $15m assistance package for digital infrastructure at Colombo, subject to congressional approval.</x:v>
+      </x:c>
+      <x:c r="M30" t="str">
+        <x:v>Planned digital systems aim to improve turnaround and reduce waiting times.</x:v>
+      </x:c>
+      <x:c r="N30" t="str">
+        <x:v>Potential efficiency gains at a major Indian Ocean transshipment gateway.</x:v>
+      </x:c>
+      <x:c r="O30" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="P30" t="str">
+        <x:v>SRC260910_011</x:v>
+      </x:c>
+      <x:c r="Q30" t="str">
+        <x:v>https://splash247.com/us-lines-up-15m-for-colombo-port-digital-upgrade/</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31">
+      <x:c r="A31" t="str">
+        <x:v>EVT260910_012</x:v>
+      </x:c>
+      <x:c r="B31" t="str">
+        <x:v>2026-09-09</x:v>
+      </x:c>
+      <x:c r="C31"/>
+      <x:c r="D31" t="str">
+        <x:v>Infrastructure Investment</x:v>
+      </x:c>
+      <x:c r="E31" t="str">
+        <x:v>Road freight corridor upgrade</x:v>
+      </x:c>
+      <x:c r="F31" t="str">
+        <x:v>Low</x:v>
+      </x:c>
+      <x:c r="G31" t="str">
+        <x:v>Entering service</x:v>
+      </x:c>
+      <x:c r="H31" t="str">
+        <x:v>Trade / Commercial</x:v>
+      </x:c>
+      <x:c r="I31" t="str">
+        <x:v>Australia</x:v>
+      </x:c>
+      <x:c r="J31" t="str">
+        <x:v>Port of Newcastle / Hunter region</x:v>
+      </x:c>
+      <x:c r="K31" t="str">
+        <x:v>Newcastle gets $1.62bn freight access upgrade</x:v>
+      </x:c>
+      <x:c r="L31" t="str">
+        <x:v>The A$2.24bn ($1.62bn) M1 extension and Hexham Straight widening improve direct road access between Port of Newcastle and the Sydney-Brisbane freight corridor.</x:v>
+      </x:c>
+      <x:c r="M31" t="str">
+        <x:v>Road bottleneck reduction and more reliable port access.</x:v>
+      </x:c>
+      <x:c r="N31" t="str">
+        <x:v>Improves port-hinterland freight reliability and east-coast logistics connectivity.</x:v>
+      </x:c>
+      <x:c r="O31" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="P31" t="str">
+        <x:v>SRC260910_012</x:v>
+      </x:c>
+      <x:c r="Q31" t="str">
+        <x:v>https://splash247.com/newcastle-gets-1-62bn-freight-access-upgrade/</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32">
+      <x:c r="A32" t="str">
+        <x:v>EVT260910_013</x:v>
+      </x:c>
+      <x:c r="B32" t="str">
+        <x:v>2026-09-10</x:v>
+      </x:c>
+      <x:c r="C32"/>
+      <x:c r="D32" t="str">
+        <x:v>Port Development</x:v>
+      </x:c>
+      <x:c r="E32" t="str">
+        <x:v>On-dock grain transloading facility</x:v>
+      </x:c>
+      <x:c r="F32" t="str">
+        <x:v>Low</x:v>
+      </x:c>
+      <x:c r="G32" t="str">
+        <x:v>Opened / operational</x:v>
+      </x:c>
+      <x:c r="H32" t="str">
+        <x:v>Trade / Commercial</x:v>
+      </x:c>
+      <x:c r="I32" t="str">
+        <x:v>United States</x:v>
+      </x:c>
+      <x:c r="J32" t="str">
+        <x:v>Port of Baltimore / Seagirt</x:v>
+      </x:c>
+      <x:c r="K32" t="str">
+        <x:v>Baltimore adds on-dock grain export gateway</x:v>
+      </x:c>
+      <x:c r="L32" t="str">
+        <x:v>Ports America Chesapeake and Frey Commodities opened a four-acre on-dock grain transloading facility at Seagirt with three silos and direct container loading.</x:v>
+      </x:c>
+      <x:c r="M32" t="str">
+        <x:v>Direct farm-to-terminal grain handling removes an offsite stuffing step.</x:v>
+      </x:c>
+      <x:c r="N32" t="str">
+        <x:v>Reduces handling and truck moves while widening Baltimore's agricultural export catchment.</x:v>
+      </x:c>
+      <x:c r="O32" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="P32" t="str">
+        <x:v>SRC260910_013</x:v>
+      </x:c>
+      <x:c r="Q32" t="str">
+        <x:v>https://splash247.com/baltimore-adds-on-dock-grain-export-gateway/</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33">
+      <x:c r="A33" t="str">
+        <x:v>EVT260910_014</x:v>
+      </x:c>
+      <x:c r="B33" t="str">
+        <x:v>2026-09-09</x:v>
+      </x:c>
+      <x:c r="C33"/>
+      <x:c r="D33" t="str">
+        <x:v>Infrastructure Investment</x:v>
+      </x:c>
+      <x:c r="E33" t="str">
+        <x:v>Caspian port and logistics hub</x:v>
+      </x:c>
+      <x:c r="F33" t="str">
         <x:v>Medium</x:v>
       </x:c>
-      <x:c r="G29" s="10" t="str">
-        <x:v>Resolved / response</x:v>
-      </x:c>
-      <x:c r="H29" s="10" t="str">
-        <x:v>Maritime</x:v>
-      </x:c>
-      <x:c r="I29" s="10" t="str">
-        <x:v>South Korea</x:v>
-      </x:c>
-      <x:c r="J29" s="10" t="str">
-        <x:v>South of Jawoldo, Incheon</x:v>
-      </x:c>
-      <x:c r="K29" s="10" t="str">
-        <x:v>Fishing vessel grounded near Jawoldo</x:v>
-      </x:c>
-      <x:c r="L29" s="10" t="str">
-        <x:v>Incheon Coast Guard reported a 4.02-ton fishing vessel driven onto rocks by strong current; one skipper rescued after response assets were deployed.</x:v>
-      </x:c>
-      <x:c r="M29" s="10" t="str">
-        <x:v>Grounding; SAR deployment</x:v>
-      </x:c>
-      <x:c r="N29" s="10" t="str">
-        <x:v>Localised navigation/safety event; validates KCG incident ingestion</x:v>
-      </x:c>
-      <x:c r="O29" s="10" t="str">
-        <x:v>High</x:v>
-      </x:c>
-      <x:c r="P29" s="10" t="str">
-        <x:v>SRC_KCG</x:v>
-      </x:c>
-      <x:c r="Q29" s="10" t="str">
-        <x:v>https://kcg.go.kr/inchoncgs/na/ntt/selectNttInfo.do?mi=2084&amp;nttSn=71395</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="30">
-      <x:c r="A30" s="10" t="str">
-        <x:v>EVT_SEC_003</x:v>
-      </x:c>
-      <x:c r="B30" s="10" t="str">
-        <x:v>2025-05-24</x:v>
-      </x:c>
-      <x:c r="C30" s="10"/>
-      <x:c r="D30" s="10" t="str">
-        <x:v>Maritime Casualty / Pollution Risk</x:v>
-      </x:c>
-      <x:c r="E30" s="10" t="str">
-        <x:v>Loss of stability / distress</x:v>
-      </x:c>
-      <x:c r="F30" s="10" t="str">
-        <x:v>High</x:v>
-      </x:c>
-      <x:c r="G30" s="10" t="str">
-        <x:v>Historical / lessons retained</x:v>
-      </x:c>
-      <x:c r="H30" s="10" t="str">
-        <x:v>Maritime</x:v>
-      </x:c>
-      <x:c r="I30" s="10" t="str">
+      <x:c r="G33" t="str">
+        <x:v>Design / survey</x:v>
+      </x:c>
+      <x:c r="H33" t="str">
+        <x:v>Trade / Commercial</x:v>
+      </x:c>
+      <x:c r="I33" t="str">
+        <x:v>Kazakhstan</x:v>
+      </x:c>
+      <x:c r="J33" t="str">
+        <x:v>Mangystau / Kuryk area</x:v>
+      </x:c>
+      <x:c r="K33" t="str">
+        <x:v>Kazakhstan advances $1bn Caspian port hub</x:v>
+      </x:c>
+      <x:c r="L33" t="str">
+        <x:v>Kazakhstan is advancing a roughly $1bn Caspian port and logistics hub with seven berths, rail and road links, ferry infrastructure and shipbuilding/repair facilities.</x:v>
+      </x:c>
+      <x:c r="M33" t="str">
+        <x:v>Large multimodal port complex moves into design and survey stage.</x:v>
+      </x:c>
+      <x:c r="N33" t="str">
+        <x:v>Adds capacity to Kazakhstan's Middle Corridor and trans-Caspian logistics network.</x:v>
+      </x:c>
+      <x:c r="O33" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="P33" t="str">
+        <x:v>SRC260910_014</x:v>
+      </x:c>
+      <x:c r="Q33" t="str">
+        <x:v>https://splash247.com/kazakhstan-advances-1bn-caspian-port-hub/</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34">
+      <x:c r="A34" t="str">
+        <x:v>EVT260910_015</x:v>
+      </x:c>
+      <x:c r="B34" t="str">
+        <x:v>2026-09-09</x:v>
+      </x:c>
+      <x:c r="C34"/>
+      <x:c r="D34" t="str">
+        <x:v>Regulatory / Legal</x:v>
+      </x:c>
+      <x:c r="E34" t="str">
+        <x:v>Port expansion court ruling</x:v>
+      </x:c>
+      <x:c r="F34" t="str">
+        <x:v>Low</x:v>
+      </x:c>
+      <x:c r="G34" t="str">
+        <x:v>Project cleared to proceed</x:v>
+      </x:c>
+      <x:c r="H34" t="str">
+        <x:v>Trade / Commercial</x:v>
+      </x:c>
+      <x:c r="I34" t="str">
+        <x:v>Spain</x:v>
+      </x:c>
+      <x:c r="J34" t="str">
+        <x:v>Port of Valencia</x:v>
+      </x:c>
+      <x:c r="K34" t="str">
+        <x:v>Valencia north terminal survives environmental court challenge</x:v>
+      </x:c>
+      <x:c r="L34" t="str">
+        <x:v>A Spanish court rejected an environmental challenge to Valencia's planned north container terminal, leaving the existing project approval in place.</x:v>
+      </x:c>
+      <x:c r="M34" t="str">
+        <x:v>Removes a legal obstacle from the terminal project.</x:v>
+      </x:c>
+      <x:c r="N34" t="str">
+        <x:v>Supports progression of a terminal designed for nearly 4.8m TEU annual capacity under a 50-year TIL concession.</x:v>
+      </x:c>
+      <x:c r="O34" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="P34" t="str">
+        <x:v>SRC260910_015</x:v>
+      </x:c>
+      <x:c r="Q34" t="str">
+        <x:v>https://splash247.com/valencia-north-terminal-survives-environmental-court-challenge/</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35">
+      <x:c r="A35" t="str">
+        <x:v>EVT260910_016</x:v>
+      </x:c>
+      <x:c r="B35" t="str">
+        <x:v>2026-09-10</x:v>
+      </x:c>
+      <x:c r="C35"/>
+      <x:c r="D35" t="str">
+        <x:v>Port Development</x:v>
+      </x:c>
+      <x:c r="E35" t="str">
+        <x:v>Container-terminal equipment expansion</x:v>
+      </x:c>
+      <x:c r="F35" t="str">
+        <x:v>Low</x:v>
+      </x:c>
+      <x:c r="G35" t="str">
+        <x:v>Equipment commissioned / expansion ongoing</x:v>
+      </x:c>
+      <x:c r="H35" t="str">
+        <x:v>Trade / Commercial</x:v>
+      </x:c>
+      <x:c r="I35" t="str">
+        <x:v>Philippines</x:v>
+      </x:c>
+      <x:c r="J35" t="str">
+        <x:v>Manila South Harbour</x:v>
+      </x:c>
+      <x:c r="K35" t="str">
+        <x:v>Manila South Harbour advances terminal expansion</x:v>
+      </x:c>
+      <x:c r="L35" t="str">
+        <x:v>DP World and Asian Terminals commissioned six hybrid RTGs as Manila South Harbour continues a wider capacity and electrification programme.</x:v>
+      </x:c>
+      <x:c r="M35" t="str">
+        <x:v>Additional yard handling capacity and equipment modernisation.</x:v>
+      </x:c>
+      <x:c r="N35" t="str">
+        <x:v>Supports higher terminal throughput and lower-emission container operations.</x:v>
+      </x:c>
+      <x:c r="O35" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="P35" t="str">
+        <x:v>SRC260910_016</x:v>
+      </x:c>
+      <x:c r="Q35" t="str">
+        <x:v>https://splash247.com/manila-south-harbour-advances-terminal-expansion/</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36">
+      <x:c r="A36" t="str">
+        <x:v>EVT260910_017</x:v>
+      </x:c>
+      <x:c r="B36" t="str">
+        <x:v>2026-09-10</x:v>
+      </x:c>
+      <x:c r="C36"/>
+      <x:c r="D36" t="str">
+        <x:v>Infrastructure Investment</x:v>
+      </x:c>
+      <x:c r="E36" t="str">
+        <x:v>Industrial park joint venture</x:v>
+      </x:c>
+      <x:c r="F36" t="str">
+        <x:v>Medium</x:v>
+      </x:c>
+      <x:c r="G36" t="str">
+        <x:v>Shareholders agreement signed</x:v>
+      </x:c>
+      <x:c r="H36" t="str">
+        <x:v>Trade / Commercial</x:v>
+      </x:c>
+      <x:c r="I36" t="str">
+        <x:v>Kenya / United Arab Emirates</x:v>
+      </x:c>
+      <x:c r="J36" t="str">
+        <x:v>Mombasa, Kenya</x:v>
+      </x:c>
+      <x:c r="K36" t="str">
+        <x:v>DP World formalises Mombasa industrial park joint venture</x:v>
+      </x:c>
+      <x:c r="L36" t="str">
+        <x:v>DP World and GulfCap Africa formalised the joint venture for a 222-hectare special economic zone near the Port of Mombasa.</x:v>
+      </x:c>
+      <x:c r="M36" t="str">
+        <x:v>Project corporate structure established; first phase planned over 40 hectares.</x:v>
+      </x:c>
+      <x:c r="N36" t="str">
+        <x:v>Links industrial, warehousing and logistics capacity more closely with Mombasa port infrastructure.</x:v>
+      </x:c>
+      <x:c r="O36" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="P36" t="str">
+        <x:v>SRC260910_017</x:v>
+      </x:c>
+      <x:c r="Q36" t="str">
+        <x:v>https://splash247.com/dp-world-formalises-mombasa-industrial-park-joint-venture/</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37">
+      <x:c r="A37" t="str">
+        <x:v>EVT260910_018</x:v>
+      </x:c>
+      <x:c r="B37" t="str">
+        <x:v>2026-09-10</x:v>
+      </x:c>
+      <x:c r="C37"/>
+      <x:c r="D37" t="str">
+        <x:v>Infrastructure Investment</x:v>
+      </x:c>
+      <x:c r="E37" t="str">
+        <x:v>Dry-bulk berth concession</x:v>
+      </x:c>
+      <x:c r="F37" t="str">
+        <x:v>Medium</x:v>
+      </x:c>
+      <x:c r="G37" t="str">
+        <x:v>Letter of award / development</x:v>
+      </x:c>
+      <x:c r="H37" t="str">
+        <x:v>Trade / Commercial</x:v>
+      </x:c>
+      <x:c r="I37" t="str">
         <x:v>India</x:v>
       </x:c>
-      <x:c r="J30" s="10" t="str">
-        <x:v>~38 nm southwest of Kochi, Kerala</x:v>
-      </x:c>
-      <x:c r="K30" s="10" t="str">
-        <x:v>MSC Elsa 3 casualty and ICG response</x:v>
-      </x:c>
-      <x:c r="L30" s="10" t="str">
-        <x:v>Indian Coast Guard records describe MSC Elsa 3 developing a severe list southwest of Kochi, triggering SAR, firefighting, salvage coordination and pollution-response monitoring.</x:v>
-      </x:c>
-      <x:c r="M30" s="10" t="str">
-        <x:v>Crew rescue; salvage; fire/pollution response</x:v>
-      </x:c>
-      <x:c r="N30" s="10" t="str">
-        <x:v>Containerised cargo and coastal pollution exposure; useful India MARSEC case record</x:v>
-      </x:c>
-      <x:c r="O30" s="10" t="str">
-        <x:v>High</x:v>
-      </x:c>
-      <x:c r="P30" s="10" t="str">
-        <x:v>SRC_ICG</x:v>
-      </x:c>
-      <x:c r="Q30" s="10" t="str">
-        <x:v>https://www.indiancoastguard.gov.in/other-assistance</x:v>
+      <x:c r="J37" t="str">
+        <x:v>Paradip Port</x:v>
+      </x:c>
+      <x:c r="K37" t="str">
+        <x:v>Adani lands 30-year Paradip berth concession</x:v>
+      </x:c>
+      <x:c r="L37" t="str">
+        <x:v>Adani Ports secured a 30-year BOT concession to develop and operate two dry-bulk berths at Paradip, adding 18m tonnes of annual mechanised capacity.</x:v>
+      </x:c>
+      <x:c r="M37" t="str">
+        <x:v>New mechanised berth and storage infrastructure planned.</x:v>
+      </x:c>
+      <x:c r="N37" t="str">
+        <x:v>Expands APSEZ's east-coast network and dry-bulk handling capacity.</x:v>
+      </x:c>
+      <x:c r="O37" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="P37" t="str">
+        <x:v>SRC260910_018</x:v>
+      </x:c>
+      <x:c r="Q37" t="str">
+        <x:v>https://splash247.com/adani-lands-30-year-paradip-berth-concession/</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38">
+      <x:c r="A38" t="str">
+        <x:v>EVT260910_019</x:v>
+      </x:c>
+      <x:c r="B38" t="str">
+        <x:v>2026-09-10</x:v>
+      </x:c>
+      <x:c r="C38"/>
+      <x:c r="D38" t="str">
+        <x:v>Contract / Charter</x:v>
+      </x:c>
+      <x:c r="E38" t="str">
+        <x:v>Offshore drilling contract</x:v>
+      </x:c>
+      <x:c r="F38" t="str">
+        <x:v>Medium</x:v>
+      </x:c>
+      <x:c r="G38" t="str">
+        <x:v>Letter of award</x:v>
+      </x:c>
+      <x:c r="H38" t="str">
+        <x:v>Trade / Commercial</x:v>
+      </x:c>
+      <x:c r="I38" t="str">
+        <x:v>Norway</x:v>
+      </x:c>
+      <x:c r="J38" t="str">
+        <x:v>Norwegian offshore sector</x:v>
+      </x:c>
+      <x:c r="K38" t="str">
+        <x:v>Odfjell Drilling lands $518m semisub deal with Vår Energi</x:v>
+      </x:c>
+      <x:c r="L38" t="str">
+        <x:v>Vår Energi awarded Odfjell Drilling a three-year contract for Deepsea Bergen starting in early 2028, with firm backlog valued at about $518m.</x:v>
+      </x:c>
+      <x:c r="M38" t="str">
+        <x:v>Extends rig employment through the first quarter of 2031.</x:v>
+      </x:c>
+      <x:c r="N38" t="str">
+        <x:v>Adds long-duration offshore drilling backlog and earnings visibility.</x:v>
+      </x:c>
+      <x:c r="O38" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="P38" t="str">
+        <x:v>SRC260910_019</x:v>
+      </x:c>
+      <x:c r="Q38" t="str">
+        <x:v>https://splash247.com/odfjell-drilling-lands-518m-semisub-deal-with-var-energi/</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39">
+      <x:c r="A39" t="str">
+        <x:v>EVT260910_020</x:v>
+      </x:c>
+      <x:c r="B39" t="str">
+        <x:v>2026-09-10</x:v>
+      </x:c>
+      <x:c r="C39"/>
+      <x:c r="D39" t="str">
+        <x:v>Corporate / Legal</x:v>
+      </x:c>
+      <x:c r="E39" t="str">
+        <x:v>Fraud charges linked to charter rates</x:v>
+      </x:c>
+      <x:c r="F39" t="str">
+        <x:v>Medium</x:v>
+      </x:c>
+      <x:c r="G39" t="str">
+        <x:v>Court proceedings</x:v>
+      </x:c>
+      <x:c r="H39" t="str">
+        <x:v>Trade / Commercial</x:v>
+      </x:c>
+      <x:c r="I39" t="str">
+        <x:v>Malaysia</x:v>
+      </x:c>
+      <x:c r="J39" t="str">
+        <x:v>Malaysia</x:v>
+      </x:c>
+      <x:c r="K39" t="str">
+        <x:v>Alam Maritim head faces fraud charges tied to vessel rates</x:v>
+      </x:c>
+      <x:c r="L39" t="str">
+        <x:v>Alam Maritim Resources CEO Azmi Ahmad was charged with two counts of fraud linked to alleged discrepancies between offshore-vessel work-order and BIMCO charter rates.</x:v>
+      </x:c>
+      <x:c r="M39" t="str">
+        <x:v>Management/legal proceedings; no immediate fleet outage reported.</x:v>
+      </x:c>
+      <x:c r="N39" t="str">
+        <x:v>Governance and counterparty risk for Alam Maritim's offshore-vessel business.</x:v>
+      </x:c>
+      <x:c r="O39" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="P39" t="str">
+        <x:v>SRC260910_020</x:v>
+      </x:c>
+      <x:c r="Q39" t="str">
+        <x:v>https://splash247.com/alam-maritim-head-faces-fraud-charges-tied-to-vessel-rates/</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40">
+      <x:c r="A40" t="str">
+        <x:v>EVT260910_021</x:v>
+      </x:c>
+      <x:c r="B40" t="str">
+        <x:v>2026-09-10</x:v>
+      </x:c>
+      <x:c r="C40"/>
+      <x:c r="D40" t="str">
+        <x:v>Fleet Investment</x:v>
+      </x:c>
+      <x:c r="E40" t="str">
+        <x:v>Tanker acquisition and charter</x:v>
+      </x:c>
+      <x:c r="F40" t="str">
+        <x:v>Medium</x:v>
+      </x:c>
+      <x:c r="G40" t="str">
+        <x:v>Acquired / delivery pending</x:v>
+      </x:c>
+      <x:c r="H40" t="str">
+        <x:v>Trade / Commercial</x:v>
+      </x:c>
+      <x:c r="I40" t="str">
+        <x:v>Germany / China / Global</x:v>
+      </x:c>
+      <x:c r="J40" t="str">
+        <x:v>Wuhu Shipyard / Great Lakes deployment</x:v>
+      </x:c>
+      <x:c r="K40" t="str">
+        <x:v>Ernst Russ doubles down on tankers with Cargill-backed pair</x:v>
+      </x:c>
+      <x:c r="L40" t="str">
+        <x:v>Ernst Russ acquired two more 18,500 dwt chemical/product tanker newbuildings and fixed both to Cargill for at least three years.</x:v>
+      </x:c>
+      <x:c r="M40" t="str">
+        <x:v>Two additional tanker deliveries expand the fleet to six vessels.</x:v>
+      </x:c>
+      <x:c r="N40" t="str">
+        <x:v>Adds about $38.3m to charter backlog and increases Great Lakes-capable tanker exposure.</x:v>
+      </x:c>
+      <x:c r="O40" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="P40" t="str">
+        <x:v>SRC260910_021</x:v>
+      </x:c>
+      <x:c r="Q40" t="str">
+        <x:v>https://splash247.com/ernst-russ-doubles-down-on-tankers-with-cargill-backed-pair/</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41">
+      <x:c r="A41" t="str">
+        <x:v>EVT260910_022</x:v>
+      </x:c>
+      <x:c r="B41" t="str">
+        <x:v>2026-09-10</x:v>
+      </x:c>
+      <x:c r="C41"/>
+      <x:c r="D41" t="str">
+        <x:v>Corporate / Legal</x:v>
+      </x:c>
+      <x:c r="E41" t="str">
+        <x:v>FMC commercial dispute</x:v>
+      </x:c>
+      <x:c r="F41" t="str">
+        <x:v>Medium</x:v>
+      </x:c>
+      <x:c r="G41" t="str">
+        <x:v>Proceedings ongoing</x:v>
+      </x:c>
+      <x:c r="H41" t="str">
+        <x:v>Trade / Commercial</x:v>
+      </x:c>
+      <x:c r="I41" t="str">
+        <x:v>United States / France</x:v>
+      </x:c>
+      <x:c r="J41" t="str">
+        <x:v>United States</x:v>
+      </x:c>
+      <x:c r="K41" t="str">
+        <x:v>CMA CGM says it met obligations in $186m Samsung dispute</x:v>
+      </x:c>
+      <x:c r="L41" t="str">
+        <x:v>CMA CGM rejected Samsung Electronics America's allegations in a $186m FMC complaint over pandemic-era store-door shipments, demurrage, detention and inland transport.</x:v>
+      </x:c>
+      <x:c r="M41" t="str">
+        <x:v>Administrative proceedings continue; no operational shutdown reported.</x:v>
+      </x:c>
+      <x:c r="N41" t="str">
+        <x:v>Potential financial, regulatory and precedent risk for carrier inland-transport and charge practices.</x:v>
+      </x:c>
+      <x:c r="O41" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="P41" t="str">
+        <x:v>SRC260910_022</x:v>
+      </x:c>
+      <x:c r="Q41" t="str">
+        <x:v>https://splash247.com/cma-cgm-says-it-met-obligations-in-186m-samsung-dispute/</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="42">
+      <x:c r="A42" t="str">
+        <x:v>EVT260910_023</x:v>
+      </x:c>
+      <x:c r="B42" t="str">
+        <x:v>2026-09-10</x:v>
+      </x:c>
+      <x:c r="C42"/>
+      <x:c r="D42" t="str">
+        <x:v>Capital Markets</x:v>
+      </x:c>
+      <x:c r="E42" t="str">
+        <x:v>Equity / capital raise</x:v>
+      </x:c>
+      <x:c r="F42" t="str">
+        <x:v>Low</x:v>
+      </x:c>
+      <x:c r="G42" t="str">
+        <x:v>Announced</x:v>
+      </x:c>
+      <x:c r="H42" t="str">
+        <x:v>Trade / Commercial</x:v>
+      </x:c>
+      <x:c r="I42" t="str">
+        <x:v>Global</x:v>
+      </x:c>
+      <x:c r="J42" t="str">
+        <x:v>Global</x:v>
+      </x:c>
+      <x:c r="K42" t="str">
+        <x:v>Safe Bulkers raises $94m for fleet push</x:v>
+      </x:c>
+      <x:c r="L42" t="str">
+        <x:v>Safe Bulkers announced a roughly $94m capital raise to support further fleet investment.</x:v>
+      </x:c>
+      <x:c r="M42" t="str">
+        <x:v>Additional financing capacity for fleet programme.</x:v>
+      </x:c>
+      <x:c r="N42" t="str">
+        <x:v>Supports vessel acquisitions/newbuilds and balance-sheet funding for fleet growth.</x:v>
+      </x:c>
+      <x:c r="O42" t="str">
+        <x:v>Medium</x:v>
+      </x:c>
+      <x:c r="P42" t="str">
+        <x:v>SRC260910_023</x:v>
+      </x:c>
+      <x:c r="Q42" t="str">
+        <x:v>https://splash247.com/safe-bulkers-raises-94m-for-fleet-push/</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="43">
+      <x:c r="A43" t="str">
+        <x:v>EVT260910_024</x:v>
+      </x:c>
+      <x:c r="B43" t="str">
+        <x:v>2026-09-10</x:v>
+      </x:c>
+      <x:c r="C43"/>
+      <x:c r="D43" t="str">
+        <x:v>Conflict / Security</x:v>
+      </x:c>
+      <x:c r="E43" t="str">
+        <x:v>Escalating attacks on shipping</x:v>
+      </x:c>
+      <x:c r="F43" t="str">
+        <x:v>Critical</x:v>
+      </x:c>
+      <x:c r="G43" t="str">
+        <x:v>Active / developing</x:v>
+      </x:c>
+      <x:c r="H43" t="str">
+        <x:v>Security / Maritime</x:v>
+      </x:c>
+      <x:c r="I43" t="str">
+        <x:v>Iran / Iraq / UAE / United States</x:v>
+      </x:c>
+      <x:c r="J43" t="str">
+        <x:v>Strait of Hormuz / northern Gulf / Gulf of Oman</x:v>
+      </x:c>
+      <x:c r="K43" t="str">
+        <x:v>Hormuz attacks reach wartime high</x:v>
+      </x:c>
+      <x:c r="L43" t="str">
+        <x:v>The U.S.-Iran conflict produced the largest wave of tanker attacks since hostilities began, with merchant casualties, tanker strikes and widening threats to shipping.</x:v>
+      </x:c>
+      <x:c r="M43" t="str">
+        <x:v>Merchant vessels struck or disabled; one seafarer killed aboard Hercules Star; tanker traffic faces acute threat exposure.</x:v>
+      </x:c>
+      <x:c r="N43" t="str">
+        <x:v>War-risk costs, tanker availability and Gulf energy flows face severe disruption risk.</x:v>
+      </x:c>
+      <x:c r="O43" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="P43" t="str">
+        <x:v>SRC260910_024</x:v>
+      </x:c>
+      <x:c r="Q43" t="str">
+        <x:v>https://splash247.com/hormuz-attacks-reach-wartime-high/</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="44">
+      <x:c r="A44" t="str">
+        <x:v>EVT260910_025</x:v>
+      </x:c>
+      <x:c r="B44" t="str">
+        <x:v>2026-09-10</x:v>
+      </x:c>
+      <x:c r="C44"/>
+      <x:c r="D44" t="str">
+        <x:v>Conflict / Security</x:v>
+      </x:c>
+      <x:c r="E44" t="str">
+        <x:v>Explosions / strike activity near coastal and military infrastructure</x:v>
+      </x:c>
+      <x:c r="F44" t="str">
+        <x:v>Critical</x:v>
+      </x:c>
+      <x:c r="G44" t="str">
+        <x:v>Active / developing</x:v>
+      </x:c>
+      <x:c r="H44" t="str">
+        <x:v>Security / Maritime / Energy</x:v>
+      </x:c>
+      <x:c r="I44" t="str">
+        <x:v>Iran / Saudi Arabia</x:v>
+      </x:c>
+      <x:c r="J44" t="str">
+        <x:v>Hormozgan coast / Qeshm / Sirik / Minab / Taif</x:v>
+      </x:c>
+      <x:c r="K44" t="str">
+        <x:v>Multiple explosions reported across Iran's Hormozgan coast and near Taif, Saudi Arabia</x:v>
+      </x:c>
+      <x:c r="L44" t="str">
+        <x:v>Iranian state media reported blasts at Qeshm Island, Sirik and Minab in Hormozgan province, while explosions were also reported near King Fahd Air Base and Taif in Saudi Arabia. Authorities in Hormozgan said sounds over Qeshm appeared to originate from the sea.</x:v>
+      </x:c>
+      <x:c r="M44" t="str">
+        <x:v>Escalation across the Hormuz coastal operating area; possible exposure of coastal, military and maritime infrastructure.</x:v>
+      </x:c>
+      <x:c r="N44" t="str">
+        <x:v>Higher Gulf war-risk exposure, stronger oil-price pressure and increased uncertainty for Hormuz shipping and regional energy flows.</x:v>
+      </x:c>
+      <x:c r="O44" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="P44" t="str">
+        <x:v>SRC260910_025</x:v>
+      </x:c>
+      <x:c r="Q44" t="str">
+        <x:v>https://gulfnews.com/world/mena/iran-rocked-by-explosions-as-trump-says-us-iran-war-wont-end-until-after-midterm-elections-1.500669266</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="45">
+      <x:c r="A45" t="str">
+        <x:v>EVT260910_026</x:v>
+      </x:c>
+      <x:c r="B45" t="str">
+        <x:v>2026-06-05</x:v>
+      </x:c>
+      <x:c r="C45"/>
+      <x:c r="D45" t="str">
+        <x:v>Conflict / Security</x:v>
+      </x:c>
+      <x:c r="E45" t="str">
+        <x:v>Drone attack on merchant cargo vessels</x:v>
+      </x:c>
+      <x:c r="F45" t="str">
+        <x:v>Critical</x:v>
+      </x:c>
+      <x:c r="G45" t="str">
+        <x:v>Completed / monitoring</x:v>
+      </x:c>
+      <x:c r="H45" t="str">
+        <x:v>Security / Maritime</x:v>
+      </x:c>
+      <x:c r="I45" t="str">
+        <x:v>Russia / Azerbaijan</x:v>
+      </x:c>
+      <x:c r="J45" t="str">
+        <x:v>Sea of Azov / Taganrog Bay / Mariupol-Berdyansk approaches</x:v>
+      </x:c>
+      <x:c r="K45" t="str">
+        <x:v>Drone attacks hit cargo vessels Natra and Zirkon in the Sea of Azov</x:v>
+      </x:c>
+      <x:c r="L45" t="str">
+        <x:v>Drone attacks struck the Palau-flagged cargo vessels Natra and Zirkon in the Sea of Azov. Azerbaijani authorities later confirmed four Azerbaijani citizens killed and four injured among 25 Azerbaijani crew members across the two vessels.</x:v>
+      </x:c>
+      <x:c r="M45" t="str">
+        <x:v>Fatal merchant-vessel attack; vessel damage; search, rescue and recovery operations required.</x:v>
+      </x:c>
+      <x:c r="N45" t="str">
+        <x:v>Demonstrates direct risk to civilian shipping in the Sea of Azov/Black Sea conflict environment and raises crew-safety and war-risk exposure.</x:v>
+      </x:c>
+      <x:c r="O45" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="P45" t="str">
+        <x:v>SRC260910_026</x:v>
+      </x:c>
+      <x:c r="Q45" t="str">
+        <x:v>https://oc-media.org/two-azerbaijani-citizens-killed-in-drone-attack-on-cargo-ship-in-black-sea/</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="46">
+      <x:c r="A46" t="str">
+        <x:v>EVT260910_027</x:v>
+      </x:c>
+      <x:c r="B46" t="str">
+        <x:v>2026-09-09</x:v>
+      </x:c>
+      <x:c r="C46"/>
+      <x:c r="D46" t="str">
+        <x:v>Conflict / Security</x:v>
+      </x:c>
+      <x:c r="E46" t="str">
+        <x:v>Drone strike on port / oil-export infrastructure</x:v>
+      </x:c>
+      <x:c r="F46" t="str">
+        <x:v>Critical</x:v>
+      </x:c>
+      <x:c r="G46" t="str">
+        <x:v>Active / developing</x:v>
+      </x:c>
+      <x:c r="H46" t="str">
+        <x:v>Security / Maritime / Energy</x:v>
+      </x:c>
+      <x:c r="I46" t="str">
+        <x:v>Russia / Ukraine</x:v>
+      </x:c>
+      <x:c r="J46" t="str">
+        <x:v>Novorossiysk, Black Sea</x:v>
+      </x:c>
+      <x:c r="K46" t="str">
+        <x:v>Ukraine targets Novorossiysk oil-export hub</x:v>
+      </x:c>
+      <x:c r="L46" t="str">
+        <x:v>Ukrainian drones struck infrastructure in and near Novorossiysk. Reporting cited four civilian deaths, damage to civil infrastructure, and a fire at a fuel-oil terminal; Ukrainian forces also said they struck the naval base.</x:v>
+      </x:c>
+      <x:c r="M46" t="str">
+        <x:v>Port and fuel-terminal damage; potential disruption to oil-export and naval operations.</x:v>
+      </x:c>
+      <x:c r="N46" t="str">
+        <x:v>Novorossiysk is a key Black Sea export hub; disruption can affect Russian crude/product flows and nearby CPC loadings carrying the majority of Kazakhstan's crude exports.</x:v>
+      </x:c>
+      <x:c r="O46" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="P46" t="str">
+        <x:v>SRC260910_027</x:v>
+      </x:c>
+      <x:c r="Q46" t="str">
+        <x:v>https://oilprice.com/Latest-Energy-News/World-News/Ukraine-Targets-Russias-Key-Black-Sea-Oil-Port.html</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -2541,69 +3358,691 @@
       </x:c>
     </x:row>
     <x:row r="20">
-      <x:c r="A20" s="10" t="str">
-        <x:v>LOC_SEC_001</x:v>
-      </x:c>
-      <x:c r="B20" s="10" t="str">
-        <x:v>EVT_SEC_001</x:v>
-      </x:c>
-      <x:c r="C20" s="10" t="str">
-        <x:v>Waters northeast of Nosappu Cape</x:v>
-      </x:c>
-      <x:c r="D20" s="10" t="str">
-        <x:v>Japan</x:v>
-      </x:c>
-      <x:c r="E20" s="10"/>
-      <x:c r="F20" s="10"/>
-      <x:c r="G20" s="10" t="str">
-        <x:v>Regional / official description</x:v>
-      </x:c>
-      <x:c r="H20" s="10" t="str">
-        <x:v>Approx. 220 km northeast of cape; retain official wording until coordinates parsed.</x:v>
+      <x:c r="A20" t="str">
+        <x:v>LOC260910_001</x:v>
+      </x:c>
+      <x:c r="B20" t="str">
+        <x:v>EVT260910_001</x:v>
+      </x:c>
+      <x:c r="C20" t="str">
+        <x:v>Jazan Refinery / Jazan</x:v>
+      </x:c>
+      <x:c r="D20" t="str">
+        <x:v>Saudi Arabia</x:v>
+      </x:c>
+      <x:c r="E20" t="n">
+        <x:v>16.889</x:v>
+      </x:c>
+      <x:c r="F20" t="n">
+        <x:v>42.551</x:v>
+      </x:c>
+      <x:c r="G20" t="str">
+        <x:v>Mapped location / approximate refinery-area coordinate</x:v>
+      </x:c>
+      <x:c r="H20" t="str">
+        <x:v>Mapped for Regional Security. Marker represents the Jazan refinery-area location for the Houthi attack event.</x:v>
       </x:c>
     </x:row>
     <x:row r="21">
-      <x:c r="A21" s="10" t="str">
-        <x:v>LOC_SEC_002</x:v>
-      </x:c>
-      <x:c r="B21" s="10" t="str">
-        <x:v>EVT_SEC_002</x:v>
-      </x:c>
-      <x:c r="C21" s="10" t="str">
-        <x:v>South of Jawoldo, Ongjin-gun, Incheon</x:v>
-      </x:c>
-      <x:c r="D21" s="10" t="str">
+      <x:c r="A21" t="str">
+        <x:v>LOC260910_002</x:v>
+      </x:c>
+      <x:c r="B21" t="str">
+        <x:v>EVT260910_002</x:v>
+      </x:c>
+      <x:c r="C21" t="str">
+        <x:v>Eastern Pacific off Ecuador</x:v>
+      </x:c>
+      <x:c r="D21" t="str">
+        <x:v>Ecuador</x:v>
+      </x:c>
+      <x:c r="E21"/>
+      <x:c r="F21"/>
+      <x:c r="G21" t="str">
+        <x:v>Named location / no exact coordinates</x:v>
+      </x:c>
+      <x:c r="H21" t="str">
+        <x:v>Location retained for event context; not plotted unless coordinates are available.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22">
+      <x:c r="A22" t="str">
+        <x:v>LOC260910_003</x:v>
+      </x:c>
+      <x:c r="B22" t="str">
+        <x:v>EVT260910_003</x:v>
+      </x:c>
+      <x:c r="C22" t="str">
+        <x:v>Kochi, India</x:v>
+      </x:c>
+      <x:c r="D22" t="str">
+        <x:v>India</x:v>
+      </x:c>
+      <x:c r="E22"/>
+      <x:c r="F22"/>
+      <x:c r="G22" t="str">
+        <x:v>Named location / no exact coordinates</x:v>
+      </x:c>
+      <x:c r="H22" t="str">
+        <x:v>Location retained for event context; not plotted unless coordinates are available.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23">
+      <x:c r="A23" t="str">
+        <x:v>LOC260910_004</x:v>
+      </x:c>
+      <x:c r="B23" t="str">
+        <x:v>EVT260910_004</x:v>
+      </x:c>
+      <x:c r="C23" t="str">
+        <x:v>Gulf of Oman / approaches to Kharg Island</x:v>
+      </x:c>
+      <x:c r="D23" t="str">
+        <x:v>Iran</x:v>
+      </x:c>
+      <x:c r="E23"/>
+      <x:c r="F23"/>
+      <x:c r="G23" t="str">
+        <x:v>Named location / no exact coordinates</x:v>
+      </x:c>
+      <x:c r="H23" t="str">
+        <x:v>Location retained for event context; not plotted unless coordinates are available.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24">
+      <x:c r="A24" t="str">
+        <x:v>LOC260910_005</x:v>
+      </x:c>
+      <x:c r="B24" t="str">
+        <x:v>EVT260910_005</x:v>
+      </x:c>
+      <x:c r="C24" t="str">
+        <x:v>Global iron-ore trade</x:v>
+      </x:c>
+      <x:c r="D24" t="str">
         <x:v>South Korea</x:v>
       </x:c>
-      <x:c r="E21" s="10"/>
-      <x:c r="F21" s="10"/>
-      <x:c r="G21" s="10" t="str">
-        <x:v>Local / official description</x:v>
-      </x:c>
-      <x:c r="H21" s="10" t="str">
-        <x:v>Reported approx. 0.2 nm south of Jawoldo.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="22">
-      <x:c r="A22" s="10" t="str">
-        <x:v>LOC_SEC_003</x:v>
-      </x:c>
-      <x:c r="B22" s="10" t="str">
-        <x:v>EVT_SEC_003</x:v>
-      </x:c>
-      <x:c r="C22" s="10" t="str">
-        <x:v>Southwest of Kochi, Kerala</x:v>
-      </x:c>
-      <x:c r="D22" s="10" t="str">
+      <x:c r="E24"/>
+      <x:c r="F24"/>
+      <x:c r="G24" t="str">
+        <x:v>Named location / no exact coordinates</x:v>
+      </x:c>
+      <x:c r="H24" t="str">
+        <x:v>Location retained for event context; not plotted unless coordinates are available.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25">
+      <x:c r="A25" t="str">
+        <x:v>LOC260910_006</x:v>
+      </x:c>
+      <x:c r="B25" t="str">
+        <x:v>EVT260910_006</x:v>
+      </x:c>
+      <x:c r="C25" t="str">
+        <x:v>Strait of Hormuz / Gulf of Oman</x:v>
+      </x:c>
+      <x:c r="D25" t="str">
+        <x:v>Iran</x:v>
+      </x:c>
+      <x:c r="E25"/>
+      <x:c r="F25"/>
+      <x:c r="G25" t="str">
+        <x:v>Named location / no exact coordinates</x:v>
+      </x:c>
+      <x:c r="H25" t="str">
+        <x:v>Location retained for event context; not plotted unless coordinates are available.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26">
+      <x:c r="A26" t="str">
+        <x:v>LOC260910_007</x:v>
+      </x:c>
+      <x:c r="B26" t="str">
+        <x:v>EVT260910_007</x:v>
+      </x:c>
+      <x:c r="C26" t="str">
+        <x:v>Austal USA</x:v>
+      </x:c>
+      <x:c r="D26" t="str">
+        <x:v>United States</x:v>
+      </x:c>
+      <x:c r="E26"/>
+      <x:c r="F26"/>
+      <x:c r="G26" t="str">
+        <x:v>Named location / no exact coordinates</x:v>
+      </x:c>
+      <x:c r="H26" t="str">
+        <x:v>Location retained for event context; not plotted unless coordinates are available.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27">
+      <x:c r="A27" t="str">
+        <x:v>LOC260910_008</x:v>
+      </x:c>
+      <x:c r="B27" t="str">
+        <x:v>EVT260910_008</x:v>
+      </x:c>
+      <x:c r="C27" t="str">
+        <x:v>Morebaya port</x:v>
+      </x:c>
+      <x:c r="D27" t="str">
+        <x:v>Guinea</x:v>
+      </x:c>
+      <x:c r="E27"/>
+      <x:c r="F27"/>
+      <x:c r="G27" t="str">
+        <x:v>Named location / no exact coordinates</x:v>
+      </x:c>
+      <x:c r="H27" t="str">
+        <x:v>Location retained for event context; not plotted unless coordinates are available.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28">
+      <x:c r="A28" t="str">
+        <x:v>LOC260910_009</x:v>
+      </x:c>
+      <x:c r="B28" t="str">
+        <x:v>EVT260910_009</x:v>
+      </x:c>
+      <x:c r="C28" t="str">
+        <x:v>Port of Songkhla</x:v>
+      </x:c>
+      <x:c r="D28" t="str">
+        <x:v>Thailand</x:v>
+      </x:c>
+      <x:c r="E28"/>
+      <x:c r="F28"/>
+      <x:c r="G28" t="str">
+        <x:v>Named location / no exact coordinates</x:v>
+      </x:c>
+      <x:c r="H28" t="str">
+        <x:v>Location retained for event context; not plotted unless coordinates are available.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29">
+      <x:c r="A29" t="str">
+        <x:v>LOC260910_010</x:v>
+      </x:c>
+      <x:c r="B29" t="str">
+        <x:v>EVT260910_010</x:v>
+      </x:c>
+      <x:c r="C29" t="str">
+        <x:v>Xiangshan Port / Ningbo</x:v>
+      </x:c>
+      <x:c r="D29" t="str">
+        <x:v>China</x:v>
+      </x:c>
+      <x:c r="E29"/>
+      <x:c r="F29"/>
+      <x:c r="G29" t="str">
+        <x:v>Named location / no exact coordinates</x:v>
+      </x:c>
+      <x:c r="H29" t="str">
+        <x:v>Location retained for event context; not plotted unless coordinates are available.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30">
+      <x:c r="A30" t="str">
+        <x:v>LOC260910_011</x:v>
+      </x:c>
+      <x:c r="B30" t="str">
+        <x:v>EVT260910_011</x:v>
+      </x:c>
+      <x:c r="C30" t="str">
+        <x:v>Port of Colombo</x:v>
+      </x:c>
+      <x:c r="D30" t="str">
+        <x:v>Sri Lanka</x:v>
+      </x:c>
+      <x:c r="E30"/>
+      <x:c r="F30"/>
+      <x:c r="G30" t="str">
+        <x:v>Named location / no exact coordinates</x:v>
+      </x:c>
+      <x:c r="H30" t="str">
+        <x:v>Location retained for event context; not plotted unless coordinates are available.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31">
+      <x:c r="A31" t="str">
+        <x:v>LOC260910_012</x:v>
+      </x:c>
+      <x:c r="B31" t="str">
+        <x:v>EVT260910_012</x:v>
+      </x:c>
+      <x:c r="C31" t="str">
+        <x:v>Port of Newcastle / Hunter region</x:v>
+      </x:c>
+      <x:c r="D31" t="str">
+        <x:v>Australia</x:v>
+      </x:c>
+      <x:c r="E31"/>
+      <x:c r="F31"/>
+      <x:c r="G31" t="str">
+        <x:v>Named location / no exact coordinates</x:v>
+      </x:c>
+      <x:c r="H31" t="str">
+        <x:v>Location retained for event context; not plotted unless coordinates are available.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32">
+      <x:c r="A32" t="str">
+        <x:v>LOC260910_013</x:v>
+      </x:c>
+      <x:c r="B32" t="str">
+        <x:v>EVT260910_013</x:v>
+      </x:c>
+      <x:c r="C32" t="str">
+        <x:v>Port of Baltimore / Seagirt</x:v>
+      </x:c>
+      <x:c r="D32" t="str">
+        <x:v>United States</x:v>
+      </x:c>
+      <x:c r="E32"/>
+      <x:c r="F32"/>
+      <x:c r="G32" t="str">
+        <x:v>Named location / no exact coordinates</x:v>
+      </x:c>
+      <x:c r="H32" t="str">
+        <x:v>Location retained for event context; not plotted unless coordinates are available.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33">
+      <x:c r="A33" t="str">
+        <x:v>LOC260910_014</x:v>
+      </x:c>
+      <x:c r="B33" t="str">
+        <x:v>EVT260910_014</x:v>
+      </x:c>
+      <x:c r="C33" t="str">
+        <x:v>Mangystau / Kuryk area</x:v>
+      </x:c>
+      <x:c r="D33" t="str">
+        <x:v>Kazakhstan</x:v>
+      </x:c>
+      <x:c r="E33"/>
+      <x:c r="F33"/>
+      <x:c r="G33" t="str">
+        <x:v>Named location / no exact coordinates</x:v>
+      </x:c>
+      <x:c r="H33" t="str">
+        <x:v>Location retained for event context; not plotted unless coordinates are available.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34">
+      <x:c r="A34" t="str">
+        <x:v>LOC260910_015</x:v>
+      </x:c>
+      <x:c r="B34" t="str">
+        <x:v>EVT260910_015</x:v>
+      </x:c>
+      <x:c r="C34" t="str">
+        <x:v>Port of Valencia</x:v>
+      </x:c>
+      <x:c r="D34" t="str">
+        <x:v>Spain</x:v>
+      </x:c>
+      <x:c r="E34"/>
+      <x:c r="F34"/>
+      <x:c r="G34" t="str">
+        <x:v>Named location / no exact coordinates</x:v>
+      </x:c>
+      <x:c r="H34" t="str">
+        <x:v>Location retained for event context; not plotted unless coordinates are available.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35">
+      <x:c r="A35" t="str">
+        <x:v>LOC260910_016</x:v>
+      </x:c>
+      <x:c r="B35" t="str">
+        <x:v>EVT260910_016</x:v>
+      </x:c>
+      <x:c r="C35" t="str">
+        <x:v>Manila South Harbour</x:v>
+      </x:c>
+      <x:c r="D35" t="str">
+        <x:v>Philippines</x:v>
+      </x:c>
+      <x:c r="E35"/>
+      <x:c r="F35"/>
+      <x:c r="G35" t="str">
+        <x:v>Named location / no exact coordinates</x:v>
+      </x:c>
+      <x:c r="H35" t="str">
+        <x:v>Location retained for event context; not plotted unless coordinates are available.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36">
+      <x:c r="A36" t="str">
+        <x:v>LOC260910_017</x:v>
+      </x:c>
+      <x:c r="B36" t="str">
+        <x:v>EVT260910_017</x:v>
+      </x:c>
+      <x:c r="C36" t="str">
+        <x:v>Mombasa, Kenya</x:v>
+      </x:c>
+      <x:c r="D36" t="str">
+        <x:v>Kenya</x:v>
+      </x:c>
+      <x:c r="E36"/>
+      <x:c r="F36"/>
+      <x:c r="G36" t="str">
+        <x:v>Named location / no exact coordinates</x:v>
+      </x:c>
+      <x:c r="H36" t="str">
+        <x:v>Location retained for event context; not plotted unless coordinates are available.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37">
+      <x:c r="A37" t="str">
+        <x:v>LOC260910_018</x:v>
+      </x:c>
+      <x:c r="B37" t="str">
+        <x:v>EVT260910_018</x:v>
+      </x:c>
+      <x:c r="C37" t="str">
+        <x:v>Paradip Port</x:v>
+      </x:c>
+      <x:c r="D37" t="str">
         <x:v>India</x:v>
       </x:c>
-      <x:c r="E22" s="10"/>
-      <x:c r="F22" s="10"/>
-      <x:c r="G22" s="10" t="str">
-        <x:v>Regional / official description</x:v>
-      </x:c>
-      <x:c r="H22" s="10" t="str">
-        <x:v>Approx. 38 nm southwest of Kochi.</x:v>
+      <x:c r="E37"/>
+      <x:c r="F37"/>
+      <x:c r="G37" t="str">
+        <x:v>Named location / no exact coordinates</x:v>
+      </x:c>
+      <x:c r="H37" t="str">
+        <x:v>Location retained for event context; not plotted unless coordinates are available.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38">
+      <x:c r="A38" t="str">
+        <x:v>LOC260910_019</x:v>
+      </x:c>
+      <x:c r="B38" t="str">
+        <x:v>EVT260910_019</x:v>
+      </x:c>
+      <x:c r="C38" t="str">
+        <x:v>Norwegian offshore sector</x:v>
+      </x:c>
+      <x:c r="D38" t="str">
+        <x:v>Norway</x:v>
+      </x:c>
+      <x:c r="E38"/>
+      <x:c r="F38"/>
+      <x:c r="G38" t="str">
+        <x:v>Named location / no exact coordinates</x:v>
+      </x:c>
+      <x:c r="H38" t="str">
+        <x:v>Location retained for event context; not plotted unless coordinates are available.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39">
+      <x:c r="A39" t="str">
+        <x:v>LOC260910_020</x:v>
+      </x:c>
+      <x:c r="B39" t="str">
+        <x:v>EVT260910_020</x:v>
+      </x:c>
+      <x:c r="C39" t="str">
+        <x:v>Malaysia</x:v>
+      </x:c>
+      <x:c r="D39" t="str">
+        <x:v>Malaysia</x:v>
+      </x:c>
+      <x:c r="E39"/>
+      <x:c r="F39"/>
+      <x:c r="G39" t="str">
+        <x:v>Named location / no exact coordinates</x:v>
+      </x:c>
+      <x:c r="H39" t="str">
+        <x:v>Location retained for event context; not plotted unless coordinates are available.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40">
+      <x:c r="A40" t="str">
+        <x:v>LOC260910_021</x:v>
+      </x:c>
+      <x:c r="B40" t="str">
+        <x:v>EVT260910_021</x:v>
+      </x:c>
+      <x:c r="C40" t="str">
+        <x:v>Wuhu Shipyard / Great Lakes deployment</x:v>
+      </x:c>
+      <x:c r="D40" t="str">
+        <x:v>Germany</x:v>
+      </x:c>
+      <x:c r="E40"/>
+      <x:c r="F40"/>
+      <x:c r="G40" t="str">
+        <x:v>Named location / no exact coordinates</x:v>
+      </x:c>
+      <x:c r="H40" t="str">
+        <x:v>Location retained for event context; not plotted unless coordinates are available.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41">
+      <x:c r="A41" t="str">
+        <x:v>LOC260910_022</x:v>
+      </x:c>
+      <x:c r="B41" t="str">
+        <x:v>EVT260910_022</x:v>
+      </x:c>
+      <x:c r="C41" t="str">
+        <x:v>United States</x:v>
+      </x:c>
+      <x:c r="D41" t="str">
+        <x:v>United States</x:v>
+      </x:c>
+      <x:c r="E41"/>
+      <x:c r="F41"/>
+      <x:c r="G41" t="str">
+        <x:v>Named location / no exact coordinates</x:v>
+      </x:c>
+      <x:c r="H41" t="str">
+        <x:v>Location retained for event context; not plotted unless coordinates are available.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="42">
+      <x:c r="A42" t="str">
+        <x:v>LOC260910_023</x:v>
+      </x:c>
+      <x:c r="B42" t="str">
+        <x:v>EVT260910_023</x:v>
+      </x:c>
+      <x:c r="C42" t="str">
+        <x:v>Global</x:v>
+      </x:c>
+      <x:c r="D42" t="str">
+        <x:v>Global</x:v>
+      </x:c>
+      <x:c r="E42"/>
+      <x:c r="F42"/>
+      <x:c r="G42" t="str">
+        <x:v>Named location / no exact coordinates</x:v>
+      </x:c>
+      <x:c r="H42" t="str">
+        <x:v>Location retained for event context; not plotted unless coordinates are available.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="43">
+      <x:c r="A43" t="str">
+        <x:v>LOC260910_024</x:v>
+      </x:c>
+      <x:c r="B43" t="str">
+        <x:v>EVT260910_024</x:v>
+      </x:c>
+      <x:c r="C43" t="str">
+        <x:v>Strait of Hormuz / northern Gulf / Gulf of Oman</x:v>
+      </x:c>
+      <x:c r="D43" t="str">
+        <x:v>Iran</x:v>
+      </x:c>
+      <x:c r="E43"/>
+      <x:c r="F43"/>
+      <x:c r="G43" t="str">
+        <x:v>Named location / no exact coordinates</x:v>
+      </x:c>
+      <x:c r="H43" t="str">
+        <x:v>Location retained for event context; not plotted unless coordinates are available.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="44">
+      <x:c r="A44" t="str">
+        <x:v>LOC260910_025A</x:v>
+      </x:c>
+      <x:c r="B44" t="str">
+        <x:v>EVT260910_025</x:v>
+      </x:c>
+      <x:c r="C44" t="str">
+        <x:v>Qeshm Island / Qeshm</x:v>
+      </x:c>
+      <x:c r="D44" t="str">
+        <x:v>Iran</x:v>
+      </x:c>
+      <x:c r="E44" t="n">
+        <x:v>26.9581</x:v>
+      </x:c>
+      <x:c r="F44" t="n">
+        <x:v>56.2719</x:v>
+      </x:c>
+      <x:c r="G44" t="str">
+        <x:v>Island / city-level</x:v>
+      </x:c>
+      <x:c r="H44" t="str">
+        <x:v>Reporting named Qeshm; marker is geographic context rather than strike-point precision.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="45">
+      <x:c r="A45" t="str">
+        <x:v>LOC260910_025B</x:v>
+      </x:c>
+      <x:c r="B45" t="str">
+        <x:v>EVT260910_025</x:v>
+      </x:c>
+      <x:c r="C45" t="str">
+        <x:v>Sirik</x:v>
+      </x:c>
+      <x:c r="D45" t="str">
+        <x:v>Iran</x:v>
+      </x:c>
+      <x:c r="E45" t="n">
+        <x:v>26.5219</x:v>
+      </x:c>
+      <x:c r="F45" t="n">
+        <x:v>57.109</x:v>
+      </x:c>
+      <x:c r="G45" t="str">
+        <x:v>Town-level</x:v>
+      </x:c>
+      <x:c r="H45" t="str">
+        <x:v>Reporting named Sirik; marker is town-level context.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="46">
+      <x:c r="A46" t="str">
+        <x:v>LOC260910_025C</x:v>
+      </x:c>
+      <x:c r="B46" t="str">
+        <x:v>EVT260910_025</x:v>
+      </x:c>
+      <x:c r="C46" t="str">
+        <x:v>Minab</x:v>
+      </x:c>
+      <x:c r="D46" t="str">
+        <x:v>Iran</x:v>
+      </x:c>
+      <x:c r="E46" t="n">
+        <x:v>27.1467</x:v>
+      </x:c>
+      <x:c r="F46" t="n">
+        <x:v>57.0801</x:v>
+      </x:c>
+      <x:c r="G46" t="str">
+        <x:v>City-level</x:v>
+      </x:c>
+      <x:c r="H46" t="str">
+        <x:v>Reporting named Minab; marker is city-level context.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="47">
+      <x:c r="A47" t="str">
+        <x:v>LOC260910_025D</x:v>
+      </x:c>
+      <x:c r="B47" t="str">
+        <x:v>EVT260910_025</x:v>
+      </x:c>
+      <x:c r="C47" t="str">
+        <x:v>Taif</x:v>
+      </x:c>
+      <x:c r="D47" t="str">
+        <x:v>Saudi Arabia</x:v>
+      </x:c>
+      <x:c r="E47" t="n">
+        <x:v>21.2703</x:v>
+      </x:c>
+      <x:c r="F47" t="n">
+        <x:v>40.4158</x:v>
+      </x:c>
+      <x:c r="G47" t="str">
+        <x:v>City-level</x:v>
+      </x:c>
+      <x:c r="H47" t="str">
+        <x:v>Explosions were reported near King Fahd Air Base and Taif; marker uses Taif city rather than a precise military-site coordinate.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="48">
+      <x:c r="A48" t="str">
+        <x:v>LOC260910_026A</x:v>
+      </x:c>
+      <x:c r="B48" t="str">
+        <x:v>EVT260910_026</x:v>
+      </x:c>
+      <x:c r="C48" t="str">
+        <x:v>Taganrog Bay / Sea of Azov</x:v>
+      </x:c>
+      <x:c r="D48" t="str">
+        <x:v>Russia</x:v>
+      </x:c>
+      <x:c r="E48" t="n">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="F48" t="n">
+        <x:v>38.6</x:v>
+      </x:c>
+      <x:c r="G48" t="str">
+        <x:v>Sea-area / approximate theatre marker</x:v>
+      </x:c>
+      <x:c r="H48" t="str">
+        <x:v>Context marker for Sea of Azov vessel attacks; not a claimed strike-point coordinate.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="49">
+      <x:c r="A49" t="str">
+        <x:v>LOC260910_027A</x:v>
+      </x:c>
+      <x:c r="B49" t="str">
+        <x:v>EVT260910_027</x:v>
+      </x:c>
+      <x:c r="C49" t="str">
+        <x:v>Novorossiysk</x:v>
+      </x:c>
+      <x:c r="D49" t="str">
+        <x:v>Russia</x:v>
+      </x:c>
+      <x:c r="E49" t="n">
+        <x:v>44.723</x:v>
+      </x:c>
+      <x:c r="F49" t="n">
+        <x:v>37.768</x:v>
+      </x:c>
+      <x:c r="G49" t="str">
+        <x:v>City / port-level</x:v>
+      </x:c>
+      <x:c r="H49" t="str">
+        <x:v>Port-city marker for the reported Novorossiysk strike; not a precise impact coordinate.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -2659,7 +4098,7 @@
         <x:v>EVT128_001</x:v>
       </x:c>
       <x:c r="C2" s="10" t="str">
-        <x:v>PORTG0242</x:v>
+        <x:v>PORT_ROTTERDAM</x:v>
       </x:c>
       <x:c r="D2" s="10" t="str">
         <x:v>Port of Rotterdam</x:v>
@@ -2737,7 +4176,7 @@
         <x:v>EVT128_002</x:v>
       </x:c>
       <x:c r="C5" s="10" t="str">
-        <x:v>PORTG0242</x:v>
+        <x:v>PORT_ROTTERDAM</x:v>
       </x:c>
       <x:c r="D5" s="10" t="str">
         <x:v>Port of Rotterdam</x:v>
@@ -2841,7 +4280,7 @@
         <x:v>EVT128_005</x:v>
       </x:c>
       <x:c r="C9" s="10" t="str">
-        <x:v>PORTG0242</x:v>
+        <x:v>PORT_ROTTERDAM</x:v>
       </x:c>
       <x:c r="D9" s="10" t="str">
         <x:v>Port of Rotterdam</x:v>
@@ -3407,106 +4846,366 @@
     </x:row>
     <x:row r="31">
       <x:c r="A31" t="str">
-        <x:v>EAL133_001</x:v>
+        <x:v>EAL260910_001</x:v>
       </x:c>
       <x:c r="B31" t="str">
-        <x:v>EVT133_001</x:v>
+        <x:v>EVT260910_008</x:v>
       </x:c>
       <x:c r="C31" t="str">
-        <x:v>VES_HERCULES_STAR</x:v>
+        <x:v>PORTG0354</x:v>
       </x:c>
       <x:c r="D31" t="str">
-        <x:v>HERCULES STAR</x:v>
+        <x:v>Morebaya Port</x:v>
       </x:c>
       <x:c r="E31" t="str">
-        <x:v>Vessel</x:v>
+        <x:v>Port</x:v>
       </x:c>
       <x:c r="F31" t="str">
-        <x:v>SUBJECT VESSEL</x:v>
+        <x:v>DIRECT_PROJECT</x:v>
       </x:c>
       <x:c r="G31" t="str">
         <x:v>High</x:v>
       </x:c>
       <x:c r="H31" t="str">
-        <x:v>Distinct from March 2026 incident.</x:v>
+        <x:v>Commissioning export infrastructure</x:v>
       </x:c>
     </x:row>
     <x:row r="32">
       <x:c r="A32" t="str">
-        <x:v>EAL133_002</x:v>
+        <x:v>EAL260910_002</x:v>
       </x:c>
       <x:c r="B32" t="str">
-        <x:v>EVT133_002</x:v>
+        <x:v>EVT260910_009</x:v>
       </x:c>
       <x:c r="C32" t="str">
-        <x:v>PORT_STEWART_BC</x:v>
+        <x:v>PORTG0355</x:v>
       </x:c>
       <x:c r="D32" t="str">
-        <x:v>Port of Stewart</x:v>
+        <x:v>Port of Songkhla</x:v>
       </x:c>
       <x:c r="E32" t="str">
         <x:v>Port</x:v>
       </x:c>
       <x:c r="F32" t="str">
-        <x:v>OPENING / EXPANSION SUBJECT</x:v>
+        <x:v>DIRECT_PROJECT</x:v>
       </x:c>
       <x:c r="G32" t="str">
-        <x:v>Medium</x:v>
+        <x:v>High</x:v>
       </x:c>
       <x:c r="H32" t="str">
-        <x:v>Headline-level evidence.</x:v>
+        <x:v>STS cranes and capacity expansion</x:v>
       </x:c>
     </x:row>
     <x:row r="33">
       <x:c r="A33" t="str">
-        <x:v>EAL134_001</x:v>
+        <x:v>EAL260910_003</x:v>
       </x:c>
       <x:c r="B33" t="str">
-        <x:v>EVT134_003</x:v>
+        <x:v>EVT260910_010</x:v>
       </x:c>
       <x:c r="C33" t="str">
-        <x:v>VES_MSC_SAMIRA_III</x:v>
+        <x:v>PORTG0358</x:v>
       </x:c>
       <x:c r="D33" t="str">
-        <x:v>MSC SAMIRA III</x:v>
+        <x:v>Xiangshan Port offshore-wind base</x:v>
       </x:c>
       <x:c r="E33" t="str">
-        <x:v>Vessel</x:v>
+        <x:v>Port / project</x:v>
       </x:c>
       <x:c r="F33" t="str">
-        <x:v>SUBJECT VESSEL</x:v>
+        <x:v>DIRECT_PROJECT</x:v>
       </x:c>
       <x:c r="G33" t="str">
         <x:v>High</x:v>
       </x:c>
       <x:c r="H33" t="str">
-        <x:v>IMO pending verification.</x:v>
+        <x:v>Specialist offshore-wind port development</x:v>
       </x:c>
     </x:row>
     <x:row r="34">
       <x:c r="A34" t="str">
-        <x:v>EAL134_002</x:v>
+        <x:v>EAL260910_004</x:v>
       </x:c>
       <x:c r="B34" t="str">
-        <x:v>EVT134_005</x:v>
+        <x:v>EVT260910_011</x:v>
       </x:c>
       <x:c r="C34" t="str">
-        <x:v>ASSET_ARCTIC_LNG2</x:v>
+        <x:v>PORTG0170</x:v>
       </x:c>
       <x:c r="D34" t="str">
-        <x:v>Arctic LNG 2</x:v>
+        <x:v>Port of Colombo</x:v>
       </x:c>
       <x:c r="E34" t="str">
-        <x:v>LNG project</x:v>
+        <x:v>Port</x:v>
       </x:c>
       <x:c r="F34" t="str">
-        <x:v>EXPORT FLEET DEPENDENCY</x:v>
+        <x:v>DIRECT_PROJECT</x:v>
       </x:c>
       <x:c r="G34" t="str">
-        <x:v>High</x:v>
+        <x:v>Medium</x:v>
       </x:c>
       <x:c r="H34" t="str">
-        <x:v>19.8 mtpa planned project capacity.</x:v>
+        <x:v>Port ID may differ in canonical table; link retained by name</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35">
+      <x:c r="A35" t="str">
+        <x:v>EAL260910_005</x:v>
+      </x:c>
+      <x:c r="B35" t="str">
+        <x:v>EVT260910_012</x:v>
+      </x:c>
+      <x:c r="C35" t="str">
+        <x:v>PORTG0356</x:v>
+      </x:c>
+      <x:c r="D35" t="str">
+        <x:v>Port of Newcastle</x:v>
+      </x:c>
+      <x:c r="E35" t="str">
+        <x:v>Port</x:v>
+      </x:c>
+      <x:c r="F35" t="str">
+        <x:v>DIRECT_PROJECT</x:v>
+      </x:c>
+      <x:c r="G35" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="H35" t="str">
+        <x:v>Road freight access upgrade</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36">
+      <x:c r="A36" t="str">
+        <x:v>EAL260910_006</x:v>
+      </x:c>
+      <x:c r="B36" t="str">
+        <x:v>EVT260910_013</x:v>
+      </x:c>
+      <x:c r="C36" t="str">
+        <x:v>PORTG0324</x:v>
+      </x:c>
+      <x:c r="D36" t="str">
+        <x:v>Port of Baltimore</x:v>
+      </x:c>
+      <x:c r="E36" t="str">
+        <x:v>Port</x:v>
+      </x:c>
+      <x:c r="F36" t="str">
+        <x:v>DIRECT_PROJECT</x:v>
+      </x:c>
+      <x:c r="G36" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="H36" t="str">
+        <x:v>On-dock grain gateway</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37">
+      <x:c r="A37" t="str">
+        <x:v>EAL260910_007</x:v>
+      </x:c>
+      <x:c r="B37" t="str">
+        <x:v>EVT260910_014</x:v>
+      </x:c>
+      <x:c r="C37" t="str">
+        <x:v>PORTG0141</x:v>
+      </x:c>
+      <x:c r="D37" t="str">
+        <x:v>Kuryk Port</x:v>
+      </x:c>
+      <x:c r="E37" t="str">
+        <x:v>Port</x:v>
+      </x:c>
+      <x:c r="F37" t="str">
+        <x:v>NETWORK_EXPOSURE</x:v>
+      </x:c>
+      <x:c r="G37" t="str">
+        <x:v>Medium</x:v>
+      </x:c>
+      <x:c r="H37" t="str">
+        <x:v>Caspian hub / Kuryk-area network</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38">
+      <x:c r="A38" t="str">
+        <x:v>EAL260910_008</x:v>
+      </x:c>
+      <x:c r="B38" t="str">
+        <x:v>EVT260910_015</x:v>
+      </x:c>
+      <x:c r="C38" t="str">
+        <x:v>PORTG0159</x:v>
+      </x:c>
+      <x:c r="D38" t="str">
+        <x:v>Port of Valencia</x:v>
+      </x:c>
+      <x:c r="E38" t="str">
+        <x:v>Port</x:v>
+      </x:c>
+      <x:c r="F38" t="str">
+        <x:v>DIRECT_PROJECT</x:v>
+      </x:c>
+      <x:c r="G38" t="str">
+        <x:v>Medium</x:v>
+      </x:c>
+      <x:c r="H38" t="str">
+        <x:v>North terminal court decision</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39">
+      <x:c r="A39" t="str">
+        <x:v>EAL260910_009</x:v>
+      </x:c>
+      <x:c r="B39" t="str">
+        <x:v>EVT260910_016</x:v>
+      </x:c>
+      <x:c r="C39" t="str">
+        <x:v>PORTG0069</x:v>
+      </x:c>
+      <x:c r="D39" t="str">
+        <x:v>Manila</x:v>
+      </x:c>
+      <x:c r="E39" t="str">
+        <x:v>Port</x:v>
+      </x:c>
+      <x:c r="F39" t="str">
+        <x:v>DIRECT_PROJECT</x:v>
+      </x:c>
+      <x:c r="G39" t="str">
+        <x:v>Medium</x:v>
+      </x:c>
+      <x:c r="H39" t="str">
+        <x:v>Manila South Harbour terminal expansion</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40">
+      <x:c r="A40" t="str">
+        <x:v>EAL260910_010</x:v>
+      </x:c>
+      <x:c r="B40" t="str">
+        <x:v>EVT260910_017</x:v>
+      </x:c>
+      <x:c r="C40" t="str">
+        <x:v>PORTG0169</x:v>
+      </x:c>
+      <x:c r="D40" t="str">
+        <x:v>Port of Mombasa</x:v>
+      </x:c>
+      <x:c r="E40" t="str">
+        <x:v>Port</x:v>
+      </x:c>
+      <x:c r="F40" t="str">
+        <x:v>NETWORK_EXPOSURE</x:v>
+      </x:c>
+      <x:c r="G40" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="H40" t="str">
+        <x:v>Industrial park located near port</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41">
+      <x:c r="A41" t="str">
+        <x:v>EAL260910_011</x:v>
+      </x:c>
+      <x:c r="B41" t="str">
+        <x:v>EVT260910_018</x:v>
+      </x:c>
+      <x:c r="C41" t="str">
+        <x:v>PORTG0357</x:v>
+      </x:c>
+      <x:c r="D41" t="str">
+        <x:v>Paradip Port</x:v>
+      </x:c>
+      <x:c r="E41" t="str">
+        <x:v>Port</x:v>
+      </x:c>
+      <x:c r="F41" t="str">
+        <x:v>DIRECT_PROJECT</x:v>
+      </x:c>
+      <x:c r="G41" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="H41" t="str">
+        <x:v>Two dry-bulk berth concession</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="42">
+      <x:c r="A42" t="str">
+        <x:v>EAL260910_026A</x:v>
+      </x:c>
+      <x:c r="B42" t="str">
+        <x:v>EVT260910_026</x:v>
+      </x:c>
+      <x:c r="C42" t="str">
+        <x:v>VESSEL_NATRA</x:v>
+      </x:c>
+      <x:c r="D42" t="str">
+        <x:v>Natra</x:v>
+      </x:c>
+      <x:c r="E42" t="str">
+        <x:v>Cargo vessel</x:v>
+      </x:c>
+      <x:c r="F42" t="str">
+        <x:v>DIRECTLY_AFFECTED</x:v>
+      </x:c>
+      <x:c r="G42" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="H42" t="str">
+        <x:v>Merchant vessel struck in Sea of Azov</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="43">
+      <x:c r="A43" t="str">
+        <x:v>EAL260910_026B</x:v>
+      </x:c>
+      <x:c r="B43" t="str">
+        <x:v>EVT260910_026</x:v>
+      </x:c>
+      <x:c r="C43" t="str">
+        <x:v>VESSEL_ZIRKON</x:v>
+      </x:c>
+      <x:c r="D43" t="str">
+        <x:v>Zirkon</x:v>
+      </x:c>
+      <x:c r="E43" t="str">
+        <x:v>Cargo vessel</x:v>
+      </x:c>
+      <x:c r="F43" t="str">
+        <x:v>DIRECTLY_AFFECTED</x:v>
+      </x:c>
+      <x:c r="G43" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="H43" t="str">
+        <x:v>Merchant vessel struck in Sea of Azov</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="44">
+      <x:c r="A44" t="str">
+        <x:v>EAL260910_027A</x:v>
+      </x:c>
+      <x:c r="B44" t="str">
+        <x:v>EVT260910_027</x:v>
+      </x:c>
+      <x:c r="C44" t="str">
+        <x:v>PORT_NOVOROSSIYSK</x:v>
+      </x:c>
+      <x:c r="D44" t="str">
+        <x:v>Port of Novorossiysk</x:v>
+      </x:c>
+      <x:c r="E44" t="str">
+        <x:v>Port / oil-export hub</x:v>
+      </x:c>
+      <x:c r="F44" t="str">
+        <x:v>DIRECTLY_AFFECTED</x:v>
+      </x:c>
+      <x:c r="G44" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="H44" t="str">
+        <x:v>Port and fuel-oil infrastructure struck</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -3928,19 +5627,19 @@
     </x:row>
     <x:row r="21">
       <x:c r="A21" t="str">
-        <x:v>ECL133_001</x:v>
+        <x:v>ECL260910_001</x:v>
       </x:c>
       <x:c r="B21" t="str">
-        <x:v>EVT133_001</x:v>
+        <x:v>EVT260910_001</x:v>
       </x:c>
       <x:c r="C21" t="str">
-        <x:v>COMP_PENINSULA</x:v>
+        <x:v>COMP_SAUDI_ARAMCO</x:v>
       </x:c>
       <x:c r="D21" t="str">
-        <x:v>Peninsula</x:v>
+        <x:v>Saudi Aramco</x:v>
       </x:c>
       <x:c r="E21" t="str">
-        <x:v>CHARTERER / INCIDENT RESPONDER</x:v>
+        <x:v>Affected energy company</x:v>
       </x:c>
       <x:c r="F21" t="str">
         <x:v>High</x:v>
@@ -3948,19 +5647,19 @@
     </x:row>
     <x:row r="22">
       <x:c r="A22" t="str">
-        <x:v>ECL133_002</x:v>
+        <x:v>ECL260910_002</x:v>
       </x:c>
       <x:c r="B22" t="str">
-        <x:v>EVT133_001</x:v>
+        <x:v>EVT260910_003</x:v>
       </x:c>
       <x:c r="C22" t="str">
-        <x:v>COMP_HERCULES_TANKER</x:v>
+        <x:v>COMP_COCHIN_SHIPYARD</x:v>
       </x:c>
       <x:c r="D22" t="str">
-        <x:v>Hercules Tanker Management</x:v>
+        <x:v>Cochin Shipyard</x:v>
       </x:c>
       <x:c r="E22" t="str">
-        <x:v>SISTER COMPANY / VESSEL PROVIDER</x:v>
+        <x:v>Joint-venture partner</x:v>
       </x:c>
       <x:c r="F22" t="str">
         <x:v>High</x:v>
@@ -3968,59 +5667,59 @@
     </x:row>
     <x:row r="23">
       <x:c r="A23" t="str">
-        <x:v>ECL133_003</x:v>
+        <x:v>ECL260910_003</x:v>
       </x:c>
       <x:c r="B23" t="str">
-        <x:v>EVT133_002</x:v>
+        <x:v>EVT260910_003</x:v>
       </x:c>
       <x:c r="C23" t="str">
-        <x:v>ORG_NISGAA_NATION</x:v>
+        <x:v>COMP_DRYDOCKS_WORLD</x:v>
       </x:c>
       <x:c r="D23" t="str">
-        <x:v>Nisg̱a'a Nation</x:v>
+        <x:v>Drydocks World</x:v>
       </x:c>
       <x:c r="E23" t="str">
-        <x:v>OPENING PARTICIPANT</x:v>
+        <x:v>Joint-venture partner / operating lead</x:v>
       </x:c>
       <x:c r="F23" t="str">
-        <x:v>Medium</x:v>
+        <x:v>High</x:v>
       </x:c>
     </x:row>
     <x:row r="24">
       <x:c r="A24" t="str">
-        <x:v>ECL133_004</x:v>
+        <x:v>ECL260910_004</x:v>
       </x:c>
       <x:c r="B24" t="str">
-        <x:v>EVT133_002</x:v>
+        <x:v>EVT260910_005</x:v>
       </x:c>
       <x:c r="C24" t="str">
-        <x:v>ORG_TAHLTAN_NATION</x:v>
+        <x:v>COMP_HMM</x:v>
       </x:c>
       <x:c r="D24" t="str">
-        <x:v>Tahltan Nation</x:v>
+        <x:v>HMM Co., Ltd.</x:v>
       </x:c>
       <x:c r="E24" t="str">
-        <x:v>OPENING PARTICIPANT</x:v>
+        <x:v>Carrier / contract party</x:v>
       </x:c>
       <x:c r="F24" t="str">
-        <x:v>Medium</x:v>
+        <x:v>High</x:v>
       </x:c>
     </x:row>
     <x:row r="25">
       <x:c r="A25" t="str">
-        <x:v>ECL133_005</x:v>
+        <x:v>ECL260910_005</x:v>
       </x:c>
       <x:c r="B25" t="str">
-        <x:v>EVT133_003</x:v>
+        <x:v>EVT260910_005</x:v>
       </x:c>
       <x:c r="C25" t="str">
-        <x:v>COMP_ROYAL_CARIBBEAN_GROUP</x:v>
+        <x:v>COMP_VALE</x:v>
       </x:c>
       <x:c r="D25" t="str">
-        <x:v>Royal Caribbean Group</x:v>
+        <x:v>Vale</x:v>
       </x:c>
       <x:c r="E25" t="str">
-        <x:v>PRIVATE-DESTINATION INVESTOR</x:v>
+        <x:v>Cargo owner / contract party</x:v>
       </x:c>
       <x:c r="F25" t="str">
         <x:v>High</x:v>
@@ -4028,19 +5727,19 @@
     </x:row>
     <x:row r="26">
       <x:c r="A26" t="str">
-        <x:v>ECL133_006</x:v>
+        <x:v>ECL260910_006</x:v>
       </x:c>
       <x:c r="B26" t="str">
-        <x:v>EVT133_003</x:v>
+        <x:v>EVT260910_007</x:v>
       </x:c>
       <x:c r="C26" t="str">
-        <x:v>COMP_CARNIVAL_CORP</x:v>
+        <x:v>COMP_AUSTAL_USA</x:v>
       </x:c>
       <x:c r="D26" t="str">
-        <x:v>Carnival Corporation &amp; plc</x:v>
+        <x:v>Austal USA</x:v>
       </x:c>
       <x:c r="E26" t="str">
-        <x:v>PRIVATE-DESTINATION INVESTOR</x:v>
+        <x:v>Acquisition target</x:v>
       </x:c>
       <x:c r="F26" t="str">
         <x:v>High</x:v>
@@ -4048,19 +5747,19 @@
     </x:row>
     <x:row r="27">
       <x:c r="A27" t="str">
-        <x:v>ECL133_007</x:v>
+        <x:v>ECL260910_007</x:v>
       </x:c>
       <x:c r="B27" t="str">
-        <x:v>EVT133_003</x:v>
+        <x:v>EVT260910_007</x:v>
       </x:c>
       <x:c r="C27" t="str">
-        <x:v>COMP_NCLH</x:v>
+        <x:v>COMP_HANWHA_GROUP</x:v>
       </x:c>
       <x:c r="D27" t="str">
-        <x:v>Norwegian Cruise Line Holdings</x:v>
+        <x:v>Hanwha Group</x:v>
       </x:c>
       <x:c r="E27" t="str">
-        <x:v>PRIVATE-DESTINATION INVESTOR</x:v>
+        <x:v>Competing bidder</x:v>
       </x:c>
       <x:c r="F27" t="str">
         <x:v>High</x:v>
@@ -4068,19 +5767,19 @@
     </x:row>
     <x:row r="28">
       <x:c r="A28" t="str">
-        <x:v>ECL134_001</x:v>
+        <x:v>ECL260910_008</x:v>
       </x:c>
       <x:c r="B28" t="str">
-        <x:v>EVT134_001</x:v>
+        <x:v>EVT260910_007</x:v>
       </x:c>
       <x:c r="C28" t="str">
-        <x:v>COMP_HUNTER_GROUP</x:v>
+        <x:v>COMP_WILDCAT_INFRA</x:v>
       </x:c>
       <x:c r="D28" t="str">
-        <x:v>Hunter Group ASA</x:v>
+        <x:v>Wildcat Infrastructure</x:v>
       </x:c>
       <x:c r="E28" t="str">
-        <x:v>CLAIMANT</x:v>
+        <x:v>Competing bidder</x:v>
       </x:c>
       <x:c r="F28" t="str">
         <x:v>High</x:v>
@@ -4088,19 +5787,19 @@
     </x:row>
     <x:row r="29">
       <x:c r="A29" t="str">
-        <x:v>ECL134_002</x:v>
+        <x:v>ECL260910_009</x:v>
       </x:c>
       <x:c r="B29" t="str">
-        <x:v>EVT134_002</x:v>
+        <x:v>EVT260910_008</x:v>
       </x:c>
       <x:c r="C29" t="str">
-        <x:v>COMP_SEASPAN_ULC</x:v>
+        <x:v>COMP_SIMFER</x:v>
       </x:c>
       <x:c r="D29" t="str">
-        <x:v>Seaspan ULC</x:v>
+        <x:v>SimFer</x:v>
       </x:c>
       <x:c r="E29" t="str">
-        <x:v>SUBCONTRACTOR / MAINTENANCE YARD</x:v>
+        <x:v>Project developer / operator</x:v>
       </x:c>
       <x:c r="F29" t="str">
         <x:v>High</x:v>
@@ -4108,19 +5807,19 @@
     </x:row>
     <x:row r="30">
       <x:c r="A30" t="str">
-        <x:v>ECL134_003</x:v>
+        <x:v>ECL260910_010</x:v>
       </x:c>
       <x:c r="B30" t="str">
-        <x:v>EVT134_002</x:v>
+        <x:v>EVT260910_009</x:v>
       </x:c>
       <x:c r="C30" t="str">
-        <x:v>COMP_BABCOCK_CANADA</x:v>
+        <x:v>COMP_CHAOPHAYA_TERMINAL</x:v>
       </x:c>
       <x:c r="D30" t="str">
-        <x:v>Babcock Canada</x:v>
+        <x:v>Chaophaya Terminal International</x:v>
       </x:c>
       <x:c r="E30" t="str">
-        <x:v>PRIME CONTRACTOR / CUSTOMER</x:v>
+        <x:v>Terminal operator</x:v>
       </x:c>
       <x:c r="F30" t="str">
         <x:v>High</x:v>
@@ -4128,19 +5827,19 @@
     </x:row>
     <x:row r="31">
       <x:c r="A31" t="str">
-        <x:v>ECL134_004</x:v>
+        <x:v>ECL260910_011</x:v>
       </x:c>
       <x:c r="B31" t="str">
-        <x:v>EVT134_003</x:v>
+        <x:v>EVT260910_013</x:v>
       </x:c>
       <x:c r="C31" t="str">
-        <x:v>COMP_MSC_SHIPMANAGEMENT</x:v>
+        <x:v>COMP_PORTS_AMERICA_CHES</x:v>
       </x:c>
       <x:c r="D31" t="str">
-        <x:v>MSC Shipmanagement Limited</x:v>
+        <x:v>Ports America Chesapeake</x:v>
       </x:c>
       <x:c r="E31" t="str">
-        <x:v>DEFENDANT / MANAGER</x:v>
+        <x:v>Facility operator / developer</x:v>
       </x:c>
       <x:c r="F31" t="str">
         <x:v>High</x:v>
@@ -4148,19 +5847,19 @@
     </x:row>
     <x:row r="32">
       <x:c r="A32" t="str">
-        <x:v>ECL134_005</x:v>
+        <x:v>ECL260910_012</x:v>
       </x:c>
       <x:c r="B32" t="str">
-        <x:v>EVT134_003</x:v>
+        <x:v>EVT260910_013</x:v>
       </x:c>
       <x:c r="C32" t="str">
-        <x:v>COMP_HONG_KONG_SPIRIT</x:v>
+        <x:v>COMP_FREY_COMMODITIES</x:v>
       </x:c>
       <x:c r="D32" t="str">
-        <x:v>Hong Kong Spirit Shipping and Trading Ltd</x:v>
+        <x:v>Frey Commodities</x:v>
       </x:c>
       <x:c r="E32" t="str">
-        <x:v>DEFENDANT / OWNER</x:v>
+        <x:v>Facility partner / user</x:v>
       </x:c>
       <x:c r="F32" t="str">
         <x:v>High</x:v>
@@ -4168,19 +5867,19 @@
     </x:row>
     <x:row r="33">
       <x:c r="A33" t="str">
-        <x:v>ECL134_006</x:v>
+        <x:v>ECL260910_013</x:v>
       </x:c>
       <x:c r="B33" t="str">
-        <x:v>EVT134_004</x:v>
+        <x:v>EVT260910_014</x:v>
       </x:c>
       <x:c r="C33" t="str">
-        <x:v>ORG_MARAD</x:v>
+        <x:v>COMP_GUOYOU_RESOURCES</x:v>
       </x:c>
       <x:c r="D33" t="str">
-        <x:v>U.S. Maritime Administration</x:v>
+        <x:v>Guo You Resources Group</x:v>
       </x:c>
       <x:c r="E33" t="str">
-        <x:v>PROGRAMME OWNER</x:v>
+        <x:v>Project developer</x:v>
       </x:c>
       <x:c r="F33" t="str">
         <x:v>High</x:v>
@@ -4188,19 +5887,19 @@
     </x:row>
     <x:row r="34">
       <x:c r="A34" t="str">
-        <x:v>ECL134_007</x:v>
+        <x:v>ECL260910_014</x:v>
       </x:c>
       <x:c r="B34" t="str">
-        <x:v>EVT134_005</x:v>
+        <x:v>EVT260910_016</x:v>
       </x:c>
       <x:c r="C34" t="str">
-        <x:v>COMP_ARCTIC_LNG2</x:v>
+        <x:v>COMP_DPW</x:v>
       </x:c>
       <x:c r="D34" t="str">
-        <x:v>Arctic LNG 2 LLC</x:v>
+        <x:v>DP World</x:v>
       </x:c>
       <x:c r="E34" t="str">
-        <x:v>CLAIMANT</x:v>
+        <x:v>Terminal investor / operator</x:v>
       </x:c>
       <x:c r="F34" t="str">
         <x:v>High</x:v>
@@ -4208,19 +5907,19 @@
     </x:row>
     <x:row r="35">
       <x:c r="A35" t="str">
-        <x:v>ECL134_008</x:v>
+        <x:v>ECL260910_015</x:v>
       </x:c>
       <x:c r="B35" t="str">
-        <x:v>EVT134_005</x:v>
+        <x:v>EVT260910_016</x:v>
       </x:c>
       <x:c r="C35" t="str">
-        <x:v>COMP_HANWHA_OCEAN</x:v>
+        <x:v>COMP_ASIAN_TERMINALS</x:v>
       </x:c>
       <x:c r="D35" t="str">
-        <x:v>Hanwha Ocean</x:v>
+        <x:v>Asian Terminals Inc</x:v>
       </x:c>
       <x:c r="E35" t="str">
-        <x:v>RESPONDENT / BUILDER</x:v>
+        <x:v>Terminal operator / partner</x:v>
       </x:c>
       <x:c r="F35" t="str">
         <x:v>High</x:v>
@@ -4228,19 +5927,19 @@
     </x:row>
     <x:row r="36">
       <x:c r="A36" t="str">
-        <x:v>ECL134_009</x:v>
+        <x:v>ECL260910_016</x:v>
       </x:c>
       <x:c r="B36" t="str">
-        <x:v>EVT134_005</x:v>
+        <x:v>EVT260910_017</x:v>
       </x:c>
       <x:c r="C36" t="str">
-        <x:v>COMP_NOVATEK</x:v>
+        <x:v>COMP_DPW</x:v>
       </x:c>
       <x:c r="D36" t="str">
-        <x:v>PAO NOVATEK</x:v>
+        <x:v>DP World</x:v>
       </x:c>
       <x:c r="E36" t="str">
-        <x:v>PROJECT LEAD / 60% OWNER</x:v>
+        <x:v>Joint-venture partner</x:v>
       </x:c>
       <x:c r="F36" t="str">
         <x:v>High</x:v>
@@ -4248,21 +5947,181 @@
     </x:row>
     <x:row r="37">
       <x:c r="A37" t="str">
-        <x:v>ECL128_015</x:v>
+        <x:v>ECL260910_017</x:v>
       </x:c>
       <x:c r="B37" t="str">
-        <x:v>EVT128_005</x:v>
+        <x:v>EVT260910_017</x:v>
       </x:c>
       <x:c r="C37" t="str">
-        <x:v>COMP_POR_AUTH</x:v>
+        <x:v>COMP_GULFCAP_AFRICA</x:v>
       </x:c>
       <x:c r="D37" t="str">
-        <x:v>Port of Rotterdam Authority</x:v>
+        <x:v>GulfCap Africa</x:v>
       </x:c>
       <x:c r="E37" t="str">
-        <x:v>Affected authority / port-system context</x:v>
+        <x:v>Joint-venture partner</x:v>
       </x:c>
       <x:c r="F37" t="str">
+        <x:v>High</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38">
+      <x:c r="A38" t="str">
+        <x:v>ECL260910_018</x:v>
+      </x:c>
+      <x:c r="B38" t="str">
+        <x:v>EVT260910_018</x:v>
+      </x:c>
+      <x:c r="C38" t="str">
+        <x:v>COMP_ADANI_PORTS</x:v>
+      </x:c>
+      <x:c r="D38" t="str">
+        <x:v>Adani Ports and Special Economic Zone</x:v>
+      </x:c>
+      <x:c r="E38" t="str">
+        <x:v>Concessionaire</x:v>
+      </x:c>
+      <x:c r="F38" t="str">
+        <x:v>High</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39">
+      <x:c r="A39" t="str">
+        <x:v>ECL260910_019</x:v>
+      </x:c>
+      <x:c r="B39" t="str">
+        <x:v>EVT260910_019</x:v>
+      </x:c>
+      <x:c r="C39" t="str">
+        <x:v>COMP_ODFJELL_DRILLING</x:v>
+      </x:c>
+      <x:c r="D39" t="str">
+        <x:v>Odfjell Drilling</x:v>
+      </x:c>
+      <x:c r="E39" t="str">
+        <x:v>Contractor</x:v>
+      </x:c>
+      <x:c r="F39" t="str">
+        <x:v>High</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40">
+      <x:c r="A40" t="str">
+        <x:v>ECL260910_020</x:v>
+      </x:c>
+      <x:c r="B40" t="str">
+        <x:v>EVT260910_019</x:v>
+      </x:c>
+      <x:c r="C40" t="str">
+        <x:v>COMP_VAR_ENERGI</x:v>
+      </x:c>
+      <x:c r="D40" t="str">
+        <x:v>Vår Energi</x:v>
+      </x:c>
+      <x:c r="E40" t="str">
+        <x:v>Customer / contract awarder</x:v>
+      </x:c>
+      <x:c r="F40" t="str">
+        <x:v>High</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41">
+      <x:c r="A41" t="str">
+        <x:v>ECL260910_021</x:v>
+      </x:c>
+      <x:c r="B41" t="str">
+        <x:v>EVT260910_020</x:v>
+      </x:c>
+      <x:c r="C41" t="str">
+        <x:v>COMP_ALAM_MARITIM</x:v>
+      </x:c>
+      <x:c r="D41" t="str">
+        <x:v>Alam Maritim Resources</x:v>
+      </x:c>
+      <x:c r="E41" t="str">
+        <x:v>Subject company</x:v>
+      </x:c>
+      <x:c r="F41" t="str">
+        <x:v>High</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="42">
+      <x:c r="A42" t="str">
+        <x:v>ECL260910_022</x:v>
+      </x:c>
+      <x:c r="B42" t="str">
+        <x:v>EVT260910_021</x:v>
+      </x:c>
+      <x:c r="C42" t="str">
+        <x:v>COMP_ERNST_RUSS</x:v>
+      </x:c>
+      <x:c r="D42" t="str">
+        <x:v>Ernst Russ</x:v>
+      </x:c>
+      <x:c r="E42" t="str">
+        <x:v>Vessel buyer / owner</x:v>
+      </x:c>
+      <x:c r="F42" t="str">
+        <x:v>High</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="43">
+      <x:c r="A43" t="str">
+        <x:v>ECL260910_023</x:v>
+      </x:c>
+      <x:c r="B43" t="str">
+        <x:v>EVT260910_021</x:v>
+      </x:c>
+      <x:c r="C43" t="str">
+        <x:v>COMP_CARGILL</x:v>
+      </x:c>
+      <x:c r="D43" t="str">
+        <x:v>Cargill</x:v>
+      </x:c>
+      <x:c r="E43" t="str">
+        <x:v>Charterer</x:v>
+      </x:c>
+      <x:c r="F43" t="str">
+        <x:v>High</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="44">
+      <x:c r="A44" t="str">
+        <x:v>ECL260910_024</x:v>
+      </x:c>
+      <x:c r="B44" t="str">
+        <x:v>EVT260910_022</x:v>
+      </x:c>
+      <x:c r="C44" t="str">
+        <x:v>COMP_CMA_CGM</x:v>
+      </x:c>
+      <x:c r="D44" t="str">
+        <x:v>CMA CGM Group</x:v>
+      </x:c>
+      <x:c r="E44" t="str">
+        <x:v>Respondent carrier</x:v>
+      </x:c>
+      <x:c r="F44" t="str">
+        <x:v>High</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="45">
+      <x:c r="A45" t="str">
+        <x:v>ECL260910_025</x:v>
+      </x:c>
+      <x:c r="B45" t="str">
+        <x:v>EVT260910_023</x:v>
+      </x:c>
+      <x:c r="C45" t="str">
+        <x:v>COMP_SAFE_BULKERS</x:v>
+      </x:c>
+      <x:c r="D45" t="str">
+        <x:v>Safe Bulkers</x:v>
+      </x:c>
+      <x:c r="E45" t="str">
+        <x:v>Issuer / fleet investor</x:v>
+      </x:c>
+      <x:c r="F45" t="str">
         <x:v>High</x:v>
       </x:c>
     </x:row>
@@ -4605,21 +6464,61 @@
     </x:row>
     <x:row r="17">
       <x:c r="A17" t="str">
-        <x:v>ESL134_001</x:v>
+        <x:v>ESL260910_025</x:v>
       </x:c>
       <x:c r="B17" t="str">
-        <x:v>EVT134_001</x:v>
+        <x:v>EVT260910_025</x:v>
       </x:c>
       <x:c r="C17" t="str">
-        <x:v>SYS_HORMUZ_SECURITY</x:v>
+        <x:v>CORRIDOR_HORMUZ</x:v>
       </x:c>
       <x:c r="D17" t="str">
-        <x:v>Persian Gulf / Hormuz / Gulf of Oman Security System</x:v>
+        <x:v>Strait of Hormuz</x:v>
       </x:c>
       <x:c r="E17" t="str">
-        <x:v>RATE / ROUTE-RISK TRANSMISSION</x:v>
+        <x:v>REGIONAL_SECURITY_EXPOSURE</x:v>
       </x:c>
       <x:c r="F17" t="str">
+        <x:v>High</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18">
+      <x:c r="A18" t="str">
+        <x:v>ESL260910_026</x:v>
+      </x:c>
+      <x:c r="B18" t="str">
+        <x:v>EVT260910_026</x:v>
+      </x:c>
+      <x:c r="C18" t="str">
+        <x:v>SYS_BLACK_SEA_AZOV</x:v>
+      </x:c>
+      <x:c r="D18" t="str">
+        <x:v>Black Sea / Sea of Azov merchant-shipping theatre</x:v>
+      </x:c>
+      <x:c r="E18" t="str">
+        <x:v>DIRECT_SECURITY_IMPACT</x:v>
+      </x:c>
+      <x:c r="F18" t="str">
+        <x:v>High</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19">
+      <x:c r="A19" t="str">
+        <x:v>ESL260910_027</x:v>
+      </x:c>
+      <x:c r="B19" t="str">
+        <x:v>EVT260910_027</x:v>
+      </x:c>
+      <x:c r="C19" t="str">
+        <x:v>SYS_BLACK_SEA_ENERGY</x:v>
+      </x:c>
+      <x:c r="D19" t="str">
+        <x:v>Black Sea energy-export system</x:v>
+      </x:c>
+      <x:c r="E19" t="str">
+        <x:v>DIRECT_SYSTEM_IMPACT</x:v>
+      </x:c>
+      <x:c r="F19" t="str">
         <x:v>High</x:v>
       </x:c>
     </x:row>
@@ -5080,176 +6979,89 @@
     </x:row>
     <x:row r="16">
       <x:c r="A16" t="str">
-        <x:v>CHAIN134_001</x:v>
+        <x:v>CHAIN260910_025</x:v>
       </x:c>
       <x:c r="B16" t="str">
-        <x:v>EVT134_001</x:v>
+        <x:v>EVT260910_025</x:v>
       </x:c>
       <x:c r="C16" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D16" t="str">
-        <x:v>Hormuz conflict risk</x:v>
+        <x:v>Explosions / strike activity across Hormozgan coast and Taif</x:v>
       </x:c>
       <x:c r="E16" t="str">
-        <x:v>Tanker availability and benchmark rates surge</x:v>
+        <x:v>Heightened threat to coastal and military infrastructure</x:v>
       </x:c>
       <x:c r="F16" t="str">
-        <x:v>Charter-rate payment dispute</x:v>
+        <x:v>Greater uncertainty around Hormuz approaches and regional air/maritime operating conditions</x:v>
       </x:c>
       <x:c r="G16" t="str">
-        <x:v>Court exposure and counterparty risk</x:v>
+        <x:v>War-risk, routing and energy-market pressure</x:v>
       </x:c>
       <x:c r="H16" t="str">
-        <x:v>Volatile energy-transport economics</x:v>
+        <x:v>Sustained Gulf trade and energy-flow disruption risk</x:v>
       </x:c>
       <x:c r="I16" t="str">
-        <x:v>Security → freight rate → legal / financial</x:v>
+        <x:v>Direct → regional → commercial</x:v>
       </x:c>
     </x:row>
     <x:row r="17">
       <x:c r="A17" t="str">
-        <x:v>CHAIN134_002</x:v>
+        <x:v>CHAIN260910_026</x:v>
       </x:c>
       <x:c r="B17" t="str">
-        <x:v>EVT134_005</x:v>
+        <x:v>EVT260910_026</x:v>
       </x:c>
       <x:c r="C17" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D17" t="str">
-        <x:v>Sanctions and contract termination</x:v>
+        <x:v>Drone attack on merchant vessels</x:v>
       </x:c>
       <x:c r="E17" t="str">
-        <x:v>Arc7 carrier delivery programme disrupted</x:v>
+        <x:v>Crew fatalities and vessel damage</x:v>
       </x:c>
       <x:c r="F17" t="str">
-        <x:v>LNG export logistics constrained</x:v>
+        <x:v>Search/rescue and recovery operations; heightened merchant-shipping caution</x:v>
       </x:c>
       <x:c r="G17" t="str">
-        <x:v>USD 1.02bn arbitration claim</x:v>
+        <x:v>Higher war-risk and crew-safety exposure in Sea of Azov traffic</x:v>
       </x:c>
       <x:c r="H17" t="str">
-        <x:v>Arctic LNG project monetization risk</x:v>
+        <x:v>Reduced operating tolerance for civilian shipping near active strike zones</x:v>
       </x:c>
       <x:c r="I17" t="str">
-        <x:v>Sanctions → fleet → export → arbitration</x:v>
+        <x:v>Direct → operational → commercial</x:v>
       </x:c>
     </x:row>
     <x:row r="18">
       <x:c r="A18" t="str">
-        <x:v>CHAIN134_003</x:v>
+        <x:v>CHAIN260910_027</x:v>
       </x:c>
       <x:c r="B18" t="str">
-        <x:v>EVT134_004</x:v>
+        <x:v>EVT260910_027</x:v>
       </x:c>
       <x:c r="C18" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D18" t="str">
-        <x:v>Shipbuilding and mariner workforce shortage</x:v>
+        <x:v>Drone strike on Novorossiysk port/energy infrastructure</x:v>
       </x:c>
       <x:c r="E18" t="str">
-        <x:v>16 institutions added</x:v>
+        <x:v>Fuel-terminal and port damage</x:v>
       </x:c>
       <x:c r="F18" t="str">
-        <x:v>Training network reaches 48 institutions / 87 facilities</x:v>
+        <x:v>Possible loading interruptions / operating restrictions</x:v>
       </x:c>
       <x:c r="G18" t="str">
-        <x:v>Larger skilled-labour pipeline</x:v>
+        <x:v>Pressure on Russian Black Sea export capacity and CPC-related logistics</x:v>
       </x:c>
       <x:c r="H18" t="str">
-        <x:v>Maritime industrial-base capacity</x:v>
+        <x:v>Potential crude-flow disruption and higher Black Sea energy-shipping risk</x:v>
       </x:c>
       <x:c r="I18" t="str">
-        <x:v>Policy → training → workforce → capacity</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19">
-      <x:c r="A19" s="10" t="str">
-        <x:v>CHAIN_SEC_001</x:v>
-      </x:c>
-      <x:c r="B19" s="10" t="str">
-        <x:v>EVT_SEC_001</x:v>
-      </x:c>
-      <x:c r="C19" s="10" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D19" s="10" t="str">
-        <x:v>Crew injury on foreign cargo vessel</x:v>
-      </x:c>
-      <x:c r="E19" s="10" t="str">
-        <x:v>SAR / medical response</x:v>
-      </x:c>
-      <x:c r="F19" s="10" t="str">
-        <x:v>Potential voyage interruption</x:v>
-      </x:c>
-      <x:c r="G19" s="10" t="str">
-        <x:v>Official response activity / nearby traffic coordination</x:v>
-      </x:c>
-      <x:c r="H19" s="10" t="str">
-        <x:v>MARSEC casualty awareness</x:v>
-      </x:c>
-      <x:c r="I19" s="10" t="str">
-        <x:v>Safety propagation</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="20">
-      <x:c r="A20" s="10" t="str">
-        <x:v>CHAIN_SEC_002</x:v>
-      </x:c>
-      <x:c r="B20" s="10" t="str">
-        <x:v>EVT_SEC_002</x:v>
-      </x:c>
-      <x:c r="C20" s="10" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D20" s="10" t="str">
-        <x:v>Strong current drives vessel onto rocks</x:v>
-      </x:c>
-      <x:c r="E20" s="10" t="str">
-        <x:v>Grounding and rescue response</x:v>
-      </x:c>
-      <x:c r="F20" s="10" t="str">
-        <x:v>Potential pollution/navigation hazard</x:v>
-      </x:c>
-      <x:c r="G20" s="10" t="str">
-        <x:v>Local operating caution</x:v>
-      </x:c>
-      <x:c r="H20" s="10" t="str">
-        <x:v>Grounding / casualty monitoring</x:v>
-      </x:c>
-      <x:c r="I20" s="10" t="str">
-        <x:v>Safety propagation</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="21">
-      <x:c r="A21" s="10" t="str">
-        <x:v>CHAIN_SEC_003</x:v>
-      </x:c>
-      <x:c r="B21" s="10" t="str">
-        <x:v>EVT_SEC_003</x:v>
-      </x:c>
-      <x:c r="C21" s="10" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D21" s="10" t="str">
-        <x:v>Loss of stability / severe list</x:v>
-      </x:c>
-      <x:c r="E21" s="10" t="str">
-        <x:v>Crew rescue and salvage response</x:v>
-      </x:c>
-      <x:c r="F21" s="10" t="str">
-        <x:v>Fire/pollution monitoring</x:v>
-      </x:c>
-      <x:c r="G21" s="10" t="str">
-        <x:v>Potential coastal/container/cargo consequence</x:v>
-      </x:c>
-      <x:c r="H21" s="10" t="str">
-        <x:v>India maritime casualty and resilience case</x:v>
-      </x:c>
-      <x:c r="I21" s="10" t="str">
-        <x:v>Safety → environmental → commercial</x:v>
+        <x:v>Direct → logistics → energy-market</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -5987,128 +7799,352 @@
     </x:row>
     <x:row r="19">
       <x:c r="A19" t="str">
-        <x:v>SRC133_001</x:v>
+        <x:v>SRC260910_001</x:v>
       </x:c>
       <x:c r="B19" t="str">
-        <x:v>Ship &amp; Bunker</x:v>
+        <x:v>The Maritime Executive</x:v>
       </x:c>
       <x:c r="C19" t="str">
-        <x:v>Peninsula confirms fatal Hercules Star incident at anchorage off Dubai; one crewmember missing; 7,998 DWT tanker chartered from Hercules Tanker Management.</x:v>
+        <x:v>Houthi Forces Attack Saudi Aramco's Jazan Refinery</x:v>
       </x:c>
       <x:c r="D19" t="str">
-        <x:v>https://shipandbunker.com/news/world/583774-peninsula-confirms-tanker-involved-in-incident-off-dubai</x:v>
+        <x:v>https://maritime-executive.com/article/houthi-forces-attack-saudi-aramco-s-jazan-refinery</x:v>
       </x:c>
     </x:row>
     <x:row r="20">
       <x:c r="A20" t="str">
-        <x:v>SRC133_002</x:v>
+        <x:v>SRC260910_002</x:v>
       </x:c>
       <x:c r="B20" t="str">
-        <x:v>CBC News</x:v>
+        <x:v>The Maritime Executive</x:v>
       </x:c>
       <x:c r="C20" t="str">
-        <x:v>Headline-level record: Nisg̱a'a and Tahltan Nations mark official opening of a Stewart, B.C. port as expansion plans take shape. Detailed ownership, capacity and terminal facts remain to be verified.</x:v>
+        <x:v>U.S. Forces Destroy Drug-Runners' Floating Gas Station Off Ecuador</x:v>
       </x:c>
       <x:c r="D20" t="str">
-        <x:v>https://www.cbc.ca/news/canada/british-columbia/nisga-a-talhtan-port-opening-9.7338188</x:v>
+        <x:v>https://maritime-executive.com/article/u-s-forces-destroy-drug-runners-floating-gas-station-off-ecuador</x:v>
       </x:c>
     </x:row>
     <x:row r="21">
       <x:c r="A21" t="str">
-        <x:v>SRC133_003</x:v>
+        <x:v>SRC260910_003</x:v>
       </x:c>
       <x:c r="B21" t="str">
-        <x:v>Reuters</x:v>
+        <x:v>Splash247</x:v>
       </x:c>
       <x:c r="C21" t="str">
-        <x:v>Cruise operators expand private destinations; 12 Caribbean private destinations reported in 2024, with substantial Royal Caribbean, Carnival and Norwegian investment.</x:v>
+        <x:v>Cochin and Drydocks World seal Kochi repair venture</x:v>
       </x:c>
       <x:c r="D21" t="str">
-        <x:v>https://www.reuters.com/business/autos-transportation/cruise-operators-reap-benefits-their-own-private-islands-2024-10-29/</x:v>
+        <x:v>https://splash247.com/cochin-and-drydocks-world-seal-kochi-repair-venture/</x:v>
       </x:c>
     </x:row>
     <x:row r="22">
       <x:c r="A22" t="str">
-        <x:v>SRC134_003</x:v>
+        <x:v>SRC260910_004</x:v>
       </x:c>
       <x:c r="B22" t="str">
-        <x:v>gCaptain</x:v>
+        <x:v>The Maritime Executive</x:v>
       </x:c>
       <x:c r="C22" t="str">
-        <x:v>Hunter Group says a counterparty owes USD 55 million amid a tanker-rate benchmark dispute.</x:v>
+        <x:v>U.S. Hits Five More Iranian Tankers After Second Attack on U.S. Warship</x:v>
       </x:c>
       <x:c r="D22" t="str">
-        <x:v>https://gcaptain.com/oil-tanker-company-says-its-owed-55-million-in-rate-dispute/</x:v>
+        <x:v>https://maritime-executive.com/article/u-s-hits-three-more-iranian-tankers-after-second-attack-on-u-s-warship</x:v>
       </x:c>
     </x:row>
     <x:row r="23">
       <x:c r="A23" t="str">
-        <x:v>SRC134_004</x:v>
+        <x:v>SRC260910_005</x:v>
       </x:c>
       <x:c r="B23" t="str">
-        <x:v>Seaspan</x:v>
+        <x:v>The Maritime Executive</x:v>
       </x:c>
       <x:c r="C23" t="str">
-        <x:v>Seaspan awarded a Babcock Canada submarine-maintenance contract extension through 2032.</x:v>
+        <x:v>HMM Continues Diversification with $3.5B Ore Deal with Vale</x:v>
       </x:c>
       <x:c r="D23" t="str">
-        <x:v>https://www.seaspan.com/press-release/seaspan-awarded-a-submarine-maintenance-contract-extension-by-babcock-canada-through-2032/</x:v>
+        <x:v>https://maritime-executive.com/article/hmm-continues-diversification-with-3-5b-ore-deal-with-vale</x:v>
       </x:c>
     </x:row>
     <x:row r="24">
       <x:c r="A24" t="str">
-        <x:v>SRC134_005</x:v>
+        <x:v>SRC260910_006</x:v>
       </x:c>
       <x:c r="B24" t="str">
-        <x:v>gCaptain</x:v>
+        <x:v>The Maritime Executive</x:v>
       </x:c>
       <x:c r="C24" t="str">
-        <x:v>MSC Shipmanagement and Hong Kong Spirit Shipping and Trading fined USD 1.75 million over illegal oily-waste discharges from MSC SAMIRA III.</x:v>
+        <x:v>Iran Battles to Beat the Blockade</x:v>
       </x:c>
       <x:c r="D24" t="str">
-        <x:v>https://gcaptain.com/msc-shipmanagement-fined-1-75-million-over-illegal-oily-waste-discharges/</x:v>
+        <x:v>https://maritime-executive.com/editorials/iran-battles-to-beat-the-blockade</x:v>
       </x:c>
     </x:row>
     <x:row r="25">
       <x:c r="A25" t="str">
-        <x:v>SRC134_006</x:v>
+        <x:v>SRC260910_007</x:v>
       </x:c>
       <x:c r="B25" t="str">
-        <x:v>gCaptain</x:v>
+        <x:v>The Maritime Executive</x:v>
       </x:c>
       <x:c r="C25" t="str">
-        <x:v>MARAD adds 16 maritime training institutions, taking the network to 48 institutions and 87 facilities.</x:v>
+        <x:v>US Investors Top Hanwha's Bid for Austal USA</x:v>
       </x:c>
       <x:c r="D25" t="str">
-        <x:v>https://gcaptain.com/u-s-adds-16-maritime-training-centers-amid-shipbuilding-push/</x:v>
+        <x:v>https://maritime-executive.com/article/us-investors-top-hanwha-s-bid-for-austal-usa</x:v>
       </x:c>
     </x:row>
     <x:row r="26">
       <x:c r="A26" t="str">
-        <x:v>SRC134_007</x:v>
+        <x:v>SRC260910_008</x:v>
       </x:c>
       <x:c r="B26" t="str">
-        <x:v>gCaptain</x:v>
+        <x:v>Splash247</x:v>
       </x:c>
       <x:c r="C26" t="str">
-        <x:v>Arctic LNG 2 seeks about USD 1 billion from Hanwha Ocean in a shipbuilding-contract dispute.</x:v>
+        <x:v>Simandou's Morebaya port moves into commissioning</x:v>
       </x:c>
       <x:c r="D26" t="str">
-        <x:v>https://gcaptain.com/russias-arctic-lng-2-seeks-1-billion-in-damages-from-south-koreas-hanwha/</x:v>
+        <x:v>https://splash247.com/simandous-morebaya-port-moves-into-commissioning/</x:v>
       </x:c>
     </x:row>
     <x:row r="27">
       <x:c r="A27" t="str">
-        <x:v>SRC134_008</x:v>
+        <x:v>SRC260910_009</x:v>
       </x:c>
       <x:c r="B27" t="str">
-        <x:v>Reuters</x:v>
+        <x:v>Splash247</x:v>
       </x:c>
       <x:c r="C27" t="str">
-        <x:v>Arctic LNG 2 seeks USD 1.02 billion / KRW 1.37 trillion at SIAC over terminated Arc7 LNG-carrier contracts.</x:v>
+        <x:v>Thailand's Songkhla gets first ship-to-shore cranes</x:v>
       </x:c>
       <x:c r="D27" t="str">
-        <x:v>https://www.reuters.com/business/energy/russias-arctic-lng-2-seeks-1-billion-damages-south-koreas-hanwha-2026-09-08/</x:v>
+        <x:v>https://splash247.com/thailands-songkhla-gets-first-ship-to-shore-cranes/</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28">
+      <x:c r="A28" t="str">
+        <x:v>SRC260910_010</x:v>
+      </x:c>
+      <x:c r="B28" t="str">
+        <x:v>Splash247</x:v>
+      </x:c>
+      <x:c r="C28" t="str">
+        <x:v>Ningbo clears $223m offshore wind port development</x:v>
+      </x:c>
+      <x:c r="D28" t="str">
+        <x:v>https://splash247.com/ningbo-clears-223m-offshore-wind-port-development/</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29">
+      <x:c r="A29" t="str">
+        <x:v>SRC260910_011</x:v>
+      </x:c>
+      <x:c r="B29" t="str">
+        <x:v>Splash247</x:v>
+      </x:c>
+      <x:c r="C29" t="str">
+        <x:v>US lines up $15m for Colombo port digital upgrade</x:v>
+      </x:c>
+      <x:c r="D29" t="str">
+        <x:v>https://splash247.com/us-lines-up-15m-for-colombo-port-digital-upgrade/</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30">
+      <x:c r="A30" t="str">
+        <x:v>SRC260910_012</x:v>
+      </x:c>
+      <x:c r="B30" t="str">
+        <x:v>Splash247</x:v>
+      </x:c>
+      <x:c r="C30" t="str">
+        <x:v>Newcastle gets $1.62bn freight access upgrade</x:v>
+      </x:c>
+      <x:c r="D30" t="str">
+        <x:v>https://splash247.com/newcastle-gets-1-62bn-freight-access-upgrade/</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31">
+      <x:c r="A31" t="str">
+        <x:v>SRC260910_013</x:v>
+      </x:c>
+      <x:c r="B31" t="str">
+        <x:v>Splash247</x:v>
+      </x:c>
+      <x:c r="C31" t="str">
+        <x:v>Baltimore adds on-dock grain export gateway</x:v>
+      </x:c>
+      <x:c r="D31" t="str">
+        <x:v>https://splash247.com/baltimore-adds-on-dock-grain-export-gateway/</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32">
+      <x:c r="A32" t="str">
+        <x:v>SRC260910_014</x:v>
+      </x:c>
+      <x:c r="B32" t="str">
+        <x:v>Splash247</x:v>
+      </x:c>
+      <x:c r="C32" t="str">
+        <x:v>Kazakhstan advances $1bn Caspian port hub</x:v>
+      </x:c>
+      <x:c r="D32" t="str">
+        <x:v>https://splash247.com/kazakhstan-advances-1bn-caspian-port-hub/</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33">
+      <x:c r="A33" t="str">
+        <x:v>SRC260910_015</x:v>
+      </x:c>
+      <x:c r="B33" t="str">
+        <x:v>Splash247</x:v>
+      </x:c>
+      <x:c r="C33" t="str">
+        <x:v>Valencia north terminal survives environmental court challenge</x:v>
+      </x:c>
+      <x:c r="D33" t="str">
+        <x:v>https://splash247.com/valencia-north-terminal-survives-environmental-court-challenge/</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34">
+      <x:c r="A34" t="str">
+        <x:v>SRC260910_016</x:v>
+      </x:c>
+      <x:c r="B34" t="str">
+        <x:v>Splash247</x:v>
+      </x:c>
+      <x:c r="C34" t="str">
+        <x:v>Manila South Harbour advances terminal expansion</x:v>
+      </x:c>
+      <x:c r="D34" t="str">
+        <x:v>https://splash247.com/manila-south-harbour-advances-terminal-expansion/</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35">
+      <x:c r="A35" t="str">
+        <x:v>SRC260910_017</x:v>
+      </x:c>
+      <x:c r="B35" t="str">
+        <x:v>Splash247</x:v>
+      </x:c>
+      <x:c r="C35" t="str">
+        <x:v>DP World formalises Mombasa industrial park joint venture</x:v>
+      </x:c>
+      <x:c r="D35" t="str">
+        <x:v>https://splash247.com/dp-world-formalises-mombasa-industrial-park-joint-venture/</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36">
+      <x:c r="A36" t="str">
+        <x:v>SRC260910_018</x:v>
+      </x:c>
+      <x:c r="B36" t="str">
+        <x:v>Splash247</x:v>
+      </x:c>
+      <x:c r="C36" t="str">
+        <x:v>Adani lands 30-year Paradip berth concession</x:v>
+      </x:c>
+      <x:c r="D36" t="str">
+        <x:v>https://splash247.com/adani-lands-30-year-paradip-berth-concession/</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37">
+      <x:c r="A37" t="str">
+        <x:v>SRC260910_019</x:v>
+      </x:c>
+      <x:c r="B37" t="str">
+        <x:v>Splash247</x:v>
+      </x:c>
+      <x:c r="C37" t="str">
+        <x:v>Odfjell Drilling lands $518m semisub deal with Vår Energi</x:v>
+      </x:c>
+      <x:c r="D37" t="str">
+        <x:v>https://splash247.com/odfjell-drilling-lands-518m-semisub-deal-with-var-energi/</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38">
+      <x:c r="A38" t="str">
+        <x:v>SRC260910_020</x:v>
+      </x:c>
+      <x:c r="B38" t="str">
+        <x:v>Splash247</x:v>
+      </x:c>
+      <x:c r="C38" t="str">
+        <x:v>Alam Maritim head faces fraud charges tied to vessel rates</x:v>
+      </x:c>
+      <x:c r="D38" t="str">
+        <x:v>https://splash247.com/alam-maritim-head-faces-fraud-charges-tied-to-vessel-rates/</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39">
+      <x:c r="A39" t="str">
+        <x:v>SRC260910_021</x:v>
+      </x:c>
+      <x:c r="B39" t="str">
+        <x:v>Splash247</x:v>
+      </x:c>
+      <x:c r="C39" t="str">
+        <x:v>Ernst Russ doubles down on tankers with Cargill-backed pair</x:v>
+      </x:c>
+      <x:c r="D39" t="str">
+        <x:v>https://splash247.com/ernst-russ-doubles-down-on-tankers-with-cargill-backed-pair/</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40">
+      <x:c r="A40" t="str">
+        <x:v>SRC260910_022</x:v>
+      </x:c>
+      <x:c r="B40" t="str">
+        <x:v>Splash247</x:v>
+      </x:c>
+      <x:c r="C40" t="str">
+        <x:v>CMA CGM says it met obligations in $186m Samsung dispute</x:v>
+      </x:c>
+      <x:c r="D40" t="str">
+        <x:v>https://splash247.com/cma-cgm-says-it-met-obligations-in-186m-samsung-dispute/</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41">
+      <x:c r="A41" t="str">
+        <x:v>SRC260910_023</x:v>
+      </x:c>
+      <x:c r="B41" t="str">
+        <x:v>Splash247</x:v>
+      </x:c>
+      <x:c r="C41" t="str">
+        <x:v>Safe Bulkers raises $94m for fleet push</x:v>
+      </x:c>
+      <x:c r="D41" t="str">
+        <x:v>https://splash247.com/safe-bulkers-raises-94m-for-fleet-push/</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="42">
+      <x:c r="A42" t="str">
+        <x:v>SRC260910_024</x:v>
+      </x:c>
+      <x:c r="B42" t="str">
+        <x:v>Splash247</x:v>
+      </x:c>
+      <x:c r="C42" t="str">
+        <x:v>Hormuz attacks reach wartime high</x:v>
+      </x:c>
+      <x:c r="D42" t="str">
+        <x:v>https://splash247.com/hormuz-attacks-reach-wartime-high/</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="43">
+      <x:c r="A43" t="str">
+        <x:v>SRC260910_025</x:v>
+      </x:c>
+      <x:c r="B43" t="str">
+        <x:v>Gulf News</x:v>
+      </x:c>
+      <x:c r="C43" t="str">
+        <x:v>Hormozgan / Qeshm / Sirik / Minab / Taif explosions</x:v>
+      </x:c>
+      <x:c r="D43" t="str">
+        <x:v>https://gulfnews.com/world/mena/iran-rocked-by-explosions-as-trump-says-us-iran-war-wont-end-until-after-midterm-elections-1.500669266</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/data/13_events_hazards.xlsx
+++ b/data/13_events_hazards.xlsx
@@ -2,16 +2,16 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Events" sheetId="1" r:id="R81fefc1772aa4a55"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Event Locations" sheetId="2" r:id="R7e92f84546aa4868"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Event Asset Links" sheetId="3" r:id="Ree6e7f5511aa49fc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Event Company Links" sheetId="4" r:id="R538f77c7a22346cf"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Event System Links" sheetId="5" r:id="Rf276195771d947d8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Impact Chains" sheetId="6" r:id="R4e243b1778384eae"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Event Status History" sheetId="7" r:id="R86b814b329ac48cc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Event Taxonomy" sheetId="8" r:id="R2f5e4e35339c4056"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="9" r:id="R5901a4f7b3414520"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overview" sheetId="10" r:id="R22533ce8a4054d5a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Events" sheetId="1" r:id="R927b3c0d35114a86"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Event Locations" sheetId="2" r:id="Rdf5f0ab6b6a84015"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Event Asset Links" sheetId="3" r:id="R6da9788c953948ef"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Event Company Links" sheetId="4" r:id="R65042351f2144dc0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Event System Links" sheetId="5" r:id="R8b8c626f1d1749be"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Impact Chains" sheetId="6" r:id="Rfc59275c74b04406"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Event Status History" sheetId="7" r:id="Rb4c58a6eaea84d8d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Event Taxonomy" sheetId="8" r:id="Rccdab749efba448c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="9" r:id="Rfc1a818d8e4144c0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overview" sheetId="10" r:id="Rf0118c9b286c44cc"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -71,7 +71,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="19">
+  <x:cellXfs count="20">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -105,6 +105,7 @@
     <x:xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -2674,6 +2675,57 @@
         <x:v>https://oilprice.com/Latest-Energy-News/World-News/Ukraine-Targets-Russias-Key-Black-Sea-Oil-Port.html</x:v>
       </x:c>
     </x:row>
+    <x:row r="47">
+      <x:c r="A47" s="10" t="str">
+        <x:v>EVT260911_001</x:v>
+      </x:c>
+      <x:c r="B47" s="10" t="str">
+        <x:v>2026-09-10</x:v>
+      </x:c>
+      <x:c r="C47" s="10"/>
+      <x:c r="D47" s="10" t="str">
+        <x:v>Port / Infrastructure Incident</x:v>
+      </x:c>
+      <x:c r="E47" s="10" t="str">
+        <x:v>Shipyard / vessel fire</x:v>
+      </x:c>
+      <x:c r="F47" s="10" t="str">
+        <x:v>Critical</x:v>
+      </x:c>
+      <x:c r="G47" s="10" t="str">
+        <x:v>Investigation / recovery</x:v>
+      </x:c>
+      <x:c r="H47" s="10" t="str">
+        <x:v>Maritime / Shipyard</x:v>
+      </x:c>
+      <x:c r="I47" s="10" t="str">
+        <x:v>China</x:v>
+      </x:c>
+      <x:c r="J47" s="10" t="str">
+        <x:v>Qingdao Beihai Shipbuilding, Qingdao</x:v>
+      </x:c>
+      <x:c r="K47" s="10" t="str">
+        <x:v>Ocean Melody fire kills 25 at Qingdao Beihai shipyard</x:v>
+      </x:c>
+      <x:c r="L47" s="10" t="str">
+        <x:v>Fire broke out aboard Liberia-flagged bulk carrier Ocean Melody while under repair/inspection at Qingdao Beihai Shipbuilding. Reuters reported 25 fatalities and five hospitalized.</x:v>
+      </x:c>
+      <x:c r="M47" s="10" t="str">
+        <x:v>Fatal shipyard/vessel casualty; investigation and potential local yard recovery constraints</x:v>
+      </x:c>
+      <x:c r="N47" s="10" t="str">
+        <x:v>Potential repair-slot disruption and wider safety-inspection implications if restrictions expand across CSSC or Chinese yards.</x:v>
+      </x:c>
+      <x:c r="O47" s="10" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="P47" s="10" t="str">
+        <x:v>SRC260911_001</x:v>
+      </x:c>
+      <x:c r="Q47" s="10" t="str">
+        <x:v>https://www.reuters.com/world/asia-pacific/fire-cargo-vessel-china-shipyard-causes-major-casualties-state-media-reports-2026-09-10/</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -4045,6 +4097,28 @@
         <x:v>Port-city marker for the reported Novorossiysk strike; not a precise impact coordinate.</x:v>
       </x:c>
     </x:row>
+    <x:row r="50">
+      <x:c r="A50" s="10" t="str">
+        <x:v>LOC260911_001</x:v>
+      </x:c>
+      <x:c r="B50" s="10" t="str">
+        <x:v>EVT260911_001</x:v>
+      </x:c>
+      <x:c r="C50" s="10" t="str">
+        <x:v>Qingdao Beihai Shipbuilding</x:v>
+      </x:c>
+      <x:c r="D50" s="10" t="str">
+        <x:v>China</x:v>
+      </x:c>
+      <x:c r="E50" s="10"/>
+      <x:c r="F50" s="10"/>
+      <x:c r="G50" s="10" t="str">
+        <x:v>Shipyard-level</x:v>
+      </x:c>
+      <x:c r="H50" s="10" t="str">
+        <x:v>Qingdao, Shandong; no coordinates stored in this release</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -5208,6 +5282,58 @@
         <x:v>Port and fuel-oil infrastructure struck</x:v>
       </x:c>
     </x:row>
+    <x:row r="45">
+      <x:c r="A45" s="10" t="str">
+        <x:v>EAL260911_001</x:v>
+      </x:c>
+      <x:c r="B45" s="10" t="str">
+        <x:v>EVT260911_001</x:v>
+      </x:c>
+      <x:c r="C45" s="10" t="str">
+        <x:v>VESSEL_OCEAN_MELODY</x:v>
+      </x:c>
+      <x:c r="D45" s="10" t="str">
+        <x:v>Ocean Melody</x:v>
+      </x:c>
+      <x:c r="E45" s="10" t="str">
+        <x:v>Vessel</x:v>
+      </x:c>
+      <x:c r="F45" s="10" t="str">
+        <x:v>DIRECTLY_AFFECTED</x:v>
+      </x:c>
+      <x:c r="G45" s="10" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="H45" s="10" t="str">
+        <x:v>Fire occurred while vessel was under repair / inspection</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="46">
+      <x:c r="A46" s="10" t="str">
+        <x:v>EAL260911_002</x:v>
+      </x:c>
+      <x:c r="B46" s="10" t="str">
+        <x:v>EVT260911_001</x:v>
+      </x:c>
+      <x:c r="C46" s="10" t="str">
+        <x:v>YARD_QINGDAO_BEIHAI</x:v>
+      </x:c>
+      <x:c r="D46" s="10" t="str">
+        <x:v>Qingdao Beihai Shipbuilding</x:v>
+      </x:c>
+      <x:c r="E46" s="10" t="str">
+        <x:v>Shipyard</x:v>
+      </x:c>
+      <x:c r="F46" s="10" t="str">
+        <x:v>INCIDENT_LOCATION</x:v>
+      </x:c>
+      <x:c r="G46" s="10" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="H46" s="10" t="str">
+        <x:v>Fatal fire at CSSC-controlled Qingdao yard</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -6122,6 +6248,66 @@
         <x:v>Issuer / fleet investor</x:v>
       </x:c>
       <x:c r="F45" t="str">
+        <x:v>High</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="46">
+      <x:c r="A46" s="10" t="str">
+        <x:v>ECL260911_001</x:v>
+      </x:c>
+      <x:c r="B46" s="10" t="str">
+        <x:v>EVT260911_001</x:v>
+      </x:c>
+      <x:c r="C46" s="10" t="str">
+        <x:v>COMP_CSSC</x:v>
+      </x:c>
+      <x:c r="D46" s="10" t="str">
+        <x:v>China State Shipbuilding Corporation (CSSC)</x:v>
+      </x:c>
+      <x:c r="E46" s="10" t="str">
+        <x:v>Controls affected shipyard</x:v>
+      </x:c>
+      <x:c r="F46" s="10" t="str">
+        <x:v>High</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="47">
+      <x:c r="A47" s="10" t="str">
+        <x:v>ECL260911_002</x:v>
+      </x:c>
+      <x:c r="B47" s="10" t="str">
+        <x:v>EVT260911_001</x:v>
+      </x:c>
+      <x:c r="C47" s="10" t="str">
+        <x:v>COMP_HUILI_SHIPPING</x:v>
+      </x:c>
+      <x:c r="D47" s="10" t="str">
+        <x:v>Huili Shipping Co Ltd</x:v>
+      </x:c>
+      <x:c r="E47" s="10" t="str">
+        <x:v>Registered vessel owner</x:v>
+      </x:c>
+      <x:c r="F47" s="10" t="str">
+        <x:v>High</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="48">
+      <x:c r="A48" s="10" t="str">
+        <x:v>ECL260911_003</x:v>
+      </x:c>
+      <x:c r="B48" s="10" t="str">
+        <x:v>EVT260911_001</x:v>
+      </x:c>
+      <x:c r="C48" s="10" t="str">
+        <x:v>COMP_YUYANGKUNPENG</x:v>
+      </x:c>
+      <x:c r="D48" s="10" t="str">
+        <x:v>Yuyangkunpeng Shanghai Ship Management</x:v>
+      </x:c>
+      <x:c r="E48" s="10" t="str">
+        <x:v>Vessel manager</x:v>
+      </x:c>
+      <x:c r="F48" s="10" t="str">
         <x:v>High</x:v>
       </x:c>
     </x:row>

--- a/data/13_events_hazards.xlsx
+++ b/data/13_events_hazards.xlsx
@@ -2,16 +2,16 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Events" sheetId="1" r:id="Rfe7236018baf4a98"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Event Locations" sheetId="2" r:id="R86eec5cda9d844cf"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Event Asset Links" sheetId="3" r:id="R6547d9e82ed6496b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Event Company Links" sheetId="4" r:id="R94c77af019074f33"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Event System Links" sheetId="5" r:id="R1a09937e11224944"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Impact Chains" sheetId="6" r:id="R67bf72a795544cf4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Event Status History" sheetId="7" r:id="Rbd474c14fccb4260"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Event Taxonomy" sheetId="8" r:id="Rbe1f2afa35e9451b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="9" r:id="R863aafdc607e4755"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overview" sheetId="10" r:id="Rc87020ee048a4932"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Events" sheetId="1" r:id="Rbcd13a3fc112482a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Event Locations" sheetId="2" r:id="Rd51ba5cd51564a6a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Event Asset Links" sheetId="3" r:id="R7fed11fec54c427a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Event Company Links" sheetId="4" r:id="Ra9b9d5e5960a48c7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Event System Links" sheetId="5" r:id="R820f382defc04f9e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Impact Chains" sheetId="6" r:id="R7ee97b5cd60448c3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Event Status History" sheetId="7" r:id="Reddd693be7894e7d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Event Taxonomy" sheetId="8" r:id="R9d6e5b5575c448ff"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="9" r:id="R31ee07381dd24204"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overview" sheetId="10" r:id="R794c527f78844a79"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -7192,6 +7192,32 @@
         <x:v>Aviation strike / cargo gateway exposure.</x:v>
       </x:c>
     </x:row>
+    <x:row r="58">
+      <x:c r="A58" t="str">
+        <x:v>EAL_SEC_008</x:v>
+      </x:c>
+      <x:c r="B58" t="str">
+        <x:v>EVT_SEC_005</x:v>
+      </x:c>
+      <x:c r="C58" t="str">
+        <x:v>PORTG0206</x:v>
+      </x:c>
+      <x:c r="D58" t="str">
+        <x:v>Port of Montevideo</x:v>
+      </x:c>
+      <x:c r="E58" t="str">
+        <x:v>Port</x:v>
+      </x:c>
+      <x:c r="F58" t="str">
+        <x:v>AFFECTED_PARENT_PORT</x:v>
+      </x:c>
+      <x:c r="G58" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="H58" t="str">
+        <x:v>Parent-port propagation for TCP strike so Port of Montevideo security/disruption view inherits terminal event.</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
